--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Neal Pool - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B516147-6270-407C-991A-329A71199FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D026180F-401F-471A-8843-557DA98CDA5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Neal Pool - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D026180F-401F-471A-8843-557DA98CDA5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D444DE9E-F926-4E2D-B376-E2386E6B5E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="57">
   <si>
     <t>Company Name</t>
   </si>
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t>Jeff Shults</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
   </si>
 </sst>
 </file>
@@ -9512,126 +9515,582 @@
       </c>
     </row>
     <row r="322" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H322" s="2"/>
-      <c r="I322" s="1"/>
+      <c r="B322" t="s">
+        <v>29</v>
+      </c>
+      <c r="C322">
+        <v>3832</v>
+      </c>
+      <c r="D322" t="s">
+        <v>50</v>
+      </c>
+      <c r="F322" t="s">
+        <v>56</v>
+      </c>
+      <c r="G322" t="s">
+        <v>10</v>
+      </c>
+      <c r="H322" s="2">
+        <v>8.3217592592592596E-3</v>
+      </c>
+      <c r="I322" s="1">
+        <v>46118.796759259261</v>
+      </c>
+      <c r="J322">
+        <v>1</v>
+      </c>
+      <c r="K322" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="323" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H323" s="2"/>
-      <c r="I323" s="1"/>
+      <c r="B323" t="s">
+        <v>29</v>
+      </c>
+      <c r="C323">
+        <v>2740</v>
+      </c>
+      <c r="D323" t="s">
+        <v>34</v>
+      </c>
+      <c r="F323" t="s">
+        <v>56</v>
+      </c>
+      <c r="G323" t="s">
+        <v>10</v>
+      </c>
+      <c r="H323" s="2">
+        <v>8.4259259259259253E-3</v>
+      </c>
+      <c r="I323" s="1">
+        <v>46118.796759259261</v>
+      </c>
+      <c r="J323">
+        <v>1</v>
+      </c>
+      <c r="K323" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="324" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H324" s="2"/>
-      <c r="I324" s="1"/>
+      <c r="B324" t="s">
+        <v>29</v>
+      </c>
+      <c r="C324">
+        <v>3885</v>
+      </c>
+      <c r="D324" t="s">
+        <v>51</v>
+      </c>
+      <c r="F324" t="s">
+        <v>56</v>
+      </c>
+      <c r="G324" t="s">
+        <v>10</v>
+      </c>
+      <c r="H324" s="2">
+        <v>7.0949074074074074E-3</v>
+      </c>
+      <c r="I324" s="1">
+        <v>46118.797453703701</v>
+      </c>
+      <c r="J324">
+        <v>0</v>
+      </c>
+      <c r="K324" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="325" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H325" s="2"/>
-      <c r="I325" s="1"/>
+      <c r="B325" t="s">
+        <v>29</v>
+      </c>
+      <c r="C325">
+        <v>2742</v>
+      </c>
+      <c r="D325" t="s">
+        <v>36</v>
+      </c>
+      <c r="F325" t="s">
+        <v>56</v>
+      </c>
+      <c r="G325" t="s">
+        <v>10</v>
+      </c>
+      <c r="H325" s="2">
+        <v>7.8819444444444449E-3</v>
+      </c>
+      <c r="I325" s="1">
+        <v>46118.798148148147</v>
+      </c>
+      <c r="J325">
+        <v>1</v>
+      </c>
+      <c r="K325" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="326" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H326" s="2"/>
-      <c r="I326" s="1"/>
+      <c r="B326" t="s">
+        <v>29</v>
+      </c>
+      <c r="C326">
+        <v>2737</v>
+      </c>
+      <c r="D326" t="s">
+        <v>37</v>
+      </c>
+      <c r="F326" t="s">
+        <v>56</v>
+      </c>
+      <c r="G326" t="s">
+        <v>12</v>
+      </c>
+      <c r="H326" s="2">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="I326" s="1">
+        <v>46118.798148148147</v>
+      </c>
+      <c r="J326">
+        <v>0</v>
+      </c>
+      <c r="K326" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="327" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H327" s="2"/>
       <c r="I327" s="1"/>
+      <c r="K327" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="328" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H328" s="2"/>
-      <c r="I328" s="1"/>
+      <c r="B328" t="s">
+        <v>29</v>
+      </c>
+      <c r="C328">
+        <v>2748</v>
+      </c>
+      <c r="D328" t="s">
+        <v>38</v>
+      </c>
+      <c r="F328" t="s">
+        <v>56</v>
+      </c>
+      <c r="G328" t="s">
+        <v>13</v>
+      </c>
+      <c r="H328" s="2">
+        <v>0</v>
+      </c>
+      <c r="I328" s="1">
+        <v>46118.798842592594</v>
+      </c>
+      <c r="J328">
+        <v>1</v>
+      </c>
+      <c r="K328" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="329" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H329" s="2"/>
-      <c r="I329" s="1"/>
+      <c r="B329" t="s">
+        <v>29</v>
+      </c>
+      <c r="C329">
+        <v>2745</v>
+      </c>
+      <c r="D329" t="s">
+        <v>39</v>
+      </c>
+      <c r="F329" t="s">
+        <v>56</v>
+      </c>
+      <c r="G329" t="s">
+        <v>10</v>
+      </c>
+      <c r="H329" s="2">
+        <v>7.9745370370370369E-3</v>
+      </c>
+      <c r="I329" s="1">
+        <v>46118.799537037034</v>
+      </c>
+      <c r="J329">
+        <v>1</v>
+      </c>
+      <c r="K329" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="330" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H330" s="2"/>
-      <c r="I330" s="1"/>
+      <c r="B330" t="s">
+        <v>29</v>
+      </c>
+      <c r="C330">
+        <v>2246</v>
+      </c>
+      <c r="D330" t="s">
+        <v>30</v>
+      </c>
+      <c r="F330" t="s">
+        <v>56</v>
+      </c>
+      <c r="G330" t="s">
+        <v>10</v>
+      </c>
+      <c r="H330" s="2">
+        <v>7.4652777777777781E-3</v>
+      </c>
+      <c r="I330" s="1">
+        <v>46118.799537037034</v>
+      </c>
+      <c r="J330">
+        <v>1</v>
+      </c>
+      <c r="K330" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="331" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H331" s="2"/>
-      <c r="I331" s="1"/>
+      <c r="B331" t="s">
+        <v>29</v>
+      </c>
+      <c r="C331">
+        <v>5274</v>
+      </c>
+      <c r="D331" t="s">
+        <v>55</v>
+      </c>
+      <c r="F331" t="s">
+        <v>56</v>
+      </c>
+      <c r="G331" t="s">
+        <v>10</v>
+      </c>
+      <c r="H331" s="2">
+        <v>1.1469907407407408E-2</v>
+      </c>
+      <c r="I331" s="1">
+        <v>46118.80023148148</v>
+      </c>
+      <c r="J331">
+        <v>1</v>
+      </c>
+      <c r="K331" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="332" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H332" s="2"/>
-      <c r="I332" s="1"/>
+      <c r="B332" t="s">
+        <v>29</v>
+      </c>
+      <c r="C332">
+        <v>2749</v>
+      </c>
+      <c r="D332" t="s">
+        <v>42</v>
+      </c>
+      <c r="F332" t="s">
+        <v>56</v>
+      </c>
+      <c r="G332" t="s">
+        <v>12</v>
+      </c>
+      <c r="H332" s="2">
+        <v>6.5393518518518517E-3</v>
+      </c>
+      <c r="I332" s="1">
+        <v>46118.800925925927</v>
+      </c>
+      <c r="J332">
+        <v>1</v>
+      </c>
+      <c r="K332" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="333" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H333" s="2"/>
       <c r="I333" s="1"/>
+      <c r="K333" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="334" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H334" s="2"/>
-      <c r="I334" s="1"/>
+      <c r="B334" t="s">
+        <v>29</v>
+      </c>
+      <c r="C334">
+        <v>5032</v>
+      </c>
+      <c r="D334" t="s">
+        <v>54</v>
+      </c>
+      <c r="F334" t="s">
+        <v>56</v>
+      </c>
+      <c r="G334" t="s">
+        <v>10</v>
+      </c>
+      <c r="H334" s="2">
+        <v>7.4537037037037037E-3</v>
+      </c>
+      <c r="I334" s="1">
+        <v>46118.801620370374</v>
+      </c>
+      <c r="J334">
+        <v>1</v>
+      </c>
+      <c r="K334" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="335" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H335" s="2"/>
-      <c r="I335" s="1"/>
+      <c r="B335" t="s">
+        <v>29</v>
+      </c>
+      <c r="C335">
+        <v>4755</v>
+      </c>
+      <c r="D335" t="s">
+        <v>53</v>
+      </c>
+      <c r="F335" t="s">
+        <v>56</v>
+      </c>
+      <c r="G335" t="s">
+        <v>13</v>
+      </c>
+      <c r="H335" s="2">
+        <v>0</v>
+      </c>
+      <c r="I335" s="1">
+        <v>46118.801620370374</v>
+      </c>
+      <c r="J335">
+        <v>1</v>
+      </c>
+      <c r="K335" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="336" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H336" s="2"/>
-      <c r="I336" s="1"/>
-    </row>
-    <row r="337" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H337" s="2"/>
-      <c r="I337" s="1"/>
-    </row>
-    <row r="338" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H338" s="2"/>
-      <c r="I338" s="1"/>
-    </row>
-    <row r="339" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H339" s="2"/>
-      <c r="I339" s="1"/>
-    </row>
-    <row r="340" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H340" s="2"/>
-      <c r="I340" s="1"/>
-    </row>
-    <row r="341" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H341" s="2"/>
-      <c r="I341" s="1"/>
-    </row>
-    <row r="342" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B336" t="s">
+        <v>29</v>
+      </c>
+      <c r="C336">
+        <v>2245</v>
+      </c>
+      <c r="D336" t="s">
+        <v>32</v>
+      </c>
+      <c r="F336" t="s">
+        <v>56</v>
+      </c>
+      <c r="G336" t="s">
+        <v>10</v>
+      </c>
+      <c r="H336" s="2">
+        <v>7.1064814814814819E-3</v>
+      </c>
+      <c r="I336" s="1">
+        <v>46118.802314814813</v>
+      </c>
+      <c r="J336">
+        <v>1</v>
+      </c>
+      <c r="K336" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="337" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B337" t="s">
+        <v>29</v>
+      </c>
+      <c r="C337">
+        <v>2750</v>
+      </c>
+      <c r="D337" t="s">
+        <v>44</v>
+      </c>
+      <c r="F337" t="s">
+        <v>56</v>
+      </c>
+      <c r="G337" t="s">
+        <v>10</v>
+      </c>
+      <c r="H337" s="2">
+        <v>8.4953703703703701E-3</v>
+      </c>
+      <c r="I337" s="1">
+        <v>46118.802314814813</v>
+      </c>
+      <c r="J337">
+        <v>1</v>
+      </c>
+      <c r="K337" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B338" t="s">
+        <v>29</v>
+      </c>
+      <c r="C338">
+        <v>2747</v>
+      </c>
+      <c r="D338" t="s">
+        <v>45</v>
+      </c>
+      <c r="F338" t="s">
+        <v>56</v>
+      </c>
+      <c r="G338" t="s">
+        <v>10</v>
+      </c>
+      <c r="H338" s="2">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="I338" s="1">
+        <v>46118.80300925926</v>
+      </c>
+      <c r="J338">
+        <v>0</v>
+      </c>
+      <c r="K338" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="339" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B339" t="s">
+        <v>29</v>
+      </c>
+      <c r="C339">
+        <v>2741</v>
+      </c>
+      <c r="D339" t="s">
+        <v>46</v>
+      </c>
+      <c r="F339" t="s">
+        <v>56</v>
+      </c>
+      <c r="G339" t="s">
+        <v>13</v>
+      </c>
+      <c r="H339" s="2">
+        <v>0</v>
+      </c>
+      <c r="I339" s="1">
+        <v>46118.803703703707</v>
+      </c>
+      <c r="J339">
+        <v>1</v>
+      </c>
+      <c r="K339" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="340" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B340" t="s">
+        <v>29</v>
+      </c>
+      <c r="C340">
+        <v>2739</v>
+      </c>
+      <c r="D340" t="s">
+        <v>47</v>
+      </c>
+      <c r="F340" t="s">
+        <v>56</v>
+      </c>
+      <c r="G340" t="s">
+        <v>10</v>
+      </c>
+      <c r="H340" s="2">
+        <v>7.4884259259259262E-3</v>
+      </c>
+      <c r="I340" s="1">
+        <v>46118.803703703707</v>
+      </c>
+      <c r="J340">
+        <v>1</v>
+      </c>
+      <c r="K340" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="341" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B341" t="s">
+        <v>29</v>
+      </c>
+      <c r="C341">
+        <v>2736</v>
+      </c>
+      <c r="D341" t="s">
+        <v>48</v>
+      </c>
+      <c r="F341" t="s">
+        <v>56</v>
+      </c>
+      <c r="G341" t="s">
+        <v>13</v>
+      </c>
+      <c r="H341" s="2">
+        <v>0</v>
+      </c>
+      <c r="I341" s="1">
+        <v>46118.804398148146</v>
+      </c>
+      <c r="J341">
+        <v>1</v>
+      </c>
+      <c r="K341" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="342" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H342" s="2"/>
       <c r="I342" s="1"/>
     </row>
-    <row r="343" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H343" s="2"/>
       <c r="I343" s="1"/>
     </row>
-    <row r="344" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H344" s="2"/>
       <c r="I344" s="1"/>
     </row>
-    <row r="345" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H345" s="2"/>
       <c r="I345" s="1"/>
     </row>
-    <row r="346" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H346" s="2"/>
       <c r="I346" s="1"/>
     </row>
-    <row r="347" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H347" s="2"/>
       <c r="I347" s="1"/>
     </row>
-    <row r="348" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H348" s="2"/>
       <c r="I348" s="1"/>
     </row>
-    <row r="349" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H349" s="2"/>
       <c r="I349" s="1"/>
     </row>
-    <row r="350" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H350" s="2"/>
       <c r="I350" s="1"/>
     </row>
-    <row r="351" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H351" s="2"/>
       <c r="I351" s="1"/>
     </row>
-    <row r="352" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H352" s="2"/>
       <c r="I352" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Neal Pool - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D444DE9E-F926-4E2D-B376-E2386E6B5E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0F7EBF-D78B-4AB8-AFD4-0D4F5D364798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -9689,7 +9689,7 @@
         <v>46118.798842592594</v>
       </c>
       <c r="J328">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K328" t="s">
         <v>11</v>
@@ -9861,16 +9861,16 @@
         <v>56</v>
       </c>
       <c r="G335" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H335" s="2">
-        <v>0</v>
+        <v>8.4027777777777781E-3</v>
       </c>
       <c r="I335" s="1">
         <v>46118.801620370374</v>
       </c>
       <c r="J335">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K335" t="s">
         <v>11</v>
@@ -9986,7 +9986,7 @@
         <v>46118.803703703707</v>
       </c>
       <c r="J339">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K339" t="s">
         <v>11</v>
@@ -10035,16 +10035,16 @@
         <v>56</v>
       </c>
       <c r="G341" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H341" s="2">
-        <v>0</v>
+        <v>4.1319444444444442E-3</v>
       </c>
       <c r="I341" s="1">
         <v>46118.804398148146</v>
       </c>
       <c r="J341">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K341" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Neal Pool - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0F7EBF-D78B-4AB8-AFD4-0D4F5D364798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACCC5DC-2060-49AC-80C3-2261132CD9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -9689,7 +9689,7 @@
         <v>46118.798842592594</v>
       </c>
       <c r="J328">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K328" t="s">
         <v>11</v>
@@ -9977,16 +9977,16 @@
         <v>56</v>
       </c>
       <c r="G339" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H339" s="2">
-        <v>0</v>
+        <v>5.7060185185185183E-3</v>
       </c>
       <c r="I339" s="1">
         <v>46118.803703703707</v>
       </c>
       <c r="J339">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K339" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Neal Pool - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACCC5DC-2060-49AC-80C3-2261132CD9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28A0836-08E4-4995-BECC-4661194B4C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="58">
   <si>
     <t>Company Name</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
+  </si>
+  <si>
+    <t>Rules for Safe Driving</t>
   </si>
 </sst>
 </file>
@@ -9680,16 +9683,16 @@
         <v>56</v>
       </c>
       <c r="G328" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H328" s="2">
-        <v>0</v>
+        <v>1.412037037037037E-2</v>
       </c>
       <c r="I328" s="1">
         <v>46118.798842592594</v>
       </c>
       <c r="J328">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K328" t="s">
         <v>11</v>
@@ -10051,110 +10054,560 @@
       </c>
     </row>
     <row r="342" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H342" s="2"/>
-      <c r="I342" s="1"/>
+      <c r="B342" t="s">
+        <v>29</v>
+      </c>
+      <c r="C342">
+        <v>3832</v>
+      </c>
+      <c r="D342" t="s">
+        <v>50</v>
+      </c>
+      <c r="F342" t="s">
+        <v>57</v>
+      </c>
+      <c r="G342" t="s">
+        <v>10</v>
+      </c>
+      <c r="H342" s="2">
+        <v>5.092592592592593E-3</v>
+      </c>
+      <c r="I342" s="1">
+        <v>46146.687268518515</v>
+      </c>
+      <c r="J342">
+        <v>0</v>
+      </c>
+      <c r="K342" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="343" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H343" s="2"/>
-      <c r="I343" s="1"/>
+      <c r="B343" t="s">
+        <v>29</v>
+      </c>
+      <c r="C343">
+        <v>2740</v>
+      </c>
+      <c r="D343" t="s">
+        <v>34</v>
+      </c>
+      <c r="F343" t="s">
+        <v>57</v>
+      </c>
+      <c r="G343" t="s">
+        <v>13</v>
+      </c>
+      <c r="H343" s="2">
+        <v>0</v>
+      </c>
+      <c r="I343" s="1">
+        <v>46146.687962962962</v>
+      </c>
+      <c r="J343">
+        <v>0</v>
+      </c>
+      <c r="K343" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="344" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H344" s="2"/>
-      <c r="I344" s="1"/>
+      <c r="B344" t="s">
+        <v>29</v>
+      </c>
+      <c r="C344">
+        <v>3885</v>
+      </c>
+      <c r="D344" t="s">
+        <v>51</v>
+      </c>
+      <c r="F344" t="s">
+        <v>57</v>
+      </c>
+      <c r="G344" t="s">
+        <v>10</v>
+      </c>
+      <c r="H344" s="2">
+        <v>4.6759259259259263E-3</v>
+      </c>
+      <c r="I344" s="1">
+        <v>46146.687962962962</v>
+      </c>
+      <c r="J344">
+        <v>0</v>
+      </c>
+      <c r="K344" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="345" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H345" s="2"/>
-      <c r="I345" s="1"/>
+      <c r="B345" t="s">
+        <v>29</v>
+      </c>
+      <c r="C345">
+        <v>2742</v>
+      </c>
+      <c r="D345" t="s">
+        <v>36</v>
+      </c>
+      <c r="F345" t="s">
+        <v>57</v>
+      </c>
+      <c r="G345" t="s">
+        <v>13</v>
+      </c>
+      <c r="H345" s="2">
+        <v>0</v>
+      </c>
+      <c r="I345" s="1">
+        <v>46146.688657407409</v>
+      </c>
+      <c r="J345">
+        <v>0</v>
+      </c>
+      <c r="K345" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="346" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H346" s="2"/>
-      <c r="I346" s="1"/>
+      <c r="B346" t="s">
+        <v>29</v>
+      </c>
+      <c r="C346">
+        <v>2737</v>
+      </c>
+      <c r="D346" t="s">
+        <v>37</v>
+      </c>
+      <c r="F346" t="s">
+        <v>57</v>
+      </c>
+      <c r="G346" t="s">
+        <v>13</v>
+      </c>
+      <c r="H346" s="2">
+        <v>0</v>
+      </c>
+      <c r="I346" s="1">
+        <v>46146.689351851855</v>
+      </c>
+      <c r="J346">
+        <v>0</v>
+      </c>
+      <c r="K346" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="347" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H347" s="2"/>
-      <c r="I347" s="1"/>
+      <c r="B347" t="s">
+        <v>29</v>
+      </c>
+      <c r="C347">
+        <v>2748</v>
+      </c>
+      <c r="D347" t="s">
+        <v>38</v>
+      </c>
+      <c r="F347" t="s">
+        <v>57</v>
+      </c>
+      <c r="G347" t="s">
+        <v>13</v>
+      </c>
+      <c r="H347" s="2">
+        <v>0</v>
+      </c>
+      <c r="I347" s="1">
+        <v>46146.689351851855</v>
+      </c>
+      <c r="J347">
+        <v>0</v>
+      </c>
+      <c r="K347" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="348" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H348" s="2"/>
-      <c r="I348" s="1"/>
+      <c r="B348" t="s">
+        <v>29</v>
+      </c>
+      <c r="C348">
+        <v>2745</v>
+      </c>
+      <c r="D348" t="s">
+        <v>39</v>
+      </c>
+      <c r="F348" t="s">
+        <v>57</v>
+      </c>
+      <c r="G348" t="s">
+        <v>13</v>
+      </c>
+      <c r="H348" s="2">
+        <v>0</v>
+      </c>
+      <c r="I348" s="1">
+        <v>46146.690046296295</v>
+      </c>
+      <c r="J348">
+        <v>0</v>
+      </c>
+      <c r="K348" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="349" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H349" s="2"/>
-      <c r="I349" s="1"/>
+      <c r="B349" t="s">
+        <v>29</v>
+      </c>
+      <c r="C349">
+        <v>2246</v>
+      </c>
+      <c r="D349" t="s">
+        <v>30</v>
+      </c>
+      <c r="F349" t="s">
+        <v>57</v>
+      </c>
+      <c r="G349" t="s">
+        <v>13</v>
+      </c>
+      <c r="H349" s="2">
+        <v>0</v>
+      </c>
+      <c r="I349" s="1">
+        <v>46146.690740740742</v>
+      </c>
+      <c r="J349">
+        <v>0</v>
+      </c>
+      <c r="K349" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="350" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H350" s="2"/>
-      <c r="I350" s="1"/>
+      <c r="B350" t="s">
+        <v>29</v>
+      </c>
+      <c r="C350">
+        <v>5274</v>
+      </c>
+      <c r="D350" t="s">
+        <v>55</v>
+      </c>
+      <c r="F350" t="s">
+        <v>57</v>
+      </c>
+      <c r="G350" t="s">
+        <v>13</v>
+      </c>
+      <c r="H350" s="2">
+        <v>0</v>
+      </c>
+      <c r="I350" s="1">
+        <v>46146.690740740742</v>
+      </c>
+      <c r="J350">
+        <v>0</v>
+      </c>
+      <c r="K350" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="351" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H351" s="2"/>
-      <c r="I351" s="1"/>
+      <c r="B351" t="s">
+        <v>29</v>
+      </c>
+      <c r="C351">
+        <v>2749</v>
+      </c>
+      <c r="D351" t="s">
+        <v>42</v>
+      </c>
+      <c r="F351" t="s">
+        <v>57</v>
+      </c>
+      <c r="G351" t="s">
+        <v>13</v>
+      </c>
+      <c r="H351" s="2">
+        <v>0</v>
+      </c>
+      <c r="I351" s="1">
+        <v>46146.691435185188</v>
+      </c>
+      <c r="J351">
+        <v>0</v>
+      </c>
+      <c r="K351" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="352" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H352" s="2"/>
-      <c r="I352" s="1"/>
-    </row>
-    <row r="353" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H353" s="2"/>
-      <c r="I353" s="1"/>
-    </row>
-    <row r="354" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H354" s="2"/>
-      <c r="I354" s="1"/>
-    </row>
-    <row r="355" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H355" s="2"/>
-      <c r="I355" s="1"/>
-    </row>
-    <row r="356" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H356" s="2"/>
-      <c r="I356" s="1"/>
-    </row>
-    <row r="357" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H357" s="2"/>
-      <c r="I357" s="1"/>
-    </row>
-    <row r="358" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H358" s="2"/>
-      <c r="I358" s="1"/>
-    </row>
-    <row r="359" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H359" s="2"/>
-      <c r="I359" s="1"/>
-    </row>
-    <row r="360" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B352" t="s">
+        <v>29</v>
+      </c>
+      <c r="C352">
+        <v>5032</v>
+      </c>
+      <c r="D352" t="s">
+        <v>54</v>
+      </c>
+      <c r="F352" t="s">
+        <v>57</v>
+      </c>
+      <c r="G352" t="s">
+        <v>13</v>
+      </c>
+      <c r="H352" s="2">
+        <v>0</v>
+      </c>
+      <c r="I352" s="1">
+        <v>46146.692129629628</v>
+      </c>
+      <c r="J352">
+        <v>0</v>
+      </c>
+      <c r="K352" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="353" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B353" t="s">
+        <v>29</v>
+      </c>
+      <c r="C353">
+        <v>4755</v>
+      </c>
+      <c r="D353" t="s">
+        <v>53</v>
+      </c>
+      <c r="F353" t="s">
+        <v>57</v>
+      </c>
+      <c r="G353" t="s">
+        <v>13</v>
+      </c>
+      <c r="H353" s="2">
+        <v>0</v>
+      </c>
+      <c r="I353" s="1">
+        <v>46146.668634259258</v>
+      </c>
+      <c r="J353">
+        <v>0</v>
+      </c>
+      <c r="K353" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B354" t="s">
+        <v>29</v>
+      </c>
+      <c r="C354">
+        <v>2245</v>
+      </c>
+      <c r="D354" t="s">
+        <v>32</v>
+      </c>
+      <c r="F354" t="s">
+        <v>57</v>
+      </c>
+      <c r="G354" t="s">
+        <v>13</v>
+      </c>
+      <c r="H354" s="2">
+        <v>0</v>
+      </c>
+      <c r="I354" s="1">
+        <v>46146.669328703705</v>
+      </c>
+      <c r="J354">
+        <v>0</v>
+      </c>
+      <c r="K354" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="355" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B355" t="s">
+        <v>29</v>
+      </c>
+      <c r="C355">
+        <v>2750</v>
+      </c>
+      <c r="D355" t="s">
+        <v>44</v>
+      </c>
+      <c r="F355" t="s">
+        <v>57</v>
+      </c>
+      <c r="G355" t="s">
+        <v>13</v>
+      </c>
+      <c r="H355" s="2">
+        <v>0</v>
+      </c>
+      <c r="I355" s="1">
+        <v>46146.670023148145</v>
+      </c>
+      <c r="J355">
+        <v>0</v>
+      </c>
+      <c r="K355" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B356" t="s">
+        <v>29</v>
+      </c>
+      <c r="C356">
+        <v>2747</v>
+      </c>
+      <c r="D356" t="s">
+        <v>45</v>
+      </c>
+      <c r="F356" t="s">
+        <v>57</v>
+      </c>
+      <c r="G356" t="s">
+        <v>13</v>
+      </c>
+      <c r="H356" s="2">
+        <v>0</v>
+      </c>
+      <c r="I356" s="1">
+        <v>46146.670023148145</v>
+      </c>
+      <c r="J356">
+        <v>0</v>
+      </c>
+      <c r="K356" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="357" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B357" t="s">
+        <v>29</v>
+      </c>
+      <c r="C357">
+        <v>2741</v>
+      </c>
+      <c r="D357" t="s">
+        <v>46</v>
+      </c>
+      <c r="F357" t="s">
+        <v>57</v>
+      </c>
+      <c r="G357" t="s">
+        <v>13</v>
+      </c>
+      <c r="H357" s="2">
+        <v>0</v>
+      </c>
+      <c r="I357" s="1">
+        <v>46146.670717592591</v>
+      </c>
+      <c r="J357">
+        <v>0</v>
+      </c>
+      <c r="K357" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="358" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B358" t="s">
+        <v>29</v>
+      </c>
+      <c r="C358">
+        <v>2739</v>
+      </c>
+      <c r="D358" t="s">
+        <v>47</v>
+      </c>
+      <c r="F358" t="s">
+        <v>57</v>
+      </c>
+      <c r="G358" t="s">
+        <v>10</v>
+      </c>
+      <c r="H358" s="2">
+        <v>4.9537037037037041E-3</v>
+      </c>
+      <c r="I358" s="1">
+        <v>46146.671412037038</v>
+      </c>
+      <c r="J358">
+        <v>0</v>
+      </c>
+      <c r="K358" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="359" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B359" t="s">
+        <v>29</v>
+      </c>
+      <c r="C359">
+        <v>2736</v>
+      </c>
+      <c r="D359" t="s">
+        <v>48</v>
+      </c>
+      <c r="F359" t="s">
+        <v>57</v>
+      </c>
+      <c r="G359" t="s">
+        <v>10</v>
+      </c>
+      <c r="H359" s="2">
+        <v>4.4212962962962964E-3</v>
+      </c>
+      <c r="I359" s="1">
+        <v>46146.672106481485</v>
+      </c>
+      <c r="J359">
+        <v>0</v>
+      </c>
+      <c r="K359" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="360" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H360" s="2"/>
       <c r="I360" s="1"/>
     </row>
-    <row r="361" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H361" s="2"/>
       <c r="I361" s="1"/>
     </row>
-    <row r="362" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H362" s="2"/>
       <c r="I362" s="1"/>
     </row>
-    <row r="363" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H363" s="2"/>
       <c r="I363" s="1"/>
     </row>
-    <row r="364" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H364" s="2"/>
       <c r="I364" s="1"/>
     </row>
-    <row r="365" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H365" s="2"/>
       <c r="I365" s="1"/>
     </row>
-    <row r="366" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H366" s="2"/>
       <c r="I366" s="1"/>
     </row>
-    <row r="367" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H367" s="2"/>
       <c r="I367" s="1"/>
     </row>
-    <row r="368" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H368" s="2"/>
       <c r="I368" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Neal Pool - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28A0836-08E4-4995-BECC-4661194B4C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5377555B-68A0-47ED-BCC6-95F4ED7A434B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="58">
   <si>
     <t>Company Name</t>
   </si>
@@ -10096,10 +10096,10 @@
         <v>57</v>
       </c>
       <c r="G343" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H343" s="2">
-        <v>0</v>
+        <v>5.138888888888889E-3</v>
       </c>
       <c r="I343" s="1">
         <v>46146.687962962962</v>
@@ -10154,10 +10154,10 @@
         <v>57</v>
       </c>
       <c r="G345" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H345" s="2">
-        <v>0</v>
+        <v>5.0347222222222225E-3</v>
       </c>
       <c r="I345" s="1">
         <v>46146.688657407409</v>
@@ -10270,10 +10270,10 @@
         <v>57</v>
       </c>
       <c r="G349" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H349" s="2">
-        <v>0</v>
+        <v>6.1921296296296299E-3</v>
       </c>
       <c r="I349" s="1">
         <v>46146.690740740742</v>
@@ -10299,10 +10299,10 @@
         <v>57</v>
       </c>
       <c r="G350" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H350" s="2">
-        <v>0</v>
+        <v>8.6226851851851846E-3</v>
       </c>
       <c r="I350" s="1">
         <v>46146.690740740742</v>
@@ -10328,10 +10328,10 @@
         <v>57</v>
       </c>
       <c r="G351" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H351" s="2">
-        <v>0</v>
+        <v>1.4722222222222222E-2</v>
       </c>
       <c r="I351" s="1">
         <v>46146.691435185188</v>
@@ -10357,10 +10357,10 @@
         <v>57</v>
       </c>
       <c r="G352" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H352" s="2">
-        <v>0</v>
+        <v>2.5462962962962961E-4</v>
       </c>
       <c r="I352" s="1">
         <v>46146.692129629628</v>
@@ -10373,32 +10373,10 @@
       </c>
     </row>
     <row r="353" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B353" t="s">
-        <v>29</v>
-      </c>
-      <c r="C353">
-        <v>4755</v>
-      </c>
-      <c r="D353" t="s">
-        <v>53</v>
-      </c>
-      <c r="F353" t="s">
-        <v>57</v>
-      </c>
-      <c r="G353" t="s">
-        <v>13</v>
-      </c>
-      <c r="H353" s="2">
-        <v>0</v>
-      </c>
-      <c r="I353" s="1">
-        <v>46146.668634259258</v>
-      </c>
-      <c r="J353">
-        <v>0</v>
-      </c>
+      <c r="H353" s="2"/>
+      <c r="I353" s="1"/>
       <c r="K353" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="354" spans="2:11" x14ac:dyDescent="0.25">
@@ -10406,10 +10384,10 @@
         <v>29</v>
       </c>
       <c r="C354">
-        <v>2245</v>
+        <v>4755</v>
       </c>
       <c r="D354" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F354" t="s">
         <v>57</v>
@@ -10421,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="I354" s="1">
-        <v>46146.669328703705</v>
+        <v>46146.668634259258</v>
       </c>
       <c r="J354">
         <v>0</v>
@@ -10435,22 +10413,22 @@
         <v>29</v>
       </c>
       <c r="C355">
-        <v>2750</v>
+        <v>2245</v>
       </c>
       <c r="D355" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F355" t="s">
         <v>57</v>
       </c>
       <c r="G355" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H355" s="2">
-        <v>0</v>
+        <v>4.5717592592592589E-3</v>
       </c>
       <c r="I355" s="1">
-        <v>46146.670023148145</v>
+        <v>46146.669328703705</v>
       </c>
       <c r="J355">
         <v>0</v>
@@ -10464,10 +10442,10 @@
         <v>29</v>
       </c>
       <c r="C356">
-        <v>2747</v>
+        <v>2750</v>
       </c>
       <c r="D356" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F356" t="s">
         <v>57</v>
@@ -10493,22 +10471,22 @@
         <v>29</v>
       </c>
       <c r="C357">
-        <v>2741</v>
+        <v>2747</v>
       </c>
       <c r="D357" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F357" t="s">
         <v>57</v>
       </c>
       <c r="G357" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H357" s="2">
-        <v>0</v>
+        <v>5.1041666666666666E-3</v>
       </c>
       <c r="I357" s="1">
-        <v>46146.670717592591</v>
+        <v>46146.670023148145</v>
       </c>
       <c r="J357">
         <v>0</v>
@@ -10522,22 +10500,22 @@
         <v>29</v>
       </c>
       <c r="C358">
-        <v>2739</v>
+        <v>2741</v>
       </c>
       <c r="D358" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F358" t="s">
         <v>57</v>
       </c>
       <c r="G358" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H358" s="2">
-        <v>4.9537037037037041E-3</v>
+        <v>0</v>
       </c>
       <c r="I358" s="1">
-        <v>46146.671412037038</v>
+        <v>46146.670717592591</v>
       </c>
       <c r="J358">
         <v>0</v>
@@ -10551,10 +10529,10 @@
         <v>29</v>
       </c>
       <c r="C359">
-        <v>2736</v>
+        <v>2739</v>
       </c>
       <c r="D359" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F359" t="s">
         <v>57</v>
@@ -10563,10 +10541,10 @@
         <v>10</v>
       </c>
       <c r="H359" s="2">
-        <v>4.4212962962962964E-3</v>
+        <v>4.9537037037037041E-3</v>
       </c>
       <c r="I359" s="1">
-        <v>46146.672106481485</v>
+        <v>46146.671412037038</v>
       </c>
       <c r="J359">
         <v>0</v>
@@ -10576,8 +10554,33 @@
       </c>
     </row>
     <row r="360" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H360" s="2"/>
-      <c r="I360" s="1"/>
+      <c r="B360" t="s">
+        <v>29</v>
+      </c>
+      <c r="C360">
+        <v>2736</v>
+      </c>
+      <c r="D360" t="s">
+        <v>48</v>
+      </c>
+      <c r="F360" t="s">
+        <v>57</v>
+      </c>
+      <c r="G360" t="s">
+        <v>10</v>
+      </c>
+      <c r="H360" s="2">
+        <v>4.4212962962962964E-3</v>
+      </c>
+      <c r="I360" s="1">
+        <v>46146.672106481485</v>
+      </c>
+      <c r="J360">
+        <v>0</v>
+      </c>
+      <c r="K360" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="361" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H361" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Neal Pool - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385594E3-C479-49A0-B62D-B1AAD03D3132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BD77A1-8AC3-4EA1-A318-164EFEF48A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -10183,16 +10183,16 @@
         <v>57</v>
       </c>
       <c r="G346" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H346" s="2">
-        <v>0</v>
+        <v>5.1967592592592595E-3</v>
       </c>
       <c r="I346" s="1">
         <v>46146.689351851855</v>
       </c>
       <c r="J346">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K346" t="s">
         <v>11</v>
@@ -10241,10 +10241,10 @@
         <v>57</v>
       </c>
       <c r="G348" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H348" s="2">
-        <v>0</v>
+        <v>5.2893518518518515E-3</v>
       </c>
       <c r="I348" s="1">
         <v>46146.690046296295</v>
@@ -10402,7 +10402,7 @@
         <v>46146.668634259258</v>
       </c>
       <c r="J354">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K354" t="s">
         <v>11</v>
@@ -10509,16 +10509,16 @@
         <v>57</v>
       </c>
       <c r="G358" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H358" s="2">
-        <v>0</v>
+        <v>6.5509259259259262E-3</v>
       </c>
       <c r="I358" s="1">
         <v>46146.670717592591</v>
       </c>
       <c r="J358">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K358" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Neal Pool - Samsara\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\neal-pool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1FA4090-EB2F-464B-B657-AF26A52CB914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE80602-3B11-4B2D-960F-1F92E5246F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -10745,7 +10745,7 @@
         <v>10</v>
       </c>
       <c r="H365" s="2">
-        <v>1.607638888888889E-2</v>
+        <v>1.7013888888888887E-2</v>
       </c>
       <c r="I365" s="1">
         <v>46174.59988425926</v>
@@ -10829,16 +10829,16 @@
         <v>25</v>
       </c>
       <c r="G368" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H368" s="2">
-        <v>0</v>
+        <v>8.5879629629629622E-3</v>
       </c>
       <c r="I368" s="1">
         <v>46176.470138888886</v>
       </c>
       <c r="J368">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K368" t="s">
         <v>11</v>
@@ -10887,16 +10887,16 @@
         <v>25</v>
       </c>
       <c r="G370" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H370" s="2">
-        <v>0</v>
+        <v>7.5578703703703702E-3</v>
       </c>
       <c r="I370" s="1">
         <v>46176.470833333333</v>
       </c>
       <c r="J370">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K370" t="s">
         <v>11</v>
@@ -10954,7 +10954,7 @@
         <v>46176.47152777778</v>
       </c>
       <c r="J372">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K372" t="s">
         <v>11</v>
@@ -10983,7 +10983,7 @@
         <v>46176.47152777778</v>
       </c>
       <c r="J373">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K373" t="s">
         <v>11</v>
@@ -11003,16 +11003,16 @@
         <v>25</v>
       </c>
       <c r="G374" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H374" s="2">
-        <v>0</v>
+        <v>6.8171296296296296E-3</v>
       </c>
       <c r="I374" s="1">
         <v>46176.472222222219</v>
       </c>
       <c r="J374">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K374" t="s">
         <v>11</v>
@@ -11099,7 +11099,7 @@
         <v>46176.472916666666</v>
       </c>
       <c r="J377">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K377" t="s">
         <v>11</v>
@@ -11119,16 +11119,16 @@
         <v>25</v>
       </c>
       <c r="G378" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H378" s="2">
-        <v>0</v>
+        <v>7.2453703703703708E-3</v>
       </c>
       <c r="I378" s="1">
         <v>46176.472916666666</v>
       </c>
       <c r="J378">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K378" t="s">
         <v>11</v>
@@ -11148,16 +11148,16 @@
         <v>25</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H379" s="2">
-        <v>0</v>
+        <v>7.0023148148148145E-3</v>
       </c>
       <c r="I379" s="1">
         <v>46176.473611111112</v>
       </c>
       <c r="J379">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K379" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\neal-pool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87A4FFE7-446C-4B7C-8FAE-0B177C2FF883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B0102D9-F8E9-4DF5-85E8-0693311C1470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -119,25 +119,25 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Safe RR Crossing</t>
+    <t>Work Zone Safety</t>
+  </si>
+  <si>
+    <t>Fatigue</t>
+  </si>
+  <si>
+    <t>Camera Event Management (Onboarding)</t>
+  </si>
+  <si>
+    <t>Dangers of Aggressive Driving for CMV Drivers</t>
+  </si>
+  <si>
+    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
     <t>3 points of contact</t>
   </si>
   <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Dangers of Aggressive Driving for CMV Drivers</t>
-  </si>
-  <si>
     <t>Vehicle &amp; Roadside Inspections CMV</t>
-  </si>
-  <si>
-    <t>Camera Event Management Orientation for Drivers</t>
-  </si>
-  <si>
-    <t>Fatigue</t>
   </si>
   <si>
     <t>Micro-Learn Safe Following Distance</t>
@@ -146,13 +146,13 @@
     <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
+    <t>Safe RR Crossing</t>
+  </si>
+  <si>
     <t>Neal Pool Rekers</t>
   </si>
   <si>
     <t>Jaymie Pool</t>
-  </si>
-  <si>
-    <t>Camera Event Management (Onboarding)</t>
   </si>
   <si>
     <t>Liz Guthrie</t>
@@ -595,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -644,16 +644,16 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2">
         <v>2246</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>13</v>
@@ -673,7 +673,7 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>2245</v>
@@ -682,7 +682,7 @@
         <v>38</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -702,7 +702,7 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4">
         <v>2738</v>
@@ -711,7 +711,7 @@
         <v>39</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>13</v>
@@ -731,7 +731,7 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5">
         <v>2740</v>
@@ -740,7 +740,7 @@
         <v>40</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>13</v>
@@ -760,7 +760,7 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>2735</v>
@@ -769,7 +769,7 @@
         <v>41</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>2742</v>
@@ -798,7 +798,7 @@
         <v>42</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8">
         <v>2737</v>
@@ -827,7 +827,7 @@
         <v>43</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>12</v>
@@ -856,7 +856,7 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10">
         <v>2748</v>
@@ -865,7 +865,7 @@
         <v>44</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -885,7 +885,7 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11">
         <v>2745</v>
@@ -894,7 +894,7 @@
         <v>45</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -914,16 +914,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E12">
         <v>2246</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -943,7 +943,7 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>2743</v>
@@ -952,7 +952,7 @@
         <v>46</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -972,7 +972,7 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14">
         <v>2746</v>
@@ -981,7 +981,7 @@
         <v>47</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>13</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E15">
         <v>2749</v>
@@ -1010,7 +1010,7 @@
         <v>48</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E16">
         <v>2734</v>
@@ -1039,7 +1039,7 @@
         <v>49</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E17">
         <v>2245</v>
@@ -1068,7 +1068,7 @@
         <v>38</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E18">
         <v>2750</v>
@@ -1097,7 +1097,7 @@
         <v>50</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E19">
         <v>2747</v>
@@ -1126,7 +1126,7 @@
         <v>51</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20">
         <v>2741</v>
@@ -1155,7 +1155,7 @@
         <v>52</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21">
         <v>2739</v>
@@ -1184,7 +1184,7 @@
         <v>53</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>12</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E23">
         <v>2736</v>
@@ -1222,7 +1222,7 @@
         <v>54</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E24">
         <v>2738</v>
@@ -1271,7 +1271,7 @@
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E25">
         <v>2740</v>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E26">
         <v>2735</v>
@@ -1329,7 +1329,7 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E27">
         <v>2742</v>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E28">
         <v>2737</v>
@@ -1387,7 +1387,7 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E29">
         <v>2748</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E30">
         <v>2745</v>
@@ -1445,13 +1445,13 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E31">
         <v>2246</v>
       </c>
       <c r="F31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>16</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E33">
         <v>2743</v>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E34">
         <v>2746</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E35">
         <v>2749</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E36">
         <v>2734</v>
@@ -1599,7 +1599,7 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E37">
         <v>2245</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E38">
         <v>2750</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E39">
         <v>2747</v>
@@ -1686,7 +1686,7 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E40">
         <v>2741</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E41">
         <v>2739</v>
@@ -1744,7 +1744,7 @@
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E42">
         <v>2736</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E43">
         <v>2738</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E44">
         <v>2740</v>
@@ -1831,7 +1831,7 @@
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E45">
         <v>2742</v>
@@ -1860,7 +1860,7 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E46">
         <v>2737</v>
@@ -1889,7 +1889,7 @@
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E47">
         <v>2748</v>
@@ -1918,7 +1918,7 @@
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E48">
         <v>2745</v>
@@ -1947,13 +1947,13 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E49">
         <v>2246</v>
       </c>
       <c r="F49" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>17</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E50">
         <v>2743</v>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E51">
         <v>2746</v>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E52">
         <v>2749</v>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E53">
         <v>2734</v>
@@ -2092,7 +2092,7 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E54">
         <v>2245</v>
@@ -2121,7 +2121,7 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E55">
         <v>2750</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E56">
         <v>2747</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E57">
         <v>2741</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="58" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E58">
         <v>2739</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E59">
         <v>2736</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E60">
         <v>2738</v>
@@ -2275,7 +2275,7 @@
         <v>39</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>12</v>
@@ -2304,7 +2304,7 @@
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E62">
         <v>2740</v>
@@ -2313,7 +2313,7 @@
         <v>40</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>13</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E63">
         <v>2742</v>
@@ -2342,7 +2342,7 @@
         <v>42</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E64">
         <v>2737</v>
@@ -2371,7 +2371,7 @@
         <v>43</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -2391,7 +2391,7 @@
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E65">
         <v>2748</v>
@@ -2400,7 +2400,7 @@
         <v>44</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2420,7 +2420,7 @@
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E66">
         <v>2745</v>
@@ -2429,7 +2429,7 @@
         <v>45</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2449,16 +2449,16 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E67">
         <v>2246</v>
       </c>
       <c r="F67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2478,7 +2478,7 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E68">
         <v>2743</v>
@@ -2487,7 +2487,7 @@
         <v>46</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>10</v>
@@ -2507,7 +2507,7 @@
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E69">
         <v>2746</v>
@@ -2516,7 +2516,7 @@
         <v>47</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>13</v>
@@ -2536,7 +2536,7 @@
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E70">
         <v>2749</v>
@@ -2545,7 +2545,7 @@
         <v>48</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E71">
         <v>2734</v>
@@ -2574,7 +2574,7 @@
         <v>49</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2594,7 +2594,7 @@
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E72">
         <v>2245</v>
@@ -2603,7 +2603,7 @@
         <v>38</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>10</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E73">
         <v>2750</v>
@@ -2632,7 +2632,7 @@
         <v>50</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>10</v>
@@ -2652,7 +2652,7 @@
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E74">
         <v>2747</v>
@@ -2661,7 +2661,7 @@
         <v>51</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2681,7 +2681,7 @@
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E75">
         <v>2741</v>
@@ -2690,7 +2690,7 @@
         <v>52</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>13</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D76" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E76">
         <v>2739</v>
@@ -2719,7 +2719,7 @@
         <v>53</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>10</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E77">
         <v>2736</v>
@@ -2748,7 +2748,7 @@
         <v>54</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>10</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E78">
         <v>2738</v>
@@ -2777,7 +2777,7 @@
         <v>39</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>13</v>
@@ -2797,7 +2797,7 @@
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E79">
         <v>2740</v>
@@ -2806,7 +2806,7 @@
         <v>40</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>13</v>
@@ -2826,7 +2826,7 @@
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E80">
         <v>2742</v>
@@ -2835,7 +2835,7 @@
         <v>42</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -2855,7 +2855,7 @@
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E81">
         <v>2737</v>
@@ -2864,7 +2864,7 @@
         <v>43</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>13</v>
@@ -2884,7 +2884,7 @@
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E82">
         <v>2748</v>
@@ -2893,7 +2893,7 @@
         <v>44</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E83">
         <v>2745</v>
@@ -2922,7 +2922,7 @@
         <v>45</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>10</v>
@@ -2942,16 +2942,16 @@
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E84">
         <v>2246</v>
       </c>
       <c r="F84" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2971,7 +2971,7 @@
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E85">
         <v>2743</v>
@@ -2980,7 +2980,7 @@
         <v>46</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -3000,7 +3000,7 @@
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E86">
         <v>2746</v>
@@ -3009,7 +3009,7 @@
         <v>47</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E87">
         <v>2749</v>
@@ -3038,7 +3038,7 @@
         <v>48</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>10</v>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E88">
         <v>2734</v>
@@ -3067,7 +3067,7 @@
         <v>49</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -3087,7 +3087,7 @@
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D89" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E89">
         <v>2245</v>
@@ -3096,7 +3096,7 @@
         <v>38</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>10</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E90">
         <v>2750</v>
@@ -3125,7 +3125,7 @@
         <v>50</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>10</v>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E91">
         <v>2747</v>
@@ -3154,7 +3154,7 @@
         <v>51</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>13</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E92">
         <v>2741</v>
@@ -3183,7 +3183,7 @@
         <v>52</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>10</v>
@@ -3203,7 +3203,7 @@
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D93" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E93">
         <v>2739</v>
@@ -3212,7 +3212,7 @@
         <v>53</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>10</v>
@@ -3232,7 +3232,7 @@
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E94">
         <v>2736</v>
@@ -3241,7 +3241,7 @@
         <v>54</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>12</v>
@@ -3270,7 +3270,7 @@
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D96" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E96">
         <v>2738</v>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="97" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E97">
         <v>2740</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E98">
         <v>2742</v>
@@ -3357,7 +3357,7 @@
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E99">
         <v>2737</v>
@@ -3386,7 +3386,7 @@
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D100" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E100">
         <v>2748</v>
@@ -3415,7 +3415,7 @@
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D101" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E101">
         <v>2745</v>
@@ -3444,13 +3444,13 @@
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E102">
         <v>2246</v>
       </c>
       <c r="F102" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>20</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E103">
         <v>2743</v>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="104" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E104">
         <v>2749</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E105">
         <v>2734</v>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="107" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E107">
         <v>2245</v>
@@ -3598,7 +3598,7 @@
     </row>
     <row r="108" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D108" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E108">
         <v>2750</v>
@@ -3627,7 +3627,7 @@
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E109">
         <v>2747</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="110" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D110" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E110">
         <v>2741</v>
@@ -3685,7 +3685,7 @@
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E111">
         <v>2739</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E112">
         <v>2736</v>
@@ -3743,7 +3743,7 @@
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E113">
         <v>2738</v>
@@ -3772,7 +3772,7 @@
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D114" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E114">
         <v>2740</v>
@@ -3801,7 +3801,7 @@
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E115">
         <v>2742</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="116" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E116">
         <v>2737</v>
@@ -3859,7 +3859,7 @@
     </row>
     <row r="117" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D117" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E117">
         <v>2748</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="118" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D118" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E118">
         <v>2745</v>
@@ -3917,13 +3917,13 @@
     </row>
     <row r="119" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D119" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E119">
         <v>2246</v>
       </c>
       <c r="F119" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>19</v>
@@ -3946,7 +3946,7 @@
     </row>
     <row r="120" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D120" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E120">
         <v>2749</v>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E121">
         <v>2245</v>
@@ -4004,7 +4004,7 @@
     </row>
     <row r="122" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E122">
         <v>2750</v>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="123" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D123" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E123">
         <v>2747</v>
@@ -4062,7 +4062,7 @@
     </row>
     <row r="124" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E124">
         <v>2741</v>
@@ -4091,7 +4091,7 @@
     </row>
     <row r="125" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E125">
         <v>2739</v>
@@ -4120,7 +4120,7 @@
     </row>
     <row r="126" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E126">
         <v>2736</v>
@@ -4149,7 +4149,7 @@
     </row>
     <row r="127" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D127" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E127">
         <v>2738</v>
@@ -4178,7 +4178,7 @@
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E128">
         <v>2740</v>
@@ -4207,7 +4207,7 @@
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E129">
         <v>2742</v>
@@ -4236,7 +4236,7 @@
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E130">
         <v>2737</v>
@@ -4265,7 +4265,7 @@
     </row>
     <row r="131" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E131">
         <v>2748</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="132" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D132" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E132">
         <v>2745</v>
@@ -4323,13 +4323,13 @@
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E133">
         <v>2246</v>
       </c>
       <c r="F133" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>34</v>
@@ -4352,7 +4352,7 @@
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E134">
         <v>2749</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="135" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E135">
         <v>2245</v>
@@ -4410,7 +4410,7 @@
     </row>
     <row r="136" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D136" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E136">
         <v>2750</v>
@@ -4439,7 +4439,7 @@
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E137">
         <v>2747</v>
@@ -4468,7 +4468,7 @@
     </row>
     <row r="138" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E138">
         <v>2741</v>
@@ -4497,7 +4497,7 @@
     </row>
     <row r="139" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D139" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E139">
         <v>2739</v>
@@ -4526,7 +4526,7 @@
     </row>
     <row r="140" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D140" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E140">
         <v>2736</v>
@@ -4555,7 +4555,7 @@
     </row>
     <row r="141" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E141">
         <v>2738</v>
@@ -4564,7 +4564,7 @@
         <v>39</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>10</v>
@@ -4584,7 +4584,7 @@
     </row>
     <row r="142" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D142" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E142">
         <v>2740</v>
@@ -4593,7 +4593,7 @@
         <v>40</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>13</v>
@@ -4613,7 +4613,7 @@
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D143" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E143">
         <v>2742</v>
@@ -4622,7 +4622,7 @@
         <v>42</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>10</v>
@@ -4642,7 +4642,7 @@
     </row>
     <row r="144" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D144" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E144">
         <v>2737</v>
@@ -4651,7 +4651,7 @@
         <v>43</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>13</v>
@@ -4671,7 +4671,7 @@
     </row>
     <row r="145" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D145" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E145">
         <v>2748</v>
@@ -4680,7 +4680,7 @@
         <v>44</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>10</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D146" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E146">
         <v>2745</v>
@@ -4709,7 +4709,7 @@
         <v>45</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>10</v>
@@ -4729,16 +4729,16 @@
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D147" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E147">
         <v>2246</v>
       </c>
       <c r="F147" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>10</v>
@@ -4758,7 +4758,7 @@
     </row>
     <row r="148" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D148" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E148">
         <v>2749</v>
@@ -4767,7 +4767,7 @@
         <v>48</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>13</v>
@@ -4787,7 +4787,7 @@
     </row>
     <row r="149" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E149">
         <v>2245</v>
@@ -4796,7 +4796,7 @@
         <v>38</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>10</v>
@@ -4816,7 +4816,7 @@
     </row>
     <row r="150" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E150">
         <v>2750</v>
@@ -4825,7 +4825,7 @@
         <v>50</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>10</v>
@@ -4845,7 +4845,7 @@
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E151">
         <v>2747</v>
@@ -4854,7 +4854,7 @@
         <v>51</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>10</v>
@@ -4874,7 +4874,7 @@
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E152">
         <v>2741</v>
@@ -4883,7 +4883,7 @@
         <v>52</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>13</v>
@@ -4903,7 +4903,7 @@
     </row>
     <row r="153" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E153">
         <v>2739</v>
@@ -4912,7 +4912,7 @@
         <v>53</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>13</v>
@@ -4932,7 +4932,7 @@
     </row>
     <row r="154" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D154" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E154">
         <v>2736</v>
@@ -4941,7 +4941,7 @@
         <v>54</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>10</v>
@@ -4961,7 +4961,7 @@
     </row>
     <row r="155" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D155" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E155">
         <v>2738</v>
@@ -4970,7 +4970,7 @@
         <v>39</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>13</v>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="156" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D156" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E156">
         <v>2740</v>
@@ -4999,7 +4999,7 @@
         <v>40</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>13</v>
@@ -5019,7 +5019,7 @@
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D157" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E157">
         <v>2742</v>
@@ -5028,7 +5028,7 @@
         <v>42</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>10</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="158" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D158" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E158">
         <v>2737</v>
@@ -5057,7 +5057,7 @@
         <v>43</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>13</v>
@@ -5077,7 +5077,7 @@
     </row>
     <row r="159" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D159" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E159">
         <v>2748</v>
@@ -5086,7 +5086,7 @@
         <v>44</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>10</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="160" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E160">
         <v>2745</v>
@@ -5115,7 +5115,7 @@
         <v>45</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>13</v>
@@ -5135,16 +5135,16 @@
     </row>
     <row r="161" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D161" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E161">
         <v>2246</v>
       </c>
       <c r="F161" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>13</v>
@@ -5164,7 +5164,7 @@
     </row>
     <row r="162" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E162">
         <v>2749</v>
@@ -5173,7 +5173,7 @@
         <v>48</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>10</v>
@@ -5193,7 +5193,7 @@
     </row>
     <row r="163" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D163" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E163">
         <v>2245</v>
@@ -5202,7 +5202,7 @@
         <v>38</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>10</v>
@@ -5222,7 +5222,7 @@
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D164" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E164">
         <v>2750</v>
@@ -5231,7 +5231,7 @@
         <v>50</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>10</v>
@@ -5251,7 +5251,7 @@
     </row>
     <row r="165" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D165" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E165">
         <v>2747</v>
@@ -5260,7 +5260,7 @@
         <v>51</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>13</v>
@@ -5280,7 +5280,7 @@
     </row>
     <row r="166" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D166" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E166">
         <v>2741</v>
@@ -5289,7 +5289,7 @@
         <v>52</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>13</v>
@@ -5309,7 +5309,7 @@
     </row>
     <row r="167" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D167" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E167">
         <v>2739</v>
@@ -5318,7 +5318,7 @@
         <v>53</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>12</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="169" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D169" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E169">
         <v>2736</v>
@@ -5356,7 +5356,7 @@
         <v>54</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>10</v>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="170" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D170" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E170">
         <v>2738</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="172" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D172" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E172">
         <v>3832</v>
@@ -5443,7 +5443,7 @@
     </row>
     <row r="173" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D173" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E173">
         <v>2740</v>
@@ -5472,7 +5472,7 @@
     </row>
     <row r="174" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D174" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E174">
         <v>3885</v>
@@ -5501,7 +5501,7 @@
     </row>
     <row r="175" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D175" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E175">
         <v>2742</v>
@@ -5530,7 +5530,7 @@
     </row>
     <row r="176" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D176" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E176">
         <v>2737</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="178" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D178" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E178">
         <v>2748</v>
@@ -5597,7 +5597,7 @@
     </row>
     <row r="179" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D179" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E179">
         <v>2745</v>
@@ -5626,13 +5626,13 @@
     </row>
     <row r="180" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D180" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E180">
         <v>2246</v>
       </c>
       <c r="F180" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>29</v>
@@ -5655,7 +5655,7 @@
     </row>
     <row r="181" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D181" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E181">
         <v>2749</v>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="182" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D182" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E182">
         <v>2245</v>
@@ -5713,7 +5713,7 @@
     </row>
     <row r="183" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D183" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E183">
         <v>2750</v>
@@ -5742,7 +5742,7 @@
     </row>
     <row r="184" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D184" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E184">
         <v>2747</v>
@@ -5771,7 +5771,7 @@
     </row>
     <row r="185" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D185" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E185">
         <v>2741</v>
@@ -5800,7 +5800,7 @@
     </row>
     <row r="186" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D186" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E186">
         <v>2739</v>
@@ -5829,7 +5829,7 @@
     </row>
     <row r="187" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D187" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E187">
         <v>2736</v>
@@ -5858,7 +5858,7 @@
     </row>
     <row r="188" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D188" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E188">
         <v>2738</v>
@@ -5887,7 +5887,7 @@
     </row>
     <row r="189" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D189" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E189">
         <v>3832</v>
@@ -5916,7 +5916,7 @@
     </row>
     <row r="190" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D190" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E190">
         <v>2740</v>
@@ -5945,7 +5945,7 @@
     </row>
     <row r="191" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D191" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E191">
         <v>3885</v>
@@ -5974,7 +5974,7 @@
     </row>
     <row r="192" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D192" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E192">
         <v>2742</v>
@@ -6003,7 +6003,7 @@
     </row>
     <row r="193" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D193" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E193">
         <v>2737</v>
@@ -6032,7 +6032,7 @@
     </row>
     <row r="194" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D194" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E194">
         <v>2748</v>
@@ -6061,7 +6061,7 @@
     </row>
     <row r="195" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D195" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E195">
         <v>2745</v>
@@ -6090,13 +6090,13 @@
     </row>
     <row r="196" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D196" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E196">
         <v>2246</v>
       </c>
       <c r="F196" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>33</v>
@@ -6119,7 +6119,7 @@
     </row>
     <row r="197" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D197" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E197">
         <v>2743</v>
@@ -6148,7 +6148,7 @@
     </row>
     <row r="198" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D198" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E198">
         <v>2749</v>
@@ -6177,7 +6177,7 @@
     </row>
     <row r="199" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D199" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E199">
         <v>2245</v>
@@ -6206,7 +6206,7 @@
     </row>
     <row r="200" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D200" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E200">
         <v>2750</v>
@@ -6235,7 +6235,7 @@
     </row>
     <row r="201" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D201" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E201">
         <v>2747</v>
@@ -6264,7 +6264,7 @@
     </row>
     <row r="202" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D202" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E202">
         <v>2741</v>
@@ -6293,7 +6293,7 @@
     </row>
     <row r="203" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D203" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E203">
         <v>2739</v>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="204" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D204" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E204">
         <v>2736</v>
@@ -6351,7 +6351,7 @@
     </row>
     <row r="205" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D205" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E205">
         <v>2738</v>
@@ -6360,7 +6360,7 @@
         <v>39</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>10</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="206" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D206" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E206">
         <v>3832</v>
@@ -6389,7 +6389,7 @@
         <v>55</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>10</v>
@@ -6409,7 +6409,7 @@
     </row>
     <row r="207" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D207" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E207">
         <v>2740</v>
@@ -6418,7 +6418,7 @@
         <v>40</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>13</v>
@@ -6438,7 +6438,7 @@
     </row>
     <row r="208" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D208" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E208">
         <v>3885</v>
@@ -6447,7 +6447,7 @@
         <v>56</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>10</v>
@@ -6467,7 +6467,7 @@
     </row>
     <row r="209" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D209" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E209">
         <v>2742</v>
@@ -6476,7 +6476,7 @@
         <v>42</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>10</v>
@@ -6496,7 +6496,7 @@
     </row>
     <row r="210" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D210" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E210">
         <v>2737</v>
@@ -6505,7 +6505,7 @@
         <v>43</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>10</v>
@@ -6525,7 +6525,7 @@
     </row>
     <row r="211" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D211" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E211">
         <v>2748</v>
@@ -6534,7 +6534,7 @@
         <v>44</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>10</v>
@@ -6554,7 +6554,7 @@
     </row>
     <row r="212" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D212" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E212">
         <v>2745</v>
@@ -6563,7 +6563,7 @@
         <v>45</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>10</v>
@@ -6583,16 +6583,16 @@
     </row>
     <row r="213" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D213" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E213">
         <v>2246</v>
       </c>
       <c r="F213" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>10</v>
@@ -6612,7 +6612,7 @@
     </row>
     <row r="214" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D214" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E214">
         <v>2743</v>
@@ -6621,7 +6621,7 @@
         <v>46</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>10</v>
@@ -6641,7 +6641,7 @@
     </row>
     <row r="215" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D215" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E215">
         <v>2749</v>
@@ -6650,7 +6650,7 @@
         <v>48</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>10</v>
@@ -6670,7 +6670,7 @@
     </row>
     <row r="216" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D216" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E216">
         <v>4755</v>
@@ -6679,7 +6679,7 @@
         <v>57</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>10</v>
@@ -6699,7 +6699,7 @@
     </row>
     <row r="217" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D217" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E217">
         <v>2245</v>
@@ -6708,7 +6708,7 @@
         <v>38</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>10</v>
@@ -6728,7 +6728,7 @@
     </row>
     <row r="218" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D218" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E218">
         <v>2750</v>
@@ -6737,7 +6737,7 @@
         <v>50</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>10</v>
@@ -6757,7 +6757,7 @@
     </row>
     <row r="219" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D219" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E219">
         <v>2747</v>
@@ -6766,7 +6766,7 @@
         <v>51</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>10</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="220" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D220" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E220">
         <v>2741</v>
@@ -6795,7 +6795,7 @@
         <v>52</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>10</v>
@@ -6815,7 +6815,7 @@
     </row>
     <row r="221" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D221" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E221">
         <v>2739</v>
@@ -6824,7 +6824,7 @@
         <v>53</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>10</v>
@@ -6844,7 +6844,7 @@
     </row>
     <row r="222" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D222" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E222">
         <v>2736</v>
@@ -6853,7 +6853,7 @@
         <v>54</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>10</v>
@@ -6873,7 +6873,7 @@
     </row>
     <row r="223" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D223" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E223">
         <v>2738</v>
@@ -6902,7 +6902,7 @@
     </row>
     <row r="224" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D224" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E224">
         <v>3832</v>
@@ -6931,7 +6931,7 @@
     </row>
     <row r="225" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D225" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E225">
         <v>2740</v>
@@ -6969,7 +6969,7 @@
     </row>
     <row r="227" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D227" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E227">
         <v>3885</v>
@@ -6998,7 +6998,7 @@
     </row>
     <row r="228" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D228" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E228">
         <v>2742</v>
@@ -7027,7 +7027,7 @@
     </row>
     <row r="229" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D229" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E229">
         <v>2737</v>
@@ -7056,7 +7056,7 @@
     </row>
     <row r="230" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D230" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E230">
         <v>2748</v>
@@ -7085,7 +7085,7 @@
     </row>
     <row r="231" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D231" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E231">
         <v>2745</v>
@@ -7114,13 +7114,13 @@
     </row>
     <row r="232" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D232" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E232">
         <v>2246</v>
       </c>
       <c r="F232" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>16</v>
@@ -7143,7 +7143,7 @@
     </row>
     <row r="233" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D233" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E233">
         <v>2743</v>
@@ -7172,7 +7172,7 @@
     </row>
     <row r="234" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D234" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E234">
         <v>2749</v>
@@ -7201,7 +7201,7 @@
     </row>
     <row r="235" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D235" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E235">
         <v>4755</v>
@@ -7230,7 +7230,7 @@
     </row>
     <row r="236" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D236" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E236">
         <v>2245</v>
@@ -7259,7 +7259,7 @@
     </row>
     <row r="237" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D237" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E237">
         <v>2750</v>
@@ -7288,7 +7288,7 @@
     </row>
     <row r="238" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D238" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E238">
         <v>2747</v>
@@ -7317,7 +7317,7 @@
     </row>
     <row r="239" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D239" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E239">
         <v>2741</v>
@@ -7346,7 +7346,7 @@
     </row>
     <row r="240" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D240" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E240">
         <v>2739</v>
@@ -7375,7 +7375,7 @@
     </row>
     <row r="241" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D241" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E241">
         <v>2736</v>
@@ -7404,7 +7404,7 @@
     </row>
     <row r="242" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D242" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E242">
         <v>2738</v>
@@ -7433,7 +7433,7 @@
     </row>
     <row r="243" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D243" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E243">
         <v>3832</v>
@@ -7462,7 +7462,7 @@
     </row>
     <row r="244" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D244" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E244">
         <v>2740</v>
@@ -7491,7 +7491,7 @@
     </row>
     <row r="245" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D245" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E245">
         <v>3885</v>
@@ -7520,7 +7520,7 @@
     </row>
     <row r="246" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D246" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E246">
         <v>2742</v>
@@ -7558,7 +7558,7 @@
     </row>
     <row r="248" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D248" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E248">
         <v>2737</v>
@@ -7587,7 +7587,7 @@
     </row>
     <row r="249" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D249" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E249">
         <v>2748</v>
@@ -7616,7 +7616,7 @@
     </row>
     <row r="250" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D250" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E250">
         <v>2745</v>
@@ -7645,13 +7645,13 @@
     </row>
     <row r="251" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D251" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E251">
         <v>2246</v>
       </c>
       <c r="F251" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>17</v>
@@ -7674,7 +7674,7 @@
     </row>
     <row r="252" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D252" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E252">
         <v>2749</v>
@@ -7703,7 +7703,7 @@
     </row>
     <row r="253" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D253" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E253">
         <v>5032</v>
@@ -7732,7 +7732,7 @@
     </row>
     <row r="254" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D254" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E254">
         <v>4755</v>
@@ -7770,7 +7770,7 @@
     </row>
     <row r="256" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D256" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E256">
         <v>2245</v>
@@ -7799,7 +7799,7 @@
     </row>
     <row r="257" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D257" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E257">
         <v>2750</v>
@@ -7828,7 +7828,7 @@
     </row>
     <row r="258" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D258" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E258">
         <v>2747</v>
@@ -7857,7 +7857,7 @@
     </row>
     <row r="259" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D259" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E259">
         <v>2741</v>
@@ -7895,7 +7895,7 @@
     </row>
     <row r="261" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D261" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E261">
         <v>2739</v>
@@ -7933,7 +7933,7 @@
     </row>
     <row r="263" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D263" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E263">
         <v>2736</v>
@@ -7962,7 +7962,7 @@
     </row>
     <row r="264" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D264" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E264">
         <v>2738</v>
@@ -7991,7 +7991,7 @@
     </row>
     <row r="265" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D265" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E265">
         <v>3832</v>
@@ -8020,7 +8020,7 @@
     </row>
     <row r="266" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D266" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E266">
         <v>2740</v>
@@ -8049,7 +8049,7 @@
     </row>
     <row r="267" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D267" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E267">
         <v>3885</v>
@@ -8078,7 +8078,7 @@
     </row>
     <row r="268" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D268" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E268">
         <v>2742</v>
@@ -8107,7 +8107,7 @@
     </row>
     <row r="269" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D269" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E269">
         <v>2737</v>
@@ -8136,7 +8136,7 @@
     </row>
     <row r="270" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D270" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E270">
         <v>2748</v>
@@ -8165,7 +8165,7 @@
     </row>
     <row r="271" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D271" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E271">
         <v>2745</v>
@@ -8194,13 +8194,13 @@
     </row>
     <row r="272" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D272" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E272">
         <v>2246</v>
       </c>
       <c r="F272" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>23</v>
@@ -8223,7 +8223,7 @@
     </row>
     <row r="273" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D273" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E273">
         <v>2749</v>
@@ -8252,7 +8252,7 @@
     </row>
     <row r="274" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D274" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E274">
         <v>5032</v>
@@ -8281,7 +8281,7 @@
     </row>
     <row r="275" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D275" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E275">
         <v>4755</v>
@@ -8310,7 +8310,7 @@
     </row>
     <row r="276" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D276" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E276">
         <v>2245</v>
@@ -8339,7 +8339,7 @@
     </row>
     <row r="277" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D277" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E277">
         <v>2750</v>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="278" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D278" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E278">
         <v>2747</v>
@@ -8397,7 +8397,7 @@
     </row>
     <row r="279" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D279" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E279">
         <v>2741</v>
@@ -8426,7 +8426,7 @@
     </row>
     <row r="280" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D280" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E280">
         <v>2739</v>
@@ -8455,7 +8455,7 @@
     </row>
     <row r="281" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D281" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E281">
         <v>2736</v>
@@ -8484,7 +8484,7 @@
     </row>
     <row r="282" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D282" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E282">
         <v>2738</v>
@@ -8493,7 +8493,7 @@
         <v>39</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>10</v>
@@ -8513,7 +8513,7 @@
     </row>
     <row r="283" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D283" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E283">
         <v>3832</v>
@@ -8522,7 +8522,7 @@
         <v>55</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>10</v>
@@ -8542,7 +8542,7 @@
     </row>
     <row r="284" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D284" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E284">
         <v>2740</v>
@@ -8551,7 +8551,7 @@
         <v>40</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>10</v>
@@ -8571,7 +8571,7 @@
     </row>
     <row r="285" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D285" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E285">
         <v>3885</v>
@@ -8580,7 +8580,7 @@
         <v>56</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>10</v>
@@ -8600,7 +8600,7 @@
     </row>
     <row r="286" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D286" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E286">
         <v>2742</v>
@@ -8609,7 +8609,7 @@
         <v>42</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>10</v>
@@ -8629,7 +8629,7 @@
     </row>
     <row r="287" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D287" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E287">
         <v>2737</v>
@@ -8638,7 +8638,7 @@
         <v>43</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>10</v>
@@ -8658,7 +8658,7 @@
     </row>
     <row r="288" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D288" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E288">
         <v>2748</v>
@@ -8667,7 +8667,7 @@
         <v>44</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>10</v>
@@ -8687,7 +8687,7 @@
     </row>
     <row r="289" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D289" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E289">
         <v>2745</v>
@@ -8696,7 +8696,7 @@
         <v>45</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>10</v>
@@ -8716,16 +8716,16 @@
     </row>
     <row r="290" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D290" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E290">
         <v>2246</v>
       </c>
       <c r="F290" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>10</v>
@@ -8745,7 +8745,7 @@
     </row>
     <row r="291" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D291" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E291">
         <v>2749</v>
@@ -8754,7 +8754,7 @@
         <v>48</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>10</v>
@@ -8774,7 +8774,7 @@
     </row>
     <row r="292" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D292" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E292">
         <v>5032</v>
@@ -8783,7 +8783,7 @@
         <v>58</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>12</v>
@@ -8812,7 +8812,7 @@
     </row>
     <row r="294" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D294" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E294">
         <v>4755</v>
@@ -8821,7 +8821,7 @@
         <v>57</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>10</v>
@@ -8841,7 +8841,7 @@
     </row>
     <row r="295" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D295" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E295">
         <v>2245</v>
@@ -8850,7 +8850,7 @@
         <v>38</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>10</v>
@@ -8870,7 +8870,7 @@
     </row>
     <row r="296" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D296" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E296">
         <v>2750</v>
@@ -8879,7 +8879,7 @@
         <v>50</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>10</v>
@@ -8899,7 +8899,7 @@
     </row>
     <row r="297" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D297" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E297">
         <v>2747</v>
@@ -8908,7 +8908,7 @@
         <v>51</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>10</v>
@@ -8928,7 +8928,7 @@
     </row>
     <row r="298" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D298" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E298">
         <v>2741</v>
@@ -8937,7 +8937,7 @@
         <v>52</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>10</v>
@@ -8957,7 +8957,7 @@
     </row>
     <row r="299" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D299" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E299">
         <v>2739</v>
@@ -8966,7 +8966,7 @@
         <v>53</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>10</v>
@@ -8986,7 +8986,7 @@
     </row>
     <row r="300" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D300" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E300">
         <v>2736</v>
@@ -8995,7 +8995,7 @@
         <v>54</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>12</v>
@@ -9024,7 +9024,7 @@
     </row>
     <row r="302" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D302" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E302">
         <v>3832</v>
@@ -9053,7 +9053,7 @@
     </row>
     <row r="303" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D303" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E303">
         <v>2740</v>
@@ -9082,7 +9082,7 @@
     </row>
     <row r="304" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D304" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E304">
         <v>3885</v>
@@ -9111,7 +9111,7 @@
     </row>
     <row r="305" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D305" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E305">
         <v>2742</v>
@@ -9140,7 +9140,7 @@
     </row>
     <row r="306" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D306" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E306">
         <v>2737</v>
@@ -9178,7 +9178,7 @@
     </row>
     <row r="308" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D308" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E308">
         <v>2748</v>
@@ -9207,7 +9207,7 @@
     </row>
     <row r="309" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D309" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E309">
         <v>2745</v>
@@ -9236,13 +9236,13 @@
     </row>
     <row r="310" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D310" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E310">
         <v>2246</v>
       </c>
       <c r="F310" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>21</v>
@@ -9265,7 +9265,7 @@
     </row>
     <row r="311" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D311" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E311">
         <v>5274</v>
@@ -9294,7 +9294,7 @@
     </row>
     <row r="312" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D312" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E312">
         <v>2749</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="313" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D313" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E313">
         <v>5032</v>
@@ -9352,7 +9352,7 @@
     </row>
     <row r="314" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D314" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E314">
         <v>4755</v>
@@ -9381,7 +9381,7 @@
     </row>
     <row r="315" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D315" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E315">
         <v>2245</v>
@@ -9410,7 +9410,7 @@
     </row>
     <row r="316" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D316" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E316">
         <v>2750</v>
@@ -9439,7 +9439,7 @@
     </row>
     <row r="317" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D317" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E317">
         <v>2747</v>
@@ -9468,7 +9468,7 @@
     </row>
     <row r="318" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D318" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E318">
         <v>2741</v>
@@ -9506,7 +9506,7 @@
     </row>
     <row r="320" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D320" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E320">
         <v>2739</v>
@@ -9535,7 +9535,7 @@
     </row>
     <row r="321" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D321" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E321">
         <v>2736</v>
@@ -9564,7 +9564,7 @@
     </row>
     <row r="322" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D322" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E322">
         <v>3832</v>
@@ -9593,7 +9593,7 @@
     </row>
     <row r="323" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D323" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E323">
         <v>2740</v>
@@ -9622,7 +9622,7 @@
     </row>
     <row r="324" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D324" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E324">
         <v>3885</v>
@@ -9651,7 +9651,7 @@
     </row>
     <row r="325" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D325" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E325">
         <v>2742</v>
@@ -9680,7 +9680,7 @@
     </row>
     <row r="326" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D326" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E326">
         <v>2737</v>
@@ -9718,7 +9718,7 @@
     </row>
     <row r="328" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D328" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E328">
         <v>2748</v>
@@ -9747,7 +9747,7 @@
     </row>
     <row r="329" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D329" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E329">
         <v>2745</v>
@@ -9776,13 +9776,13 @@
     </row>
     <row r="330" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D330" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E330">
         <v>2246</v>
       </c>
       <c r="F330" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>24</v>
@@ -9805,7 +9805,7 @@
     </row>
     <row r="331" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D331" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E331">
         <v>5274</v>
@@ -9834,7 +9834,7 @@
     </row>
     <row r="332" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D332" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E332">
         <v>2749</v>
@@ -9872,7 +9872,7 @@
     </row>
     <row r="334" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D334" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E334">
         <v>5032</v>
@@ -9901,7 +9901,7 @@
     </row>
     <row r="335" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D335" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E335">
         <v>4755</v>
@@ -9930,7 +9930,7 @@
     </row>
     <row r="336" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D336" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E336">
         <v>2245</v>
@@ -9959,7 +9959,7 @@
     </row>
     <row r="337" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D337" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E337">
         <v>2750</v>
@@ -9988,7 +9988,7 @@
     </row>
     <row r="338" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D338" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E338">
         <v>2747</v>
@@ -10017,7 +10017,7 @@
     </row>
     <row r="339" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D339" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E339">
         <v>2741</v>
@@ -10046,7 +10046,7 @@
     </row>
     <row r="340" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D340" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E340">
         <v>2739</v>
@@ -10075,7 +10075,7 @@
     </row>
     <row r="341" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D341" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E341">
         <v>2736</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="342" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D342" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E342">
         <v>3832</v>
@@ -10133,7 +10133,7 @@
     </row>
     <row r="343" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D343" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E343">
         <v>2740</v>
@@ -10162,7 +10162,7 @@
     </row>
     <row r="344" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D344" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E344">
         <v>3885</v>
@@ -10191,7 +10191,7 @@
     </row>
     <row r="345" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D345" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E345">
         <v>2742</v>
@@ -10220,7 +10220,7 @@
     </row>
     <row r="346" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D346" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E346">
         <v>2737</v>
@@ -10249,7 +10249,7 @@
     </row>
     <row r="347" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D347" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E347">
         <v>2748</v>
@@ -10278,7 +10278,7 @@
     </row>
     <row r="348" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D348" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E348">
         <v>2745</v>
@@ -10307,13 +10307,13 @@
     </row>
     <row r="349" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D349" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E349">
         <v>2246</v>
       </c>
       <c r="F349" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H349" s="2" t="s">
         <v>18</v>
@@ -10336,7 +10336,7 @@
     </row>
     <row r="350" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D350" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E350">
         <v>5274</v>
@@ -10365,7 +10365,7 @@
     </row>
     <row r="351" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D351" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E351">
         <v>2749</v>
@@ -10394,7 +10394,7 @@
     </row>
     <row r="352" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D352" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E352">
         <v>5032</v>
@@ -10432,7 +10432,7 @@
     </row>
     <row r="354" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D354" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E354">
         <v>4755</v>
@@ -10470,7 +10470,7 @@
     </row>
     <row r="356" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D356" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E356">
         <v>2245</v>
@@ -10499,7 +10499,7 @@
     </row>
     <row r="357" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D357" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E357">
         <v>2750</v>
@@ -10528,7 +10528,7 @@
     </row>
     <row r="358" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D358" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E358">
         <v>2747</v>
@@ -10557,7 +10557,7 @@
     </row>
     <row r="359" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D359" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E359">
         <v>2741</v>
@@ -10586,7 +10586,7 @@
     </row>
     <row r="360" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D360" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E360">
         <v>2739</v>
@@ -10615,7 +10615,7 @@
     </row>
     <row r="361" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D361" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E361">
         <v>2736</v>
@@ -10644,7 +10644,7 @@
     </row>
     <row r="362" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D362" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E362">
         <v>3832</v>
@@ -10673,7 +10673,7 @@
     </row>
     <row r="363" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D363" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E363">
         <v>3885</v>
@@ -10702,7 +10702,7 @@
     </row>
     <row r="364" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D364" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E364">
         <v>5032</v>
@@ -10731,7 +10731,7 @@
     </row>
     <row r="365" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D365" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E365">
         <v>2245</v>
@@ -10760,7 +10760,7 @@
     </row>
     <row r="366" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D366" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E366">
         <v>2747</v>
@@ -10789,7 +10789,7 @@
     </row>
     <row r="367" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D367" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E367">
         <v>2745</v>
@@ -10818,7 +10818,7 @@
     </row>
     <row r="368" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D368" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E368">
         <v>2740</v>
@@ -10847,7 +10847,7 @@
     </row>
     <row r="369" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D369" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E369">
         <v>2742</v>
@@ -10876,7 +10876,7 @@
     </row>
     <row r="370" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D370" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E370">
         <v>2737</v>
@@ -10905,7 +10905,7 @@
     </row>
     <row r="371" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D371" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E371">
         <v>2748</v>
@@ -10934,13 +10934,13 @@
     </row>
     <row r="372" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D372" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E372">
         <v>2246</v>
       </c>
       <c r="F372" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H372" s="2" t="s">
         <v>25</v>
@@ -10963,7 +10963,7 @@
     </row>
     <row r="373" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D373" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E373">
         <v>5274</v>
@@ -10992,7 +10992,7 @@
     </row>
     <row r="374" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D374" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E374">
         <v>5607</v>
@@ -11021,7 +11021,7 @@
     </row>
     <row r="375" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D375" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E375">
         <v>4755</v>
@@ -11050,7 +11050,7 @@
     </row>
     <row r="376" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D376" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E376">
         <v>2750</v>
@@ -11079,7 +11079,7 @@
     </row>
     <row r="377" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D377" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E377">
         <v>2741</v>
@@ -11108,7 +11108,7 @@
     </row>
     <row r="378" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D378" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E378">
         <v>2739</v>
@@ -11137,7 +11137,7 @@
     </row>
     <row r="379" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D379" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E379">
         <v>2736</v>
@@ -13646,6 +13646,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -47297,7 +47298,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\neal-pool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B0102D9-F8E9-4DF5-85E8-0693311C1470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80E18B8A-B553-4F70-B142-7424B01A3B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="62">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,7 +86,13 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Speed Management</t>
+    <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Camera Event Management Orientation for Drivers</t>
+  </si>
+  <si>
+    <t>Work Zone Safety</t>
   </si>
   <si>
     <t>Winter Weather</t>
@@ -98,19 +104,25 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Space Management-Big 5</t>
+    <t>Fatigue</t>
+  </si>
+  <si>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Alert Driving</t>
   </si>
   <si>
-    <t>Drowsy Driving</t>
+    <t>Speed Management</t>
   </si>
   <si>
-    <t>Mark Complete</t>
+    <t>Space Management-Big 5</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
@@ -119,19 +131,10 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Fatigue</t>
-  </si>
-  <si>
     <t>Camera Event Management (Onboarding)</t>
   </si>
   <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
-  </si>
-  <si>
-    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
     <t>3 points of contact</t>
@@ -595,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -644,16 +647,16 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2">
         <v>2246</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>13</v>
@@ -673,16 +676,16 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3">
         <v>2245</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -702,16 +705,16 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>2738</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>13</v>
@@ -731,16 +734,16 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5">
         <v>2740</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>13</v>
@@ -760,16 +763,16 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>2735</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -789,16 +792,16 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>2742</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -818,16 +821,16 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8">
         <v>2737</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>12</v>
@@ -851,21 +854,21 @@
       <c r="J9" s="2"/>
       <c r="K9" s="1"/>
       <c r="M9" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10">
         <v>2748</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -885,16 +888,16 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>2745</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -914,16 +917,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12">
         <v>2246</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -943,16 +946,16 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13">
         <v>2743</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -972,16 +975,16 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14">
         <v>2746</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>13</v>
@@ -1001,16 +1004,16 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15">
         <v>2749</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1030,16 +1033,16 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16">
         <v>2734</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1059,16 +1062,16 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17">
         <v>2245</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1088,16 +1091,16 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18">
         <v>2750</v>
       </c>
       <c r="F18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -1117,16 +1120,16 @@
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E19">
         <v>2747</v>
       </c>
       <c r="F19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -1146,16 +1149,16 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20">
         <v>2741</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -1175,16 +1178,16 @@
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E21">
         <v>2739</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>12</v>
@@ -1208,21 +1211,21 @@
       <c r="J22" s="2"/>
       <c r="K22" s="1"/>
       <c r="M22" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23">
         <v>2736</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -1242,16 +1245,16 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E24">
         <v>2738</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>13</v>
@@ -1271,16 +1274,16 @@
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E25">
         <v>2740</v>
       </c>
       <c r="F25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>13</v>
@@ -1300,16 +1303,16 @@
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E26">
         <v>2735</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>13</v>
@@ -1329,16 +1332,16 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E27">
         <v>2742</v>
       </c>
       <c r="F27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1358,16 +1361,16 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E28">
         <v>2737</v>
       </c>
       <c r="F28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>13</v>
@@ -1387,16 +1390,16 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E29">
         <v>2748</v>
       </c>
       <c r="F29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
@@ -1416,16 +1419,16 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E30">
         <v>2745</v>
       </c>
       <c r="F30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>10</v>
@@ -1445,16 +1448,16 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E31">
         <v>2246</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>12</v>
@@ -1478,21 +1481,21 @@
       <c r="J32" s="2"/>
       <c r="K32" s="1"/>
       <c r="M32" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E33">
         <v>2743</v>
       </c>
       <c r="F33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
@@ -1512,16 +1515,16 @@
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E34">
         <v>2746</v>
       </c>
       <c r="F34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>13</v>
@@ -1541,16 +1544,16 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E35">
         <v>2749</v>
       </c>
       <c r="F35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>10</v>
@@ -1570,16 +1573,16 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E36">
         <v>2734</v>
       </c>
       <c r="F36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
@@ -1599,16 +1602,16 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E37">
         <v>2245</v>
       </c>
       <c r="F37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>10</v>
@@ -1628,16 +1631,16 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E38">
         <v>2750</v>
       </c>
       <c r="F38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
@@ -1657,16 +1660,16 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E39">
         <v>2747</v>
       </c>
       <c r="F39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1686,16 +1689,16 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E40">
         <v>2741</v>
       </c>
       <c r="F40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1715,16 +1718,16 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E41">
         <v>2739</v>
       </c>
       <c r="F41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>13</v>
@@ -1744,16 +1747,16 @@
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E42">
         <v>2736</v>
       </c>
       <c r="F42" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>10</v>
@@ -1773,16 +1776,16 @@
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E43">
         <v>2738</v>
       </c>
       <c r="F43" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>13</v>
@@ -1802,16 +1805,16 @@
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E44">
         <v>2740</v>
       </c>
       <c r="F44" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>13</v>
@@ -1831,16 +1834,16 @@
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E45">
         <v>2742</v>
       </c>
       <c r="F45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1860,16 +1863,16 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E46">
         <v>2737</v>
       </c>
       <c r="F46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>13</v>
@@ -1889,16 +1892,16 @@
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E47">
         <v>2748</v>
       </c>
       <c r="F47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -1918,16 +1921,16 @@
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E48">
         <v>2745</v>
       </c>
       <c r="F48" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -1947,16 +1950,16 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E49">
         <v>2246</v>
       </c>
       <c r="F49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>13</v>
@@ -1976,16 +1979,16 @@
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E50">
         <v>2743</v>
       </c>
       <c r="F50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
@@ -2005,16 +2008,16 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E51">
         <v>2746</v>
       </c>
       <c r="F51" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>13</v>
@@ -2034,16 +2037,16 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E52">
         <v>2749</v>
       </c>
       <c r="F52" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -2063,16 +2066,16 @@
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E53">
         <v>2734</v>
       </c>
       <c r="F53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>10</v>
@@ -2092,16 +2095,16 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E54">
         <v>2245</v>
       </c>
       <c r="F54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -2121,16 +2124,16 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E55">
         <v>2750</v>
       </c>
       <c r="F55" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2150,16 +2153,16 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E56">
         <v>2747</v>
       </c>
       <c r="F56" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>10</v>
@@ -2179,16 +2182,16 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E57">
         <v>2741</v>
       </c>
       <c r="F57" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>13</v>
@@ -2208,16 +2211,16 @@
     </row>
     <row r="58" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E58">
         <v>2739</v>
       </c>
       <c r="F58" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
@@ -2237,16 +2240,16 @@
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E59">
         <v>2736</v>
       </c>
       <c r="F59" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>10</v>
@@ -2266,16 +2269,16 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E60">
         <v>2738</v>
       </c>
       <c r="F60" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>12</v>
@@ -2299,21 +2302,21 @@
       <c r="J61" s="2"/>
       <c r="K61" s="1"/>
       <c r="M61" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E62">
         <v>2740</v>
       </c>
       <c r="F62" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>13</v>
@@ -2333,16 +2336,16 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E63">
         <v>2742</v>
       </c>
       <c r="F63" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2362,16 +2365,16 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E64">
         <v>2737</v>
       </c>
       <c r="F64" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -2391,16 +2394,16 @@
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E65">
         <v>2748</v>
       </c>
       <c r="F65" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2420,16 +2423,16 @@
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E66">
         <v>2745</v>
       </c>
       <c r="F66" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2449,16 +2452,16 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E67">
         <v>2246</v>
       </c>
       <c r="F67" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2478,16 +2481,16 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E68">
         <v>2743</v>
       </c>
       <c r="F68" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>10</v>
@@ -2507,16 +2510,16 @@
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E69">
         <v>2746</v>
       </c>
       <c r="F69" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>13</v>
@@ -2536,16 +2539,16 @@
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E70">
         <v>2749</v>
       </c>
       <c r="F70" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2565,16 +2568,16 @@
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E71">
         <v>2734</v>
       </c>
       <c r="F71" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2594,16 +2597,16 @@
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E72">
         <v>2245</v>
       </c>
       <c r="F72" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>10</v>
@@ -2623,16 +2626,16 @@
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E73">
         <v>2750</v>
       </c>
       <c r="F73" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>10</v>
@@ -2652,16 +2655,16 @@
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E74">
         <v>2747</v>
       </c>
       <c r="F74" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2681,16 +2684,16 @@
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E75">
         <v>2741</v>
       </c>
       <c r="F75" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>13</v>
@@ -2710,16 +2713,16 @@
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D76" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E76">
         <v>2739</v>
       </c>
       <c r="F76" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>10</v>
@@ -2739,16 +2742,16 @@
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E77">
         <v>2736</v>
       </c>
       <c r="F77" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>10</v>
@@ -2768,16 +2771,16 @@
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E78">
         <v>2738</v>
       </c>
       <c r="F78" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>13</v>
@@ -2797,16 +2800,16 @@
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E79">
         <v>2740</v>
       </c>
       <c r="F79" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>13</v>
@@ -2826,16 +2829,16 @@
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E80">
         <v>2742</v>
       </c>
       <c r="F80" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -2855,16 +2858,16 @@
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E81">
         <v>2737</v>
       </c>
       <c r="F81" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>13</v>
@@ -2884,16 +2887,16 @@
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E82">
         <v>2748</v>
       </c>
       <c r="F82" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2913,16 +2916,16 @@
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E83">
         <v>2745</v>
       </c>
       <c r="F83" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>10</v>
@@ -2942,16 +2945,16 @@
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E84">
         <v>2246</v>
       </c>
       <c r="F84" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2971,16 +2974,16 @@
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E85">
         <v>2743</v>
       </c>
       <c r="F85" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -3000,16 +3003,16 @@
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E86">
         <v>2746</v>
       </c>
       <c r="F86" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -3029,16 +3032,16 @@
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E87">
         <v>2749</v>
       </c>
       <c r="F87" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>10</v>
@@ -3058,16 +3061,16 @@
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E88">
         <v>2734</v>
       </c>
       <c r="F88" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -3087,16 +3090,16 @@
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D89" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E89">
         <v>2245</v>
       </c>
       <c r="F89" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>10</v>
@@ -3116,16 +3119,16 @@
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E90">
         <v>2750</v>
       </c>
       <c r="F90" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>10</v>
@@ -3145,16 +3148,16 @@
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E91">
         <v>2747</v>
       </c>
       <c r="F91" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>13</v>
@@ -3174,16 +3177,16 @@
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E92">
         <v>2741</v>
       </c>
       <c r="F92" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>10</v>
@@ -3203,16 +3206,16 @@
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D93" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E93">
         <v>2739</v>
       </c>
       <c r="F93" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>10</v>
@@ -3232,16 +3235,16 @@
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E94">
         <v>2736</v>
       </c>
       <c r="F94" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>12</v>
@@ -3265,21 +3268,21 @@
       <c r="J95" s="2"/>
       <c r="K95" s="1"/>
       <c r="M95" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D96" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E96">
         <v>2738</v>
       </c>
       <c r="F96" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>10</v>
@@ -3299,16 +3302,16 @@
     </row>
     <row r="97" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E97">
         <v>2740</v>
       </c>
       <c r="F97" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>13</v>
@@ -3328,16 +3331,16 @@
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E98">
         <v>2742</v>
       </c>
       <c r="F98" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3357,16 +3360,16 @@
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E99">
         <v>2737</v>
       </c>
       <c r="F99" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>13</v>
@@ -3386,16 +3389,16 @@
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D100" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E100">
         <v>2748</v>
       </c>
       <c r="F100" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>10</v>
@@ -3415,16 +3418,16 @@
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D101" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E101">
         <v>2745</v>
       </c>
       <c r="F101" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>10</v>
@@ -3444,16 +3447,16 @@
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E102">
         <v>2246</v>
       </c>
       <c r="F102" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>10</v>
@@ -3473,16 +3476,16 @@
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E103">
         <v>2743</v>
       </c>
       <c r="F103" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3502,16 +3505,16 @@
     </row>
     <row r="104" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E104">
         <v>2749</v>
       </c>
       <c r="F104" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>10</v>
@@ -3531,16 +3534,16 @@
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E105">
         <v>2734</v>
       </c>
       <c r="F105" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>12</v>
@@ -3564,21 +3567,21 @@
       <c r="J106" s="2"/>
       <c r="K106" s="1"/>
       <c r="M106" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E107">
         <v>2245</v>
       </c>
       <c r="F107" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>10</v>
@@ -3598,16 +3601,16 @@
     </row>
     <row r="108" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D108" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E108">
         <v>2750</v>
       </c>
       <c r="F108" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>10</v>
@@ -3627,16 +3630,16 @@
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E109">
         <v>2747</v>
       </c>
       <c r="F109" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>10</v>
@@ -3656,16 +3659,16 @@
     </row>
     <row r="110" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D110" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E110">
         <v>2741</v>
       </c>
       <c r="F110" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>10</v>
@@ -3685,16 +3688,16 @@
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E111">
         <v>2739</v>
       </c>
       <c r="F111" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>13</v>
@@ -3714,16 +3717,16 @@
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E112">
         <v>2736</v>
       </c>
       <c r="F112" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>10</v>
@@ -3743,16 +3746,16 @@
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E113">
         <v>2738</v>
       </c>
       <c r="F113" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>10</v>
@@ -3772,16 +3775,16 @@
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D114" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E114">
         <v>2740</v>
       </c>
       <c r="F114" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>13</v>
@@ -3801,16 +3804,16 @@
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E115">
         <v>2742</v>
       </c>
       <c r="F115" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>10</v>
@@ -3830,16 +3833,16 @@
     </row>
     <row r="116" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E116">
         <v>2737</v>
       </c>
       <c r="F116" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>13</v>
@@ -3859,16 +3862,16 @@
     </row>
     <row r="117" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D117" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E117">
         <v>2748</v>
       </c>
       <c r="F117" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>10</v>
@@ -3888,16 +3891,16 @@
     </row>
     <row r="118" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D118" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E118">
         <v>2745</v>
       </c>
       <c r="F118" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>10</v>
@@ -3917,16 +3920,16 @@
     </row>
     <row r="119" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D119" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E119">
         <v>2246</v>
       </c>
       <c r="F119" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>10</v>
@@ -3946,16 +3949,16 @@
     </row>
     <row r="120" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D120" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E120">
         <v>2749</v>
       </c>
       <c r="F120" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>10</v>
@@ -3975,16 +3978,16 @@
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E121">
         <v>2245</v>
       </c>
       <c r="F121" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>10</v>
@@ -4004,16 +4007,16 @@
     </row>
     <row r="122" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E122">
         <v>2750</v>
       </c>
       <c r="F122" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -4033,16 +4036,16 @@
     </row>
     <row r="123" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D123" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E123">
         <v>2747</v>
       </c>
       <c r="F123" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>10</v>
@@ -4062,16 +4065,16 @@
     </row>
     <row r="124" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E124">
         <v>2741</v>
       </c>
       <c r="F124" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>10</v>
@@ -4091,16 +4094,16 @@
     </row>
     <row r="125" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E125">
         <v>2739</v>
       </c>
       <c r="F125" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>13</v>
@@ -4120,16 +4123,16 @@
     </row>
     <row r="126" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E126">
         <v>2736</v>
       </c>
       <c r="F126" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -4149,16 +4152,16 @@
     </row>
     <row r="127" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D127" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E127">
         <v>2738</v>
       </c>
       <c r="F127" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>13</v>
@@ -4178,16 +4181,16 @@
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E128">
         <v>2740</v>
       </c>
       <c r="F128" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -4207,16 +4210,16 @@
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E129">
         <v>2742</v>
       </c>
       <c r="F129" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>10</v>
@@ -4236,16 +4239,16 @@
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E130">
         <v>2737</v>
       </c>
       <c r="F130" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4265,16 +4268,16 @@
     </row>
     <row r="131" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E131">
         <v>2748</v>
       </c>
       <c r="F131" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>10</v>
@@ -4294,16 +4297,16 @@
     </row>
     <row r="132" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D132" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E132">
         <v>2745</v>
       </c>
       <c r="F132" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>10</v>
@@ -4323,16 +4326,16 @@
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E133">
         <v>2246</v>
       </c>
       <c r="F133" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>10</v>
@@ -4352,16 +4355,16 @@
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E134">
         <v>2749</v>
       </c>
       <c r="F134" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4381,16 +4384,16 @@
     </row>
     <row r="135" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E135">
         <v>2245</v>
       </c>
       <c r="F135" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>10</v>
@@ -4410,16 +4413,16 @@
     </row>
     <row r="136" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D136" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E136">
         <v>2750</v>
       </c>
       <c r="F136" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>10</v>
@@ -4439,16 +4442,16 @@
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E137">
         <v>2747</v>
       </c>
       <c r="F137" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>13</v>
@@ -4468,16 +4471,16 @@
     </row>
     <row r="138" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E138">
         <v>2741</v>
       </c>
       <c r="F138" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>13</v>
@@ -4497,16 +4500,16 @@
     </row>
     <row r="139" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D139" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E139">
         <v>2739</v>
       </c>
       <c r="F139" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>13</v>
@@ -4526,16 +4529,16 @@
     </row>
     <row r="140" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D140" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E140">
         <v>2736</v>
       </c>
       <c r="F140" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>10</v>
@@ -4555,16 +4558,16 @@
     </row>
     <row r="141" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E141">
         <v>2738</v>
       </c>
       <c r="F141" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>10</v>
@@ -4584,16 +4587,16 @@
     </row>
     <row r="142" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D142" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E142">
         <v>2740</v>
       </c>
       <c r="F142" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>13</v>
@@ -4613,16 +4616,16 @@
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D143" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E143">
         <v>2742</v>
       </c>
       <c r="F143" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>10</v>
@@ -4642,16 +4645,16 @@
     </row>
     <row r="144" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D144" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E144">
         <v>2737</v>
       </c>
       <c r="F144" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>13</v>
@@ -4671,16 +4674,16 @@
     </row>
     <row r="145" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D145" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E145">
         <v>2748</v>
       </c>
       <c r="F145" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>10</v>
@@ -4700,16 +4703,16 @@
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D146" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E146">
         <v>2745</v>
       </c>
       <c r="F146" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>10</v>
@@ -4729,16 +4732,16 @@
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D147" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E147">
         <v>2246</v>
       </c>
       <c r="F147" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>10</v>
@@ -4758,16 +4761,16 @@
     </row>
     <row r="148" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D148" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E148">
         <v>2749</v>
       </c>
       <c r="F148" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>13</v>
@@ -4787,16 +4790,16 @@
     </row>
     <row r="149" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E149">
         <v>2245</v>
       </c>
       <c r="F149" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>10</v>
@@ -4816,16 +4819,16 @@
     </row>
     <row r="150" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E150">
         <v>2750</v>
       </c>
       <c r="F150" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>10</v>
@@ -4845,16 +4848,16 @@
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E151">
         <v>2747</v>
       </c>
       <c r="F151" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>10</v>
@@ -4874,16 +4877,16 @@
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E152">
         <v>2741</v>
       </c>
       <c r="F152" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>13</v>
@@ -4903,16 +4906,16 @@
     </row>
     <row r="153" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E153">
         <v>2739</v>
       </c>
       <c r="F153" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>13</v>
@@ -4932,16 +4935,16 @@
     </row>
     <row r="154" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D154" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E154">
         <v>2736</v>
       </c>
       <c r="F154" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>10</v>
@@ -4961,16 +4964,16 @@
     </row>
     <row r="155" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D155" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E155">
         <v>2738</v>
       </c>
       <c r="F155" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>13</v>
@@ -4990,16 +4993,16 @@
     </row>
     <row r="156" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D156" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E156">
         <v>2740</v>
       </c>
       <c r="F156" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>13</v>
@@ -5019,16 +5022,16 @@
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D157" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E157">
         <v>2742</v>
       </c>
       <c r="F157" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>10</v>
@@ -5048,16 +5051,16 @@
     </row>
     <row r="158" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D158" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E158">
         <v>2737</v>
       </c>
       <c r="F158" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>13</v>
@@ -5077,16 +5080,16 @@
     </row>
     <row r="159" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D159" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E159">
         <v>2748</v>
       </c>
       <c r="F159" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>10</v>
@@ -5106,16 +5109,16 @@
     </row>
     <row r="160" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E160">
         <v>2745</v>
       </c>
       <c r="F160" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>13</v>
@@ -5135,16 +5138,16 @@
     </row>
     <row r="161" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D161" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E161">
         <v>2246</v>
       </c>
       <c r="F161" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>13</v>
@@ -5164,16 +5167,16 @@
     </row>
     <row r="162" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E162">
         <v>2749</v>
       </c>
       <c r="F162" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>10</v>
@@ -5193,16 +5196,16 @@
     </row>
     <row r="163" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D163" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E163">
         <v>2245</v>
       </c>
       <c r="F163" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>10</v>
@@ -5222,16 +5225,16 @@
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D164" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E164">
         <v>2750</v>
       </c>
       <c r="F164" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>10</v>
@@ -5251,16 +5254,16 @@
     </row>
     <row r="165" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D165" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E165">
         <v>2747</v>
       </c>
       <c r="F165" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>13</v>
@@ -5280,16 +5283,16 @@
     </row>
     <row r="166" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D166" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E166">
         <v>2741</v>
       </c>
       <c r="F166" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>13</v>
@@ -5309,16 +5312,16 @@
     </row>
     <row r="167" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D167" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E167">
         <v>2739</v>
       </c>
       <c r="F167" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>12</v>
@@ -5342,21 +5345,21 @@
       <c r="J168" s="2"/>
       <c r="K168" s="1"/>
       <c r="M168" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="169" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D169" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E169">
         <v>2736</v>
       </c>
       <c r="F169" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>10</v>
@@ -5376,16 +5379,16 @@
     </row>
     <row r="170" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D170" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E170">
         <v>2738</v>
       </c>
       <c r="F170" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>14</v>
@@ -5409,21 +5412,21 @@
       <c r="J171" s="2"/>
       <c r="K171" s="1"/>
       <c r="M171" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D172" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E172">
         <v>3832</v>
       </c>
       <c r="F172" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>10</v>
@@ -5443,16 +5446,16 @@
     </row>
     <row r="173" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D173" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E173">
         <v>2740</v>
       </c>
       <c r="F173" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>13</v>
@@ -5472,16 +5475,16 @@
     </row>
     <row r="174" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D174" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E174">
         <v>3885</v>
       </c>
       <c r="F174" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>10</v>
@@ -5501,16 +5504,16 @@
     </row>
     <row r="175" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D175" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E175">
         <v>2742</v>
       </c>
       <c r="F175" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>10</v>
@@ -5530,16 +5533,16 @@
     </row>
     <row r="176" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D176" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E176">
         <v>2737</v>
       </c>
       <c r="F176" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>12</v>
@@ -5563,21 +5566,21 @@
       <c r="J177" s="2"/>
       <c r="K177" s="1"/>
       <c r="M177" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D178" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E178">
         <v>2748</v>
       </c>
       <c r="F178" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>10</v>
@@ -5597,16 +5600,16 @@
     </row>
     <row r="179" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D179" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E179">
         <v>2745</v>
       </c>
       <c r="F179" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>10</v>
@@ -5626,16 +5629,16 @@
     </row>
     <row r="180" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D180" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E180">
         <v>2246</v>
       </c>
       <c r="F180" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>10</v>
@@ -5655,16 +5658,16 @@
     </row>
     <row r="181" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D181" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E181">
         <v>2749</v>
       </c>
       <c r="F181" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>10</v>
@@ -5684,16 +5687,16 @@
     </row>
     <row r="182" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D182" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E182">
         <v>2245</v>
       </c>
       <c r="F182" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>10</v>
@@ -5713,16 +5716,16 @@
     </row>
     <row r="183" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D183" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E183">
         <v>2750</v>
       </c>
       <c r="F183" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>10</v>
@@ -5742,16 +5745,16 @@
     </row>
     <row r="184" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D184" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E184">
         <v>2747</v>
       </c>
       <c r="F184" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>10</v>
@@ -5771,16 +5774,16 @@
     </row>
     <row r="185" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D185" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E185">
         <v>2741</v>
       </c>
       <c r="F185" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>13</v>
@@ -5800,16 +5803,16 @@
     </row>
     <row r="186" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D186" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E186">
         <v>2739</v>
       </c>
       <c r="F186" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>13</v>
@@ -5829,16 +5832,16 @@
     </row>
     <row r="187" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D187" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E187">
         <v>2736</v>
       </c>
       <c r="F187" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>10</v>
@@ -5858,16 +5861,16 @@
     </row>
     <row r="188" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D188" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E188">
         <v>2738</v>
       </c>
       <c r="F188" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>13</v>
@@ -5887,16 +5890,16 @@
     </row>
     <row r="189" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D189" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E189">
         <v>3832</v>
       </c>
       <c r="F189" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>10</v>
@@ -5916,16 +5919,16 @@
     </row>
     <row r="190" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D190" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E190">
         <v>2740</v>
       </c>
       <c r="F190" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>13</v>
@@ -5945,16 +5948,16 @@
     </row>
     <row r="191" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D191" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E191">
         <v>3885</v>
       </c>
       <c r="F191" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>10</v>
@@ -5974,16 +5977,16 @@
     </row>
     <row r="192" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D192" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E192">
         <v>2742</v>
       </c>
       <c r="F192" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>10</v>
@@ -6003,16 +6006,16 @@
     </row>
     <row r="193" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D193" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E193">
         <v>2737</v>
       </c>
       <c r="F193" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>13</v>
@@ -6032,16 +6035,16 @@
     </row>
     <row r="194" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D194" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E194">
         <v>2748</v>
       </c>
       <c r="F194" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>10</v>
@@ -6061,16 +6064,16 @@
     </row>
     <row r="195" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D195" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E195">
         <v>2745</v>
       </c>
       <c r="F195" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>13</v>
@@ -6090,16 +6093,16 @@
     </row>
     <row r="196" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D196" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E196">
         <v>2246</v>
       </c>
       <c r="F196" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>10</v>
@@ -6119,16 +6122,16 @@
     </row>
     <row r="197" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D197" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E197">
         <v>2743</v>
       </c>
       <c r="F197" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>13</v>
@@ -6148,16 +6151,16 @@
     </row>
     <row r="198" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D198" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E198">
         <v>2749</v>
       </c>
       <c r="F198" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>10</v>
@@ -6177,16 +6180,16 @@
     </row>
     <row r="199" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D199" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E199">
         <v>2245</v>
       </c>
       <c r="F199" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>10</v>
@@ -6206,16 +6209,16 @@
     </row>
     <row r="200" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D200" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E200">
         <v>2750</v>
       </c>
       <c r="F200" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>10</v>
@@ -6235,16 +6238,16 @@
     </row>
     <row r="201" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D201" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E201">
         <v>2747</v>
       </c>
       <c r="F201" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>13</v>
@@ -6264,16 +6267,16 @@
     </row>
     <row r="202" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D202" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E202">
         <v>2741</v>
       </c>
       <c r="F202" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>13</v>
@@ -6293,16 +6296,16 @@
     </row>
     <row r="203" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D203" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E203">
         <v>2739</v>
       </c>
       <c r="F203" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>13</v>
@@ -6322,16 +6325,16 @@
     </row>
     <row r="204" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D204" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E204">
         <v>2736</v>
       </c>
       <c r="F204" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>10</v>
@@ -6351,16 +6354,16 @@
     </row>
     <row r="205" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D205" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E205">
         <v>2738</v>
       </c>
       <c r="F205" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>10</v>
@@ -6380,16 +6383,16 @@
     </row>
     <row r="206" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D206" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E206">
         <v>3832</v>
       </c>
       <c r="F206" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>10</v>
@@ -6409,16 +6412,16 @@
     </row>
     <row r="207" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D207" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E207">
         <v>2740</v>
       </c>
       <c r="F207" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>13</v>
@@ -6438,16 +6441,16 @@
     </row>
     <row r="208" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D208" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E208">
         <v>3885</v>
       </c>
       <c r="F208" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>10</v>
@@ -6467,16 +6470,16 @@
     </row>
     <row r="209" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D209" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E209">
         <v>2742</v>
       </c>
       <c r="F209" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>10</v>
@@ -6496,16 +6499,16 @@
     </row>
     <row r="210" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D210" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E210">
         <v>2737</v>
       </c>
       <c r="F210" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>10</v>
@@ -6525,16 +6528,16 @@
     </row>
     <row r="211" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D211" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E211">
         <v>2748</v>
       </c>
       <c r="F211" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>10</v>
@@ -6554,16 +6557,16 @@
     </row>
     <row r="212" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D212" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E212">
         <v>2745</v>
       </c>
       <c r="F212" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>10</v>
@@ -6583,16 +6586,16 @@
     </row>
     <row r="213" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D213" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E213">
         <v>2246</v>
       </c>
       <c r="F213" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>10</v>
@@ -6612,16 +6615,16 @@
     </row>
     <row r="214" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D214" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E214">
         <v>2743</v>
       </c>
       <c r="F214" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>10</v>
@@ -6641,16 +6644,16 @@
     </row>
     <row r="215" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D215" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E215">
         <v>2749</v>
       </c>
       <c r="F215" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>10</v>
@@ -6670,16 +6673,16 @@
     </row>
     <row r="216" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D216" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E216">
         <v>4755</v>
       </c>
       <c r="F216" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>10</v>
@@ -6699,16 +6702,16 @@
     </row>
     <row r="217" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D217" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E217">
         <v>2245</v>
       </c>
       <c r="F217" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>10</v>
@@ -6728,16 +6731,16 @@
     </row>
     <row r="218" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D218" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E218">
         <v>2750</v>
       </c>
       <c r="F218" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>10</v>
@@ -6757,16 +6760,16 @@
     </row>
     <row r="219" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D219" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E219">
         <v>2747</v>
       </c>
       <c r="F219" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>10</v>
@@ -6786,16 +6789,16 @@
     </row>
     <row r="220" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D220" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E220">
         <v>2741</v>
       </c>
       <c r="F220" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>10</v>
@@ -6815,16 +6818,16 @@
     </row>
     <row r="221" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D221" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E221">
         <v>2739</v>
       </c>
       <c r="F221" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>10</v>
@@ -6844,16 +6847,16 @@
     </row>
     <row r="222" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D222" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E222">
         <v>2736</v>
       </c>
       <c r="F222" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>10</v>
@@ -6873,16 +6876,16 @@
     </row>
     <row r="223" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D223" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E223">
         <v>2738</v>
       </c>
       <c r="F223" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>10</v>
@@ -6902,16 +6905,16 @@
     </row>
     <row r="224" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D224" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E224">
         <v>3832</v>
       </c>
       <c r="F224" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>10</v>
@@ -6931,16 +6934,16 @@
     </row>
     <row r="225" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D225" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E225">
         <v>2740</v>
       </c>
       <c r="F225" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>12</v>
@@ -6964,21 +6967,21 @@
       <c r="J226" s="2"/>
       <c r="K226" s="1"/>
       <c r="M226" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="227" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D227" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E227">
         <v>3885</v>
       </c>
       <c r="F227" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>10</v>
@@ -6998,16 +7001,16 @@
     </row>
     <row r="228" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D228" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E228">
         <v>2742</v>
       </c>
       <c r="F228" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>10</v>
@@ -7027,16 +7030,16 @@
     </row>
     <row r="229" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D229" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E229">
         <v>2737</v>
       </c>
       <c r="F229" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>10</v>
@@ -7056,16 +7059,16 @@
     </row>
     <row r="230" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D230" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E230">
         <v>2748</v>
       </c>
       <c r="F230" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>10</v>
@@ -7085,16 +7088,16 @@
     </row>
     <row r="231" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D231" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E231">
         <v>2745</v>
       </c>
       <c r="F231" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>10</v>
@@ -7114,16 +7117,16 @@
     </row>
     <row r="232" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D232" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E232">
         <v>2246</v>
       </c>
       <c r="F232" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>10</v>
@@ -7143,16 +7146,16 @@
     </row>
     <row r="233" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D233" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E233">
         <v>2743</v>
       </c>
       <c r="F233" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>13</v>
@@ -7172,16 +7175,16 @@
     </row>
     <row r="234" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D234" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E234">
         <v>2749</v>
       </c>
       <c r="F234" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>10</v>
@@ -7201,16 +7204,16 @@
     </row>
     <row r="235" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D235" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E235">
         <v>4755</v>
       </c>
       <c r="F235" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>10</v>
@@ -7230,16 +7233,16 @@
     </row>
     <row r="236" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D236" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E236">
         <v>2245</v>
       </c>
       <c r="F236" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>10</v>
@@ -7259,16 +7262,16 @@
     </row>
     <row r="237" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D237" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E237">
         <v>2750</v>
       </c>
       <c r="F237" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>10</v>
@@ -7288,16 +7291,16 @@
     </row>
     <row r="238" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D238" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E238">
         <v>2747</v>
       </c>
       <c r="F238" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>10</v>
@@ -7317,16 +7320,16 @@
     </row>
     <row r="239" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D239" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E239">
         <v>2741</v>
       </c>
       <c r="F239" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>10</v>
@@ -7346,16 +7349,16 @@
     </row>
     <row r="240" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D240" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E240">
         <v>2739</v>
       </c>
       <c r="F240" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>10</v>
@@ -7375,16 +7378,16 @@
     </row>
     <row r="241" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D241" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E241">
         <v>2736</v>
       </c>
       <c r="F241" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>10</v>
@@ -7404,16 +7407,16 @@
     </row>
     <row r="242" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D242" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E242">
         <v>2738</v>
       </c>
       <c r="F242" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>10</v>
@@ -7433,16 +7436,16 @@
     </row>
     <row r="243" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D243" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E243">
         <v>3832</v>
       </c>
       <c r="F243" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>10</v>
@@ -7462,16 +7465,16 @@
     </row>
     <row r="244" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D244" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E244">
         <v>2740</v>
       </c>
       <c r="F244" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>10</v>
@@ -7491,16 +7494,16 @@
     </row>
     <row r="245" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D245" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E245">
         <v>3885</v>
       </c>
       <c r="F245" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>10</v>
@@ -7520,16 +7523,16 @@
     </row>
     <row r="246" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D246" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E246">
         <v>2742</v>
       </c>
       <c r="F246" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>14</v>
@@ -7553,21 +7556,21 @@
       <c r="J247" s="2"/>
       <c r="K247" s="1"/>
       <c r="M247" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="248" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D248" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E248">
         <v>2737</v>
       </c>
       <c r="F248" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>10</v>
@@ -7587,16 +7590,16 @@
     </row>
     <row r="249" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D249" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E249">
         <v>2748</v>
       </c>
       <c r="F249" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>10</v>
@@ -7616,16 +7619,16 @@
     </row>
     <row r="250" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D250" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E250">
         <v>2745</v>
       </c>
       <c r="F250" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>10</v>
@@ -7645,16 +7648,16 @@
     </row>
     <row r="251" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D251" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E251">
         <v>2246</v>
       </c>
       <c r="F251" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>10</v>
@@ -7674,16 +7677,16 @@
     </row>
     <row r="252" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D252" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E252">
         <v>2749</v>
       </c>
       <c r="F252" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>10</v>
@@ -7703,16 +7706,16 @@
     </row>
     <row r="253" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D253" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E253">
         <v>5032</v>
       </c>
       <c r="F253" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>10</v>
@@ -7732,16 +7735,16 @@
     </row>
     <row r="254" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D254" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E254">
         <v>4755</v>
       </c>
       <c r="F254" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>12</v>
@@ -7765,21 +7768,21 @@
       <c r="J255" s="2"/>
       <c r="K255" s="1"/>
       <c r="M255" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="256" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D256" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E256">
         <v>2245</v>
       </c>
       <c r="F256" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>10</v>
@@ -7799,16 +7802,16 @@
     </row>
     <row r="257" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D257" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E257">
         <v>2750</v>
       </c>
       <c r="F257" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>10</v>
@@ -7828,16 +7831,16 @@
     </row>
     <row r="258" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D258" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E258">
         <v>2747</v>
       </c>
       <c r="F258" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>10</v>
@@ -7857,16 +7860,16 @@
     </row>
     <row r="259" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D259" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E259">
         <v>2741</v>
       </c>
       <c r="F259" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>12</v>
@@ -7890,21 +7893,21 @@
       <c r="J260" s="2"/>
       <c r="K260" s="1"/>
       <c r="M260" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="261" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D261" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E261">
         <v>2739</v>
       </c>
       <c r="F261" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>12</v>
@@ -7928,21 +7931,21 @@
       <c r="J262" s="2"/>
       <c r="K262" s="1"/>
       <c r="M262" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="263" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D263" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E263">
         <v>2736</v>
       </c>
       <c r="F263" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>10</v>
@@ -7962,16 +7965,16 @@
     </row>
     <row r="264" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D264" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E264">
         <v>2738</v>
       </c>
       <c r="F264" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>10</v>
@@ -7991,16 +7994,16 @@
     </row>
     <row r="265" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D265" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E265">
         <v>3832</v>
       </c>
       <c r="F265" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>10</v>
@@ -8020,16 +8023,16 @@
     </row>
     <row r="266" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D266" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E266">
         <v>2740</v>
       </c>
       <c r="F266" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>10</v>
@@ -8049,16 +8052,16 @@
     </row>
     <row r="267" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D267" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E267">
         <v>3885</v>
       </c>
       <c r="F267" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>10</v>
@@ -8078,16 +8081,16 @@
     </row>
     <row r="268" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D268" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E268">
         <v>2742</v>
       </c>
       <c r="F268" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>10</v>
@@ -8107,16 +8110,16 @@
     </row>
     <row r="269" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D269" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E269">
         <v>2737</v>
       </c>
       <c r="F269" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>10</v>
@@ -8136,16 +8139,16 @@
     </row>
     <row r="270" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D270" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E270">
         <v>2748</v>
       </c>
       <c r="F270" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>10</v>
@@ -8165,16 +8168,16 @@
     </row>
     <row r="271" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D271" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E271">
         <v>2745</v>
       </c>
       <c r="F271" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>10</v>
@@ -8194,16 +8197,16 @@
     </row>
     <row r="272" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D272" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E272">
         <v>2246</v>
       </c>
       <c r="F272" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>10</v>
@@ -8223,16 +8226,16 @@
     </row>
     <row r="273" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D273" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E273">
         <v>2749</v>
       </c>
       <c r="F273" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>10</v>
@@ -8252,16 +8255,16 @@
     </row>
     <row r="274" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D274" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E274">
         <v>5032</v>
       </c>
       <c r="F274" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>10</v>
@@ -8281,16 +8284,16 @@
     </row>
     <row r="275" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D275" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E275">
         <v>4755</v>
       </c>
       <c r="F275" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>10</v>
@@ -8310,16 +8313,16 @@
     </row>
     <row r="276" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D276" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E276">
         <v>2245</v>
       </c>
       <c r="F276" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>10</v>
@@ -8339,16 +8342,16 @@
     </row>
     <row r="277" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D277" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E277">
         <v>2750</v>
       </c>
       <c r="F277" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>10</v>
@@ -8368,16 +8371,16 @@
     </row>
     <row r="278" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D278" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E278">
         <v>2747</v>
       </c>
       <c r="F278" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>10</v>
@@ -8397,16 +8400,16 @@
     </row>
     <row r="279" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D279" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E279">
         <v>2741</v>
       </c>
       <c r="F279" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>10</v>
@@ -8426,16 +8429,16 @@
     </row>
     <row r="280" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D280" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E280">
         <v>2739</v>
       </c>
       <c r="F280" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>10</v>
@@ -8455,16 +8458,16 @@
     </row>
     <row r="281" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D281" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E281">
         <v>2736</v>
       </c>
       <c r="F281" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>10</v>
@@ -8484,16 +8487,16 @@
     </row>
     <row r="282" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D282" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E282">
         <v>2738</v>
       </c>
       <c r="F282" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>10</v>
@@ -8513,16 +8516,16 @@
     </row>
     <row r="283" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D283" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E283">
         <v>3832</v>
       </c>
       <c r="F283" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>10</v>
@@ -8542,16 +8545,16 @@
     </row>
     <row r="284" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D284" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E284">
         <v>2740</v>
       </c>
       <c r="F284" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>10</v>
@@ -8571,16 +8574,16 @@
     </row>
     <row r="285" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D285" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E285">
         <v>3885</v>
       </c>
       <c r="F285" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>10</v>
@@ -8600,16 +8603,16 @@
     </row>
     <row r="286" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D286" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E286">
         <v>2742</v>
       </c>
       <c r="F286" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>10</v>
@@ -8629,16 +8632,16 @@
     </row>
     <row r="287" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D287" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E287">
         <v>2737</v>
       </c>
       <c r="F287" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>10</v>
@@ -8658,16 +8661,16 @@
     </row>
     <row r="288" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D288" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E288">
         <v>2748</v>
       </c>
       <c r="F288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>10</v>
@@ -8687,16 +8690,16 @@
     </row>
     <row r="289" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D289" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E289">
         <v>2745</v>
       </c>
       <c r="F289" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>10</v>
@@ -8716,16 +8719,16 @@
     </row>
     <row r="290" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D290" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E290">
         <v>2246</v>
       </c>
       <c r="F290" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>10</v>
@@ -8745,16 +8748,16 @@
     </row>
     <row r="291" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D291" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E291">
         <v>2749</v>
       </c>
       <c r="F291" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>10</v>
@@ -8774,16 +8777,16 @@
     </row>
     <row r="292" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D292" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E292">
         <v>5032</v>
       </c>
       <c r="F292" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>12</v>
@@ -8807,21 +8810,21 @@
       <c r="J293" s="2"/>
       <c r="K293" s="1"/>
       <c r="M293" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="294" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D294" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E294">
         <v>4755</v>
       </c>
       <c r="F294" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>10</v>
@@ -8841,16 +8844,16 @@
     </row>
     <row r="295" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D295" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E295">
         <v>2245</v>
       </c>
       <c r="F295" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>10</v>
@@ -8870,16 +8873,16 @@
     </row>
     <row r="296" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D296" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E296">
         <v>2750</v>
       </c>
       <c r="F296" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>10</v>
@@ -8899,16 +8902,16 @@
     </row>
     <row r="297" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D297" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E297">
         <v>2747</v>
       </c>
       <c r="F297" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>10</v>
@@ -8928,16 +8931,16 @@
     </row>
     <row r="298" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D298" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E298">
         <v>2741</v>
       </c>
       <c r="F298" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>10</v>
@@ -8957,16 +8960,16 @@
     </row>
     <row r="299" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D299" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E299">
         <v>2739</v>
       </c>
       <c r="F299" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>10</v>
@@ -8986,16 +8989,16 @@
     </row>
     <row r="300" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D300" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E300">
         <v>2736</v>
       </c>
       <c r="F300" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>12</v>
@@ -9019,21 +9022,21 @@
       <c r="J301" s="2"/>
       <c r="K301" s="1"/>
       <c r="M301" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="302" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D302" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E302">
         <v>3832</v>
       </c>
       <c r="F302" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>10</v>
@@ -9053,16 +9056,16 @@
     </row>
     <row r="303" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D303" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E303">
         <v>2740</v>
       </c>
       <c r="F303" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>10</v>
@@ -9082,16 +9085,16 @@
     </row>
     <row r="304" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D304" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E304">
         <v>3885</v>
       </c>
       <c r="F304" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>10</v>
@@ -9111,16 +9114,16 @@
     </row>
     <row r="305" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D305" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E305">
         <v>2742</v>
       </c>
       <c r="F305" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>10</v>
@@ -9140,16 +9143,16 @@
     </row>
     <row r="306" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D306" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E306">
         <v>2737</v>
       </c>
       <c r="F306" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>12</v>
@@ -9173,21 +9176,21 @@
       <c r="J307" s="2"/>
       <c r="K307" s="1"/>
       <c r="M307" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="308" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D308" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E308">
         <v>2748</v>
       </c>
       <c r="F308" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>10</v>
@@ -9207,16 +9210,16 @@
     </row>
     <row r="309" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D309" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E309">
         <v>2745</v>
       </c>
       <c r="F309" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>10</v>
@@ -9236,16 +9239,16 @@
     </row>
     <row r="310" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D310" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E310">
         <v>2246</v>
       </c>
       <c r="F310" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>10</v>
@@ -9265,16 +9268,16 @@
     </row>
     <row r="311" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D311" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E311">
         <v>5274</v>
       </c>
       <c r="F311" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>10</v>
@@ -9294,16 +9297,16 @@
     </row>
     <row r="312" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D312" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E312">
         <v>2749</v>
       </c>
       <c r="F312" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>10</v>
@@ -9323,16 +9326,16 @@
     </row>
     <row r="313" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D313" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E313">
         <v>5032</v>
       </c>
       <c r="F313" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>10</v>
@@ -9352,16 +9355,16 @@
     </row>
     <row r="314" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D314" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E314">
         <v>4755</v>
       </c>
       <c r="F314" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>10</v>
@@ -9381,16 +9384,16 @@
     </row>
     <row r="315" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D315" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E315">
         <v>2245</v>
       </c>
       <c r="F315" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I315" s="1" t="s">
         <v>10</v>
@@ -9410,16 +9413,16 @@
     </row>
     <row r="316" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D316" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E316">
         <v>2750</v>
       </c>
       <c r="F316" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>10</v>
@@ -9439,16 +9442,16 @@
     </row>
     <row r="317" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D317" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E317">
         <v>2747</v>
       </c>
       <c r="F317" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>10</v>
@@ -9468,16 +9471,16 @@
     </row>
     <row r="318" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D318" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E318">
         <v>2741</v>
       </c>
       <c r="F318" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>12</v>
@@ -9501,21 +9504,21 @@
       <c r="J319" s="2"/>
       <c r="K319" s="1"/>
       <c r="M319" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="320" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D320" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E320">
         <v>2739</v>
       </c>
       <c r="F320" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>10</v>
@@ -9535,16 +9538,16 @@
     </row>
     <row r="321" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D321" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E321">
         <v>2736</v>
       </c>
       <c r="F321" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>10</v>
@@ -9564,16 +9567,16 @@
     </row>
     <row r="322" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D322" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E322">
         <v>3832</v>
       </c>
       <c r="F322" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>10</v>
@@ -9593,16 +9596,16 @@
     </row>
     <row r="323" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D323" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E323">
         <v>2740</v>
       </c>
       <c r="F323" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I323" s="1" t="s">
         <v>10</v>
@@ -9622,16 +9625,16 @@
     </row>
     <row r="324" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D324" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E324">
         <v>3885</v>
       </c>
       <c r="F324" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>10</v>
@@ -9651,16 +9654,16 @@
     </row>
     <row r="325" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D325" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E325">
         <v>2742</v>
       </c>
       <c r="F325" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>10</v>
@@ -9680,16 +9683,16 @@
     </row>
     <row r="326" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D326" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E326">
         <v>2737</v>
       </c>
       <c r="F326" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>12</v>
@@ -9713,21 +9716,21 @@
       <c r="J327" s="2"/>
       <c r="K327" s="1"/>
       <c r="M327" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="328" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D328" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E328">
         <v>2748</v>
       </c>
       <c r="F328" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>10</v>
@@ -9747,16 +9750,16 @@
     </row>
     <row r="329" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D329" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E329">
         <v>2745</v>
       </c>
       <c r="F329" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>10</v>
@@ -9776,16 +9779,16 @@
     </row>
     <row r="330" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D330" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E330">
         <v>2246</v>
       </c>
       <c r="F330" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>10</v>
@@ -9805,16 +9808,16 @@
     </row>
     <row r="331" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D331" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E331">
         <v>5274</v>
       </c>
       <c r="F331" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>10</v>
@@ -9834,16 +9837,16 @@
     </row>
     <row r="332" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D332" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E332">
         <v>2749</v>
       </c>
       <c r="F332" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>12</v>
@@ -9867,21 +9870,21 @@
       <c r="J333" s="2"/>
       <c r="K333" s="1"/>
       <c r="M333" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="334" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D334" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E334">
         <v>5032</v>
       </c>
       <c r="F334" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>10</v>
@@ -9901,16 +9904,16 @@
     </row>
     <row r="335" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D335" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E335">
         <v>4755</v>
       </c>
       <c r="F335" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>10</v>
@@ -9930,16 +9933,16 @@
     </row>
     <row r="336" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D336" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E336">
         <v>2245</v>
       </c>
       <c r="F336" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>10</v>
@@ -9959,16 +9962,16 @@
     </row>
     <row r="337" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D337" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E337">
         <v>2750</v>
       </c>
       <c r="F337" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>10</v>
@@ -9988,16 +9991,16 @@
     </row>
     <row r="338" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D338" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E338">
         <v>2747</v>
       </c>
       <c r="F338" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>10</v>
@@ -10017,16 +10020,16 @@
     </row>
     <row r="339" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D339" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E339">
         <v>2741</v>
       </c>
       <c r="F339" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>10</v>
@@ -10046,16 +10049,16 @@
     </row>
     <row r="340" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D340" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E340">
         <v>2739</v>
       </c>
       <c r="F340" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>10</v>
@@ -10075,16 +10078,16 @@
     </row>
     <row r="341" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D341" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E341">
         <v>2736</v>
       </c>
       <c r="F341" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>10</v>
@@ -10104,16 +10107,16 @@
     </row>
     <row r="342" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D342" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E342">
         <v>3832</v>
       </c>
       <c r="F342" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>10</v>
@@ -10133,16 +10136,16 @@
     </row>
     <row r="343" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D343" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E343">
         <v>2740</v>
       </c>
       <c r="F343" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>10</v>
@@ -10162,16 +10165,16 @@
     </row>
     <row r="344" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D344" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E344">
         <v>3885</v>
       </c>
       <c r="F344" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>10</v>
@@ -10191,16 +10194,16 @@
     </row>
     <row r="345" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D345" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E345">
         <v>2742</v>
       </c>
       <c r="F345" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>10</v>
@@ -10220,16 +10223,16 @@
     </row>
     <row r="346" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D346" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E346">
         <v>2737</v>
       </c>
       <c r="F346" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I346" s="1" t="s">
         <v>10</v>
@@ -10249,16 +10252,16 @@
     </row>
     <row r="347" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D347" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E347">
         <v>2748</v>
       </c>
       <c r="F347" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>10</v>
@@ -10278,16 +10281,16 @@
     </row>
     <row r="348" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D348" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E348">
         <v>2745</v>
       </c>
       <c r="F348" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>10</v>
@@ -10307,16 +10310,16 @@
     </row>
     <row r="349" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D349" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E349">
         <v>2246</v>
       </c>
       <c r="F349" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>10</v>
@@ -10336,16 +10339,16 @@
     </row>
     <row r="350" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D350" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E350">
         <v>5274</v>
       </c>
       <c r="F350" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>10</v>
@@ -10365,16 +10368,16 @@
     </row>
     <row r="351" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D351" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E351">
         <v>2749</v>
       </c>
       <c r="F351" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>10</v>
@@ -10394,16 +10397,16 @@
     </row>
     <row r="352" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D352" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E352">
         <v>5032</v>
       </c>
       <c r="F352" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>12</v>
@@ -10427,21 +10430,21 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
       <c r="M353" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="354" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D354" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E354">
         <v>4755</v>
       </c>
       <c r="F354" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I354" s="1" t="s">
         <v>14</v>
@@ -10465,21 +10468,21 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
       <c r="M355" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="356" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D356" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E356">
         <v>2245</v>
       </c>
       <c r="F356" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>10</v>
@@ -10499,16 +10502,16 @@
     </row>
     <row r="357" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D357" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E357">
         <v>2750</v>
       </c>
       <c r="F357" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I357" s="1" t="s">
         <v>10</v>
@@ -10528,16 +10531,16 @@
     </row>
     <row r="358" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D358" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E358">
         <v>2747</v>
       </c>
       <c r="F358" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I358" s="1" t="s">
         <v>10</v>
@@ -10557,16 +10560,16 @@
     </row>
     <row r="359" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D359" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E359">
         <v>2741</v>
       </c>
       <c r="F359" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I359" s="1" t="s">
         <v>10</v>
@@ -10586,16 +10589,16 @@
     </row>
     <row r="360" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D360" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E360">
         <v>2739</v>
       </c>
       <c r="F360" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H360" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I360" s="1" t="s">
         <v>10</v>
@@ -10615,16 +10618,16 @@
     </row>
     <row r="361" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D361" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E361">
         <v>2736</v>
       </c>
       <c r="F361" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H361" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I361" s="1" t="s">
         <v>10</v>
@@ -10644,16 +10647,16 @@
     </row>
     <row r="362" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D362" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E362">
         <v>3832</v>
       </c>
       <c r="F362" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I362" s="1" t="s">
         <v>10</v>
@@ -10673,16 +10676,16 @@
     </row>
     <row r="363" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D363" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E363">
         <v>3885</v>
       </c>
       <c r="F363" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H363" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I363" s="1" t="s">
         <v>10</v>
@@ -10702,16 +10705,16 @@
     </row>
     <row r="364" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D364" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E364">
         <v>5032</v>
       </c>
       <c r="F364" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H364" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I364" s="1" t="s">
         <v>10</v>
@@ -10731,16 +10734,16 @@
     </row>
     <row r="365" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D365" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E365">
         <v>2245</v>
       </c>
       <c r="F365" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H365" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I365" s="1" t="s">
         <v>10</v>
@@ -10760,16 +10763,16 @@
     </row>
     <row r="366" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D366" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E366">
         <v>2747</v>
       </c>
       <c r="F366" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I366" s="1" t="s">
         <v>10</v>
@@ -10789,16 +10792,16 @@
     </row>
     <row r="367" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D367" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E367">
         <v>2745</v>
       </c>
       <c r="F367" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>10</v>
@@ -10818,16 +10821,16 @@
     </row>
     <row r="368" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D368" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E368">
         <v>2740</v>
       </c>
       <c r="F368" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>10</v>
@@ -10847,16 +10850,16 @@
     </row>
     <row r="369" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D369" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E369">
         <v>2742</v>
       </c>
       <c r="F369" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I369" s="1" t="s">
         <v>10</v>
@@ -10876,16 +10879,16 @@
     </row>
     <row r="370" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D370" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E370">
         <v>2737</v>
       </c>
       <c r="F370" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>10</v>
@@ -10905,16 +10908,16 @@
     </row>
     <row r="371" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D371" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E371">
         <v>2748</v>
       </c>
       <c r="F371" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H371" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I371" s="1" t="s">
         <v>10</v>
@@ -10934,16 +10937,16 @@
     </row>
     <row r="372" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D372" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E372">
         <v>2246</v>
       </c>
       <c r="F372" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H372" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I372" s="1" t="s">
         <v>13</v>
@@ -10963,16 +10966,16 @@
     </row>
     <row r="373" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D373" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E373">
         <v>5274</v>
       </c>
       <c r="F373" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H373" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I373" s="1" t="s">
         <v>10</v>
@@ -10992,16 +10995,16 @@
     </row>
     <row r="374" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D374" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E374">
         <v>5607</v>
       </c>
       <c r="F374" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>10</v>
@@ -11021,16 +11024,16 @@
     </row>
     <row r="375" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D375" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E375">
         <v>4755</v>
       </c>
       <c r="F375" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>10</v>
@@ -11050,16 +11053,16 @@
     </row>
     <row r="376" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D376" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E376">
         <v>2750</v>
       </c>
       <c r="F376" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>10</v>
@@ -11079,16 +11082,16 @@
     </row>
     <row r="377" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D377" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E377">
         <v>2741</v>
       </c>
       <c r="F377" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I377" s="1" t="s">
         <v>10</v>
@@ -11108,16 +11111,16 @@
     </row>
     <row r="378" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D378" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E378">
         <v>2739</v>
       </c>
       <c r="F378" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>10</v>
@@ -11137,16 +11140,16 @@
     </row>
     <row r="379" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D379" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E379">
         <v>2736</v>
       </c>
       <c r="F379" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>10</v>
@@ -11165,126 +11168,563 @@
       </c>
     </row>
     <row r="380" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H380" s="2"/>
-      <c r="I380" s="1"/>
-      <c r="J380" s="2"/>
-      <c r="K380" s="1"/>
+      <c r="D380" t="s">
+        <v>37</v>
+      </c>
+      <c r="E380">
+        <v>3832</v>
+      </c>
+      <c r="F380" t="s">
+        <v>56</v>
+      </c>
+      <c r="H380" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I380" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J380" s="2">
+        <v>1.1678240740740741E-2</v>
+      </c>
+      <c r="K380" s="1">
+        <v>46219.632291666669</v>
+      </c>
+      <c r="L380">
+        <v>0</v>
+      </c>
+      <c r="M380" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="381" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H381" s="2"/>
-      <c r="I381" s="1"/>
-      <c r="J381" s="2"/>
-      <c r="K381" s="1"/>
+      <c r="D381" t="s">
+        <v>37</v>
+      </c>
+      <c r="E381">
+        <v>2740</v>
+      </c>
+      <c r="F381" t="s">
+        <v>41</v>
+      </c>
+      <c r="H381" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I381" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J381" s="2">
+        <v>0</v>
+      </c>
+      <c r="K381" s="1">
+        <v>46219.632986111108</v>
+      </c>
+      <c r="L381">
+        <v>0</v>
+      </c>
+      <c r="M381" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="382" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H382" s="2"/>
-      <c r="I382" s="1"/>
-      <c r="J382" s="2"/>
-      <c r="K382" s="1"/>
+      <c r="D382" t="s">
+        <v>37</v>
+      </c>
+      <c r="E382">
+        <v>3885</v>
+      </c>
+      <c r="F382" t="s">
+        <v>57</v>
+      </c>
+      <c r="H382" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I382" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J382" s="2">
+        <v>7.037037037037037E-3</v>
+      </c>
+      <c r="K382" s="1">
+        <v>46219.633680555555</v>
+      </c>
+      <c r="L382">
+        <v>0</v>
+      </c>
+      <c r="M382" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="383" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H383" s="2"/>
-      <c r="I383" s="1"/>
-      <c r="J383" s="2"/>
-      <c r="K383" s="1"/>
+      <c r="D383" t="s">
+        <v>37</v>
+      </c>
+      <c r="E383">
+        <v>2742</v>
+      </c>
+      <c r="F383" t="s">
+        <v>43</v>
+      </c>
+      <c r="H383" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I383" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J383" s="2">
+        <v>0</v>
+      </c>
+      <c r="K383" s="1">
+        <v>46219.633680555555</v>
+      </c>
+      <c r="L383">
+        <v>0</v>
+      </c>
+      <c r="M383" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="384" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H384" s="2"/>
-      <c r="I384" s="1"/>
-      <c r="J384" s="2"/>
-      <c r="K384" s="1"/>
-    </row>
-    <row r="385" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H385" s="2"/>
-      <c r="I385" s="1"/>
-      <c r="J385" s="2"/>
-      <c r="K385" s="1"/>
-    </row>
-    <row r="386" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H386" s="2"/>
-      <c r="I386" s="1"/>
-      <c r="J386" s="2"/>
-      <c r="K386" s="1"/>
-    </row>
-    <row r="387" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H387" s="2"/>
-      <c r="I387" s="1"/>
-      <c r="J387" s="2"/>
-      <c r="K387" s="1"/>
-    </row>
-    <row r="388" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H388" s="2"/>
-      <c r="I388" s="1"/>
-      <c r="J388" s="2"/>
-      <c r="K388" s="1"/>
-    </row>
-    <row r="389" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H389" s="2"/>
-      <c r="I389" s="1"/>
-      <c r="J389" s="2"/>
-      <c r="K389" s="1"/>
-    </row>
-    <row r="390" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H390" s="2"/>
-      <c r="I390" s="1"/>
-      <c r="J390" s="2"/>
-      <c r="K390" s="1"/>
-    </row>
-    <row r="391" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H391" s="2"/>
-      <c r="I391" s="1"/>
-      <c r="J391" s="2"/>
-      <c r="K391" s="1"/>
-    </row>
-    <row r="392" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H392" s="2"/>
-      <c r="I392" s="1"/>
-      <c r="J392" s="2"/>
-      <c r="K392" s="1"/>
-    </row>
-    <row r="393" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H393" s="2"/>
-      <c r="I393" s="1"/>
-      <c r="J393" s="2"/>
-      <c r="K393" s="1"/>
-    </row>
-    <row r="394" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H394" s="2"/>
-      <c r="I394" s="1"/>
-      <c r="J394" s="2"/>
-      <c r="K394" s="1"/>
-    </row>
-    <row r="395" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H395" s="2"/>
-      <c r="I395" s="1"/>
-      <c r="J395" s="2"/>
-      <c r="K395" s="1"/>
-    </row>
-    <row r="396" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H396" s="2"/>
-      <c r="I396" s="1"/>
-      <c r="J396" s="2"/>
-      <c r="K396" s="1"/>
-    </row>
-    <row r="397" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H397" s="2"/>
-      <c r="I397" s="1"/>
-      <c r="J397" s="2"/>
-      <c r="K397" s="1"/>
-    </row>
-    <row r="398" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H398" s="2"/>
-      <c r="I398" s="1"/>
-      <c r="J398" s="2"/>
-      <c r="K398" s="1"/>
-    </row>
-    <row r="399" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D384" t="s">
+        <v>37</v>
+      </c>
+      <c r="E384">
+        <v>2737</v>
+      </c>
+      <c r="F384" t="s">
+        <v>44</v>
+      </c>
+      <c r="H384" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I384" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J384" s="2">
+        <v>5.6053240740740744E-2</v>
+      </c>
+      <c r="K384" s="1">
+        <v>46219.634375000001</v>
+      </c>
+      <c r="L384">
+        <v>0</v>
+      </c>
+      <c r="M384" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="385" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D385" t="s">
+        <v>37</v>
+      </c>
+      <c r="E385">
+        <v>2748</v>
+      </c>
+      <c r="F385" t="s">
+        <v>45</v>
+      </c>
+      <c r="H385" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I385" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J385" s="2">
+        <v>4.521990740740741E-2</v>
+      </c>
+      <c r="K385" s="1">
+        <v>46219.635069444441</v>
+      </c>
+      <c r="L385">
+        <v>0</v>
+      </c>
+      <c r="M385" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="386" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D386" t="s">
+        <v>37</v>
+      </c>
+      <c r="E386">
+        <v>2745</v>
+      </c>
+      <c r="F386" t="s">
+        <v>46</v>
+      </c>
+      <c r="H386" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I386" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J386" s="2">
+        <v>0</v>
+      </c>
+      <c r="K386" s="1">
+        <v>46219.635763888888</v>
+      </c>
+      <c r="L386">
+        <v>0</v>
+      </c>
+      <c r="M386" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="387" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D387" t="s">
+        <v>37</v>
+      </c>
+      <c r="E387">
+        <v>2246</v>
+      </c>
+      <c r="F387" t="s">
+        <v>38</v>
+      </c>
+      <c r="H387" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I387" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J387" s="2">
+        <v>0</v>
+      </c>
+      <c r="K387" s="1">
+        <v>46219.635763888888</v>
+      </c>
+      <c r="L387">
+        <v>0</v>
+      </c>
+      <c r="M387" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="388" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D388" t="s">
+        <v>37</v>
+      </c>
+      <c r="E388">
+        <v>5274</v>
+      </c>
+      <c r="F388" t="s">
+        <v>60</v>
+      </c>
+      <c r="H388" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I388" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J388" s="2">
+        <v>0</v>
+      </c>
+      <c r="K388" s="1">
+        <v>46219.636458333334</v>
+      </c>
+      <c r="L388">
+        <v>0</v>
+      </c>
+      <c r="M388" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="389" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D389" t="s">
+        <v>37</v>
+      </c>
+      <c r="E389">
+        <v>5607</v>
+      </c>
+      <c r="F389" t="s">
+        <v>61</v>
+      </c>
+      <c r="H389" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I389" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J389" s="2">
+        <v>6.4583333333333333E-3</v>
+      </c>
+      <c r="K389" s="1">
+        <v>46219.637152777781</v>
+      </c>
+      <c r="L389">
+        <v>0</v>
+      </c>
+      <c r="M389" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="390" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D390" t="s">
+        <v>37</v>
+      </c>
+      <c r="E390">
+        <v>2749</v>
+      </c>
+      <c r="F390" t="s">
+        <v>49</v>
+      </c>
+      <c r="H390" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I390" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J390" s="2">
+        <v>0</v>
+      </c>
+      <c r="K390" s="1">
+        <v>46219.63784722222</v>
+      </c>
+      <c r="L390">
+        <v>0</v>
+      </c>
+      <c r="M390" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="391" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D391" t="s">
+        <v>37</v>
+      </c>
+      <c r="E391">
+        <v>5032</v>
+      </c>
+      <c r="F391" t="s">
+        <v>59</v>
+      </c>
+      <c r="H391" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I391" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J391" s="2">
+        <v>0</v>
+      </c>
+      <c r="K391" s="1">
+        <v>46219.638541666667</v>
+      </c>
+      <c r="L391">
+        <v>0</v>
+      </c>
+      <c r="M391" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="392" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D392" t="s">
+        <v>37</v>
+      </c>
+      <c r="E392">
+        <v>4755</v>
+      </c>
+      <c r="F392" t="s">
+        <v>58</v>
+      </c>
+      <c r="H392" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I392" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J392" s="2">
+        <v>0</v>
+      </c>
+      <c r="K392" s="1">
+        <v>46219.638541666667</v>
+      </c>
+      <c r="L392">
+        <v>0</v>
+      </c>
+      <c r="M392" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="393" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D393" t="s">
+        <v>37</v>
+      </c>
+      <c r="E393">
+        <v>2245</v>
+      </c>
+      <c r="F393" t="s">
+        <v>39</v>
+      </c>
+      <c r="H393" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I393" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J393" s="2">
+        <v>0</v>
+      </c>
+      <c r="K393" s="1">
+        <v>46219.639236111114</v>
+      </c>
+      <c r="L393">
+        <v>0</v>
+      </c>
+      <c r="M393" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="394" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D394" t="s">
+        <v>37</v>
+      </c>
+      <c r="E394">
+        <v>2750</v>
+      </c>
+      <c r="F394" t="s">
+        <v>51</v>
+      </c>
+      <c r="H394" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I394" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J394" s="2">
+        <v>6.6087962962962966E-3</v>
+      </c>
+      <c r="K394" s="1">
+        <v>46219.639930555553</v>
+      </c>
+      <c r="L394">
+        <v>0</v>
+      </c>
+      <c r="M394" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="395" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D395" t="s">
+        <v>37</v>
+      </c>
+      <c r="E395">
+        <v>2747</v>
+      </c>
+      <c r="F395" t="s">
+        <v>52</v>
+      </c>
+      <c r="H395" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I395" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J395" s="2">
+        <v>0</v>
+      </c>
+      <c r="K395" s="1">
+        <v>46219.639930555553</v>
+      </c>
+      <c r="L395">
+        <v>0</v>
+      </c>
+      <c r="M395" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="396" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D396" t="s">
+        <v>37</v>
+      </c>
+      <c r="E396">
+        <v>2741</v>
+      </c>
+      <c r="F396" t="s">
+        <v>53</v>
+      </c>
+      <c r="H396" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I396" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J396" s="2">
+        <v>0</v>
+      </c>
+      <c r="K396" s="1">
+        <v>46219.640625</v>
+      </c>
+      <c r="L396">
+        <v>0</v>
+      </c>
+      <c r="M396" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="397" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D397" t="s">
+        <v>37</v>
+      </c>
+      <c r="E397">
+        <v>2739</v>
+      </c>
+      <c r="F397" t="s">
+        <v>54</v>
+      </c>
+      <c r="H397" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I397" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J397" s="2">
+        <v>0</v>
+      </c>
+      <c r="K397" s="1">
+        <v>46219.641319444447</v>
+      </c>
+      <c r="L397">
+        <v>0</v>
+      </c>
+      <c r="M397" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="398" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D398" t="s">
+        <v>37</v>
+      </c>
+      <c r="E398">
+        <v>2736</v>
+      </c>
+      <c r="F398" t="s">
+        <v>55</v>
+      </c>
+      <c r="H398" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I398" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J398" s="2">
+        <v>6.7592592592592591E-3</v>
+      </c>
+      <c r="K398" s="1">
+        <v>46219.642013888886</v>
+      </c>
+      <c r="L398">
+        <v>0</v>
+      </c>
+      <c r="M398" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="399" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H399" s="2"/>
       <c r="I399" s="1"/>
       <c r="J399" s="2"/>
       <c r="K399" s="1"/>
     </row>
-    <row r="400" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="400" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H400" s="2"/>
       <c r="I400" s="1"/>
       <c r="J400" s="2"/>
@@ -13575,6 +14015,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -13670,6 +14111,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -13693,6 +14135,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -13956,6 +14399,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -13967,6 +14411,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -13978,6 +14423,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -14593,6 +15039,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -14717,6 +15164,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -14859,6 +15307,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -14888,6 +15337,7 @@
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -14958,6 +15408,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -14981,6 +15432,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -15045,6 +15497,7 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
@@ -15098,6 +15551,7 @@
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -15265,6 +15719,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -15276,6 +15731,7 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
@@ -15287,6 +15743,7 @@
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -15322,6 +15779,7 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
@@ -15471,6 +15929,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -15718,6 +16177,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -15776,6 +16236,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -15834,6 +16295,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -15845,6 +16307,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -15910,6 +16373,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -15945,6 +16409,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -16010,6 +16475,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -16056,6 +16522,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -16115,6 +16582,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -16173,6 +16641,7 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
@@ -16237,6 +16706,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -16319,6 +16789,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -16382,6 +16853,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -16397,6 +16869,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -16432,6 +16905,7 @@
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -16697,6 +17171,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -16980,6 +17455,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -16997,6 +17473,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -17020,6 +17497,7 @@
     <row r="1367" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1367" s="2"/>
       <c r="I1367" s="1"/>
+      <c r="J1367" s="2"/>
       <c r="K1367" s="1"/>
     </row>
     <row r="1368" spans="8:11" x14ac:dyDescent="0.3">
@@ -17037,6 +17515,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -17369,6 +17848,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -17457,6 +17937,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -17550,6 +18031,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -17609,11 +18091,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -17665,6 +18149,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -17706,6 +18191,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -17750,6 +18236,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -17796,11 +18283,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -17998,6 +18487,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -18027,6 +18517,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -18042,6 +18534,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -18101,6 +18594,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -18172,6 +18666,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -18213,6 +18708,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -18331,6 +18827,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -18395,6 +18892,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -18519,6 +19017,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -18745,6 +19244,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -18862,6 +19362,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -18945,6 +19446,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -19004,6 +19506,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -19027,6 +19530,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -19074,6 +19578,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -19133,6 +19638,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -19156,6 +19662,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -19173,6 +19680,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -19256,6 +19764,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -19447,6 +19956,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -47303,6 +47813,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -47310,6 +47821,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -47317,6 +47829,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -47332,6 +47845,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -47341,6 +47855,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -47348,9 +47863,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -47358,12 +47879,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -47371,12 +47895,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -47388,9 +47915,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -47405,6 +47934,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -47431,6 +47961,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -47441,7 +47972,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -47449,6 +47985,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -47460,6 +47997,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -47467,6 +48005,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -47481,13 +48020,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -47498,15 +48043,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -47522,6 +48070,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -47540,6 +48089,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -47551,6 +48101,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -47568,18 +48119,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -47608,6 +48164,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -47615,9 +48172,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -47640,12 +48199,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -47660,9 +48222,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -47678,12 +48242,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -47704,6 +48270,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -47715,9 +48282,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -47729,6 +48298,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -47768,9 +48338,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -47778,9 +48350,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -47791,6 +48365,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -47798,18 +48373,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -47817,6 +48400,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -47827,6 +48411,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -47853,15 +48438,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -47883,6 +48472,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -47890,9 +48480,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -47900,6 +48492,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -47911,6 +48504,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -47925,6 +48519,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -47934,6 +48532,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -47945,6 +48544,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -47955,10 +48555,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -47966,6 +48571,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -47980,6 +48586,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -48002,6 +48609,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -48021,25 +48629,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -48047,6 +48667,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -48054,15 +48675,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -48076,6 +48704,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -48094,9 +48723,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -48104,9 +48735,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -48114,6 +48747,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -48130,10 +48764,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\neal-pool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{310FD037-D6EE-4247-8876-D3AD2654253D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{148C8D81-2E0E-4BFA-B572-C88936BFBF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="63">
   <si>
     <t>Company Name</t>
   </si>
@@ -128,6 +128,9 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
+    <t>Dangers of Distracted Driving</t>
+  </si>
+  <si>
     <t>Camera Event Management (Onboarding)</t>
   </si>
   <si>
@@ -137,16 +140,16 @@
     <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
+    <t>Micro-Learn Safe Following Distance</t>
+  </si>
+  <si>
+    <t>Hazcom for CDL Drivers</t>
+  </si>
+  <si>
     <t>3 points of contact</t>
   </si>
   <si>
     <t>Vehicle &amp; Roadside Inspections CMV</t>
-  </si>
-  <si>
-    <t>Micro-Learn Safe Following Distance</t>
-  </si>
-  <si>
-    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>Safe RR Crossing</t>
@@ -598,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7404"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -613,50 +616,50 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2">
         <v>2246</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -674,18 +677,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3">
         <v>2245</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
@@ -703,15 +706,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>2738</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -732,15 +735,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5">
         <v>2740</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -761,15 +764,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6">
         <v>2735</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -790,15 +793,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7">
         <v>2742</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -819,15 +822,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>2737</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
@@ -848,7 +851,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2"/>
@@ -856,15 +859,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>2748</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
@@ -885,15 +888,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11">
         <v>2745</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
@@ -914,15 +917,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12">
         <v>2246</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
@@ -943,15 +946,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>2743</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
@@ -972,15 +975,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>2746</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
@@ -1001,15 +1004,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>2749</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
@@ -1030,15 +1033,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>2734</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
@@ -1061,13 +1064,13 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17">
         <v>2245</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
@@ -1090,13 +1093,13 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18">
         <v>2750</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
@@ -1119,13 +1122,13 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19">
         <v>2747</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
@@ -1148,13 +1151,13 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20">
         <v>2741</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
@@ -1177,13 +1180,13 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21">
         <v>2739</v>
       </c>
       <c r="D21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
@@ -1214,13 +1217,13 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C23">
         <v>2736</v>
       </c>
       <c r="D23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
@@ -1243,13 +1246,13 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C24">
         <v>2738</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s">
         <v>17</v>
@@ -1272,13 +1275,13 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C25">
         <v>2740</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
         <v>17</v>
@@ -1301,13 +1304,13 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C26">
         <v>2735</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s">
         <v>17</v>
@@ -1330,13 +1333,13 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27">
         <v>2742</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s">
         <v>17</v>
@@ -1359,13 +1362,13 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28">
         <v>2737</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>17</v>
@@ -1388,13 +1391,13 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C29">
         <v>2748</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
         <v>17</v>
@@ -1417,13 +1420,13 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>2745</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F30" t="s">
         <v>17</v>
@@ -1446,13 +1449,13 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31">
         <v>2246</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F31" t="s">
         <v>17</v>
@@ -1483,13 +1486,13 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C33">
         <v>2743</v>
       </c>
       <c r="D33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F33" t="s">
         <v>17</v>
@@ -1512,13 +1515,13 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C34">
         <v>2746</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F34" t="s">
         <v>17</v>
@@ -1541,13 +1544,13 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C35">
         <v>2749</v>
       </c>
       <c r="D35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F35" t="s">
         <v>17</v>
@@ -1570,13 +1573,13 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>2734</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F36" t="s">
         <v>17</v>
@@ -1599,13 +1602,13 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C37">
         <v>2245</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F37" t="s">
         <v>17</v>
@@ -1628,13 +1631,13 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C38">
         <v>2750</v>
       </c>
       <c r="D38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F38" t="s">
         <v>17</v>
@@ -1657,13 +1660,13 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C39">
         <v>2747</v>
       </c>
       <c r="D39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F39" t="s">
         <v>17</v>
@@ -1686,13 +1689,13 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C40">
         <v>2741</v>
       </c>
       <c r="D40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F40" t="s">
         <v>17</v>
@@ -1715,13 +1718,13 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C41">
         <v>2739</v>
       </c>
       <c r="D41" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F41" t="s">
         <v>17</v>
@@ -1744,13 +1747,13 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C42">
         <v>2736</v>
       </c>
       <c r="D42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F42" t="s">
         <v>17</v>
@@ -1773,13 +1776,13 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C43">
         <v>2738</v>
       </c>
       <c r="D43" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -1802,13 +1805,13 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C44">
         <v>2740</v>
       </c>
       <c r="D44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F44" t="s">
         <v>18</v>
@@ -1831,13 +1834,13 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C45">
         <v>2742</v>
       </c>
       <c r="D45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
@@ -1860,13 +1863,13 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C46">
         <v>2737</v>
       </c>
       <c r="D46" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F46" t="s">
         <v>18</v>
@@ -1889,13 +1892,13 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C47">
         <v>2748</v>
       </c>
       <c r="D47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F47" t="s">
         <v>18</v>
@@ -1918,13 +1921,13 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C48">
         <v>2745</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F48" t="s">
         <v>18</v>
@@ -1947,13 +1950,13 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C49">
         <v>2246</v>
       </c>
       <c r="D49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F49" t="s">
         <v>18</v>
@@ -1976,13 +1979,13 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C50">
         <v>2743</v>
       </c>
       <c r="D50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F50" t="s">
         <v>18</v>
@@ -2005,13 +2008,13 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C51">
         <v>2746</v>
       </c>
       <c r="D51" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F51" t="s">
         <v>18</v>
@@ -2034,13 +2037,13 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C52">
         <v>2749</v>
       </c>
       <c r="D52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F52" t="s">
         <v>18</v>
@@ -2063,13 +2066,13 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C53">
         <v>2734</v>
       </c>
       <c r="D53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F53" t="s">
         <v>18</v>
@@ -2092,13 +2095,13 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C54">
         <v>2245</v>
       </c>
       <c r="D54" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F54" t="s">
         <v>18</v>
@@ -2121,13 +2124,13 @@
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C55">
         <v>2750</v>
       </c>
       <c r="D55" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F55" t="s">
         <v>18</v>
@@ -2150,13 +2153,13 @@
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C56">
         <v>2747</v>
       </c>
       <c r="D56" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F56" t="s">
         <v>18</v>
@@ -2179,13 +2182,13 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C57">
         <v>2741</v>
       </c>
       <c r="D57" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F57" t="s">
         <v>18</v>
@@ -2208,13 +2211,13 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C58">
         <v>2739</v>
       </c>
       <c r="D58" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F58" t="s">
         <v>18</v>
@@ -2237,13 +2240,13 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C59">
         <v>2736</v>
       </c>
       <c r="D59" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F59" t="s">
         <v>18</v>
@@ -2266,16 +2269,16 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C60">
         <v>2738</v>
       </c>
       <c r="D60" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G60" t="s">
         <v>12</v>
@@ -2303,16 +2306,16 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C62">
         <v>2740</v>
       </c>
       <c r="D62" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F62" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G62" t="s">
         <v>13</v>
@@ -2332,16 +2335,16 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C63">
         <v>2742</v>
       </c>
       <c r="D63" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F63" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G63" t="s">
         <v>10</v>
@@ -2361,16 +2364,16 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C64">
         <v>2737</v>
       </c>
       <c r="D64" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F64" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G64" t="s">
         <v>10</v>
@@ -2390,16 +2393,16 @@
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C65">
         <v>2748</v>
       </c>
       <c r="D65" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F65" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G65" t="s">
         <v>10</v>
@@ -2419,16 +2422,16 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C66">
         <v>2745</v>
       </c>
       <c r="D66" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F66" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G66" t="s">
         <v>10</v>
@@ -2448,16 +2451,16 @@
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C67">
         <v>2246</v>
       </c>
       <c r="D67" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G67" t="s">
         <v>10</v>
@@ -2477,16 +2480,16 @@
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C68">
         <v>2743</v>
       </c>
       <c r="D68" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F68" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G68" t="s">
         <v>10</v>
@@ -2506,16 +2509,16 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C69">
         <v>2746</v>
       </c>
       <c r="D69" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G69" t="s">
         <v>13</v>
@@ -2535,16 +2538,16 @@
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C70">
         <v>2749</v>
       </c>
       <c r="D70" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F70" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G70" t="s">
         <v>10</v>
@@ -2564,16 +2567,16 @@
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C71">
         <v>2734</v>
       </c>
       <c r="D71" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F71" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G71" t="s">
         <v>10</v>
@@ -2593,16 +2596,16 @@
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C72">
         <v>2245</v>
       </c>
       <c r="D72" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F72" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G72" t="s">
         <v>10</v>
@@ -2622,16 +2625,16 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C73">
         <v>2750</v>
       </c>
       <c r="D73" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F73" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G73" t="s">
         <v>10</v>
@@ -2651,16 +2654,16 @@
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C74">
         <v>2747</v>
       </c>
       <c r="D74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F74" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G74" t="s">
         <v>10</v>
@@ -2680,16 +2683,16 @@
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C75">
         <v>2741</v>
       </c>
       <c r="D75" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F75" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G75" t="s">
         <v>13</v>
@@ -2709,16 +2712,16 @@
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C76">
         <v>2739</v>
       </c>
       <c r="D76" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F76" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G76" t="s">
         <v>10</v>
@@ -2738,16 +2741,16 @@
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C77">
         <v>2736</v>
       </c>
       <c r="D77" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F77" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G77" t="s">
         <v>10</v>
@@ -2767,16 +2770,16 @@
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C78">
         <v>2738</v>
       </c>
       <c r="D78" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F78" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G78" t="s">
         <v>13</v>
@@ -2796,16 +2799,16 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C79">
         <v>2740</v>
       </c>
       <c r="D79" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F79" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G79" t="s">
         <v>13</v>
@@ -2825,16 +2828,16 @@
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C80">
         <v>2742</v>
       </c>
       <c r="D80" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F80" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G80" t="s">
         <v>10</v>
@@ -2854,16 +2857,16 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C81">
         <v>2737</v>
       </c>
       <c r="D81" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F81" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G81" t="s">
         <v>13</v>
@@ -2883,16 +2886,16 @@
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C82">
         <v>2748</v>
       </c>
       <c r="D82" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F82" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G82" t="s">
         <v>10</v>
@@ -2912,16 +2915,16 @@
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C83">
         <v>2745</v>
       </c>
       <c r="D83" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F83" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G83" t="s">
         <v>10</v>
@@ -2941,16 +2944,16 @@
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C84">
         <v>2246</v>
       </c>
       <c r="D84" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F84" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G84" t="s">
         <v>10</v>
@@ -2970,16 +2973,16 @@
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C85">
         <v>2743</v>
       </c>
       <c r="D85" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F85" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G85" t="s">
         <v>10</v>
@@ -2999,16 +3002,16 @@
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C86">
         <v>2746</v>
       </c>
       <c r="D86" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F86" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G86" t="s">
         <v>13</v>
@@ -3028,16 +3031,16 @@
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C87">
         <v>2749</v>
       </c>
       <c r="D87" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F87" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G87" t="s">
         <v>10</v>
@@ -3057,16 +3060,16 @@
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C88">
         <v>2734</v>
       </c>
       <c r="D88" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F88" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G88" t="s">
         <v>13</v>
@@ -3086,16 +3089,16 @@
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C89">
         <v>2245</v>
       </c>
       <c r="D89" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F89" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G89" t="s">
         <v>10</v>
@@ -3115,16 +3118,16 @@
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C90">
         <v>2750</v>
       </c>
       <c r="D90" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F90" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G90" t="s">
         <v>10</v>
@@ -3144,16 +3147,16 @@
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C91">
         <v>2747</v>
       </c>
       <c r="D91" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F91" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G91" t="s">
         <v>13</v>
@@ -3173,16 +3176,16 @@
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C92">
         <v>2741</v>
       </c>
       <c r="D92" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F92" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G92" t="s">
         <v>10</v>
@@ -3202,16 +3205,16 @@
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C93">
         <v>2739</v>
       </c>
       <c r="D93" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F93" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G93" t="s">
         <v>10</v>
@@ -3231,16 +3234,16 @@
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C94">
         <v>2736</v>
       </c>
       <c r="D94" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F94" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G94" t="s">
         <v>12</v>
@@ -3268,13 +3271,13 @@
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C96">
         <v>2738</v>
       </c>
       <c r="D96" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F96" t="s">
         <v>22</v>
@@ -3297,13 +3300,13 @@
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C97">
         <v>2740</v>
       </c>
       <c r="D97" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F97" t="s">
         <v>22</v>
@@ -3326,13 +3329,13 @@
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C98">
         <v>2742</v>
       </c>
       <c r="D98" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F98" t="s">
         <v>22</v>
@@ -3355,13 +3358,13 @@
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C99">
         <v>2737</v>
       </c>
       <c r="D99" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F99" t="s">
         <v>22</v>
@@ -3384,13 +3387,13 @@
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C100">
         <v>2748</v>
       </c>
       <c r="D100" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F100" t="s">
         <v>22</v>
@@ -3413,13 +3416,13 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C101">
         <v>2745</v>
       </c>
       <c r="D101" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F101" t="s">
         <v>22</v>
@@ -3442,13 +3445,13 @@
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C102">
         <v>2246</v>
       </c>
       <c r="D102" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F102" t="s">
         <v>22</v>
@@ -3471,13 +3474,13 @@
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C103">
         <v>2743</v>
       </c>
       <c r="D103" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F103" t="s">
         <v>22</v>
@@ -3500,13 +3503,13 @@
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C104">
         <v>2749</v>
       </c>
       <c r="D104" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F104" t="s">
         <v>22</v>
@@ -3529,13 +3532,13 @@
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C105">
         <v>2734</v>
       </c>
       <c r="D105" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F105" t="s">
         <v>22</v>
@@ -3566,13 +3569,13 @@
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C107">
         <v>2245</v>
       </c>
       <c r="D107" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F107" t="s">
         <v>22</v>
@@ -3595,13 +3598,13 @@
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C108">
         <v>2750</v>
       </c>
       <c r="D108" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F108" t="s">
         <v>22</v>
@@ -3624,13 +3627,13 @@
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C109">
         <v>2747</v>
       </c>
       <c r="D109" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F109" t="s">
         <v>22</v>
@@ -3653,13 +3656,13 @@
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C110">
         <v>2741</v>
       </c>
       <c r="D110" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F110" t="s">
         <v>22</v>
@@ -3682,13 +3685,13 @@
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C111">
         <v>2739</v>
       </c>
       <c r="D111" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F111" t="s">
         <v>22</v>
@@ -3711,13 +3714,13 @@
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C112">
         <v>2736</v>
       </c>
       <c r="D112" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F112" t="s">
         <v>22</v>
@@ -3740,13 +3743,13 @@
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C113">
         <v>2738</v>
       </c>
       <c r="D113" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F113" t="s">
         <v>24</v>
@@ -3769,13 +3772,13 @@
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C114">
         <v>2740</v>
       </c>
       <c r="D114" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F114" t="s">
         <v>24</v>
@@ -3798,13 +3801,13 @@
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C115">
         <v>2742</v>
       </c>
       <c r="D115" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F115" t="s">
         <v>24</v>
@@ -3827,13 +3830,13 @@
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C116">
         <v>2737</v>
       </c>
       <c r="D116" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F116" t="s">
         <v>24</v>
@@ -3856,13 +3859,13 @@
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C117">
         <v>2748</v>
       </c>
       <c r="D117" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F117" t="s">
         <v>24</v>
@@ -3885,13 +3888,13 @@
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C118">
         <v>2745</v>
       </c>
       <c r="D118" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F118" t="s">
         <v>24</v>
@@ -3914,13 +3917,13 @@
     </row>
     <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C119">
         <v>2246</v>
       </c>
       <c r="D119" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F119" t="s">
         <v>24</v>
@@ -3943,13 +3946,13 @@
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C120">
         <v>2749</v>
       </c>
       <c r="D120" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F120" t="s">
         <v>24</v>
@@ -3972,13 +3975,13 @@
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C121">
         <v>2245</v>
       </c>
       <c r="D121" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F121" t="s">
         <v>24</v>
@@ -4001,13 +4004,13 @@
     </row>
     <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C122">
         <v>2750</v>
       </c>
       <c r="D122" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F122" t="s">
         <v>24</v>
@@ -4030,13 +4033,13 @@
     </row>
     <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C123">
         <v>2747</v>
       </c>
       <c r="D123" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F123" t="s">
         <v>24</v>
@@ -4059,13 +4062,13 @@
     </row>
     <row r="124" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C124">
         <v>2741</v>
       </c>
       <c r="D124" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F124" t="s">
         <v>24</v>
@@ -4088,13 +4091,13 @@
     </row>
     <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C125">
         <v>2739</v>
       </c>
       <c r="D125" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F125" t="s">
         <v>24</v>
@@ -4117,13 +4120,13 @@
     </row>
     <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C126">
         <v>2736</v>
       </c>
       <c r="D126" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F126" t="s">
         <v>24</v>
@@ -4146,16 +4149,16 @@
     </row>
     <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C127">
         <v>2738</v>
       </c>
       <c r="D127" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F127" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G127" t="s">
         <v>13</v>
@@ -4175,16 +4178,16 @@
     </row>
     <row r="128" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C128">
         <v>2740</v>
       </c>
       <c r="D128" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F128" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G128" t="s">
         <v>13</v>
@@ -4204,16 +4207,16 @@
     </row>
     <row r="129" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C129">
         <v>2742</v>
       </c>
       <c r="D129" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F129" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G129" t="s">
         <v>10</v>
@@ -4233,16 +4236,16 @@
     </row>
     <row r="130" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C130">
         <v>2737</v>
       </c>
       <c r="D130" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F130" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G130" t="s">
         <v>13</v>
@@ -4262,16 +4265,16 @@
     </row>
     <row r="131" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C131">
         <v>2748</v>
       </c>
       <c r="D131" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F131" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G131" t="s">
         <v>10</v>
@@ -4291,16 +4294,16 @@
     </row>
     <row r="132" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C132">
         <v>2745</v>
       </c>
       <c r="D132" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F132" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G132" t="s">
         <v>10</v>
@@ -4320,16 +4323,16 @@
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C133">
         <v>2246</v>
       </c>
       <c r="D133" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F133" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G133" t="s">
         <v>10</v>
@@ -4349,16 +4352,16 @@
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C134">
         <v>2749</v>
       </c>
       <c r="D134" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F134" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G134" t="s">
         <v>10</v>
@@ -4378,16 +4381,16 @@
     </row>
     <row r="135" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C135">
         <v>2245</v>
       </c>
       <c r="D135" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F135" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G135" t="s">
         <v>10</v>
@@ -4407,16 +4410,16 @@
     </row>
     <row r="136" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C136">
         <v>2750</v>
       </c>
       <c r="D136" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F136" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G136" t="s">
         <v>10</v>
@@ -4436,16 +4439,16 @@
     </row>
     <row r="137" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C137">
         <v>2747</v>
       </c>
       <c r="D137" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F137" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G137" t="s">
         <v>13</v>
@@ -4465,16 +4468,16 @@
     </row>
     <row r="138" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C138">
         <v>2741</v>
       </c>
       <c r="D138" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F138" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G138" t="s">
         <v>13</v>
@@ -4494,16 +4497,16 @@
     </row>
     <row r="139" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C139">
         <v>2739</v>
       </c>
       <c r="D139" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F139" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G139" t="s">
         <v>13</v>
@@ -4523,16 +4526,16 @@
     </row>
     <row r="140" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C140">
         <v>2736</v>
       </c>
       <c r="D140" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F140" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G140" t="s">
         <v>10</v>
@@ -4552,13 +4555,13 @@
     </row>
     <row r="141" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C141">
         <v>2738</v>
       </c>
       <c r="D141" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F141" t="s">
         <v>20</v>
@@ -4581,13 +4584,13 @@
     </row>
     <row r="142" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C142">
         <v>2740</v>
       </c>
       <c r="D142" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F142" t="s">
         <v>20</v>
@@ -4610,13 +4613,13 @@
     </row>
     <row r="143" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C143">
         <v>2742</v>
       </c>
       <c r="D143" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F143" t="s">
         <v>20</v>
@@ -4639,13 +4642,13 @@
     </row>
     <row r="144" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C144">
         <v>2737</v>
       </c>
       <c r="D144" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F144" t="s">
         <v>20</v>
@@ -4668,13 +4671,13 @@
     </row>
     <row r="145" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C145">
         <v>2748</v>
       </c>
       <c r="D145" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F145" t="s">
         <v>20</v>
@@ -4697,13 +4700,13 @@
     </row>
     <row r="146" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C146">
         <v>2745</v>
       </c>
       <c r="D146" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F146" t="s">
         <v>20</v>
@@ -4726,13 +4729,13 @@
     </row>
     <row r="147" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C147">
         <v>2246</v>
       </c>
       <c r="D147" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F147" t="s">
         <v>20</v>
@@ -4755,13 +4758,13 @@
     </row>
     <row r="148" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C148">
         <v>2749</v>
       </c>
       <c r="D148" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F148" t="s">
         <v>20</v>
@@ -4784,13 +4787,13 @@
     </row>
     <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C149">
         <v>2245</v>
       </c>
       <c r="D149" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F149" t="s">
         <v>20</v>
@@ -4813,13 +4816,13 @@
     </row>
     <row r="150" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C150">
         <v>2750</v>
       </c>
       <c r="D150" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F150" t="s">
         <v>20</v>
@@ -4842,13 +4845,13 @@
     </row>
     <row r="151" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C151">
         <v>2747</v>
       </c>
       <c r="D151" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F151" t="s">
         <v>20</v>
@@ -4871,13 +4874,13 @@
     </row>
     <row r="152" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C152">
         <v>2741</v>
       </c>
       <c r="D152" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F152" t="s">
         <v>20</v>
@@ -4900,13 +4903,13 @@
     </row>
     <row r="153" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C153">
         <v>2739</v>
       </c>
       <c r="D153" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F153" t="s">
         <v>20</v>
@@ -4929,13 +4932,13 @@
     </row>
     <row r="154" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C154">
         <v>2736</v>
       </c>
       <c r="D154" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F154" t="s">
         <v>20</v>
@@ -4958,13 +4961,13 @@
     </row>
     <row r="155" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C155">
         <v>2738</v>
       </c>
       <c r="D155" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F155" t="s">
         <v>16</v>
@@ -4987,13 +4990,13 @@
     </row>
     <row r="156" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C156">
         <v>2740</v>
       </c>
       <c r="D156" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F156" t="s">
         <v>16</v>
@@ -5016,13 +5019,13 @@
     </row>
     <row r="157" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C157">
         <v>2742</v>
       </c>
       <c r="D157" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F157" t="s">
         <v>16</v>
@@ -5045,13 +5048,13 @@
     </row>
     <row r="158" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C158">
         <v>2737</v>
       </c>
       <c r="D158" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F158" t="s">
         <v>16</v>
@@ -5074,13 +5077,13 @@
     </row>
     <row r="159" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C159">
         <v>2748</v>
       </c>
       <c r="D159" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F159" t="s">
         <v>16</v>
@@ -5103,13 +5106,13 @@
     </row>
     <row r="160" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C160">
         <v>2745</v>
       </c>
       <c r="D160" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F160" t="s">
         <v>16</v>
@@ -5132,13 +5135,13 @@
     </row>
     <row r="161" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C161">
         <v>2246</v>
       </c>
       <c r="D161" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F161" t="s">
         <v>16</v>
@@ -5161,13 +5164,13 @@
     </row>
     <row r="162" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C162">
         <v>2749</v>
       </c>
       <c r="D162" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F162" t="s">
         <v>16</v>
@@ -5190,13 +5193,13 @@
     </row>
     <row r="163" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C163">
         <v>2245</v>
       </c>
       <c r="D163" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F163" t="s">
         <v>16</v>
@@ -5219,13 +5222,13 @@
     </row>
     <row r="164" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C164">
         <v>2750</v>
       </c>
       <c r="D164" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F164" t="s">
         <v>16</v>
@@ -5248,13 +5251,13 @@
     </row>
     <row r="165" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B165" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C165">
         <v>2747</v>
       </c>
       <c r="D165" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F165" t="s">
         <v>16</v>
@@ -5277,13 +5280,13 @@
     </row>
     <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C166">
         <v>2741</v>
       </c>
       <c r="D166" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F166" t="s">
         <v>16</v>
@@ -5306,13 +5309,13 @@
     </row>
     <row r="167" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C167">
         <v>2739</v>
       </c>
       <c r="D167" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F167" t="s">
         <v>16</v>
@@ -5343,13 +5346,13 @@
     </row>
     <row r="169" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C169">
         <v>2736</v>
       </c>
       <c r="D169" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F169" t="s">
         <v>16</v>
@@ -5372,16 +5375,16 @@
     </row>
     <row r="170" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B170" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C170">
         <v>2738</v>
       </c>
       <c r="D170" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F170" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G170" t="s">
         <v>14</v>
@@ -5409,16 +5412,16 @@
     </row>
     <row r="172" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B172" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C172">
         <v>3832</v>
       </c>
       <c r="D172" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F172" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G172" t="s">
         <v>10</v>
@@ -5438,16 +5441,16 @@
     </row>
     <row r="173" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B173" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C173">
         <v>2740</v>
       </c>
       <c r="D173" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F173" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G173" t="s">
         <v>13</v>
@@ -5467,16 +5470,16 @@
     </row>
     <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C174">
         <v>3885</v>
       </c>
       <c r="D174" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F174" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G174" t="s">
         <v>10</v>
@@ -5496,16 +5499,16 @@
     </row>
     <row r="175" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C175">
         <v>2742</v>
       </c>
       <c r="D175" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F175" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G175" t="s">
         <v>10</v>
@@ -5525,16 +5528,16 @@
     </row>
     <row r="176" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C176">
         <v>2737</v>
       </c>
       <c r="D176" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F176" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G176" t="s">
         <v>12</v>
@@ -5562,16 +5565,16 @@
     </row>
     <row r="178" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B178" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C178">
         <v>2748</v>
       </c>
       <c r="D178" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F178" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G178" t="s">
         <v>10</v>
@@ -5591,16 +5594,16 @@
     </row>
     <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C179">
         <v>2745</v>
       </c>
       <c r="D179" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F179" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G179" t="s">
         <v>10</v>
@@ -5620,16 +5623,16 @@
     </row>
     <row r="180" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B180" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C180">
         <v>2246</v>
       </c>
       <c r="D180" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F180" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G180" t="s">
         <v>10</v>
@@ -5649,16 +5652,16 @@
     </row>
     <row r="181" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C181">
         <v>2749</v>
       </c>
       <c r="D181" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F181" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G181" t="s">
         <v>10</v>
@@ -5678,16 +5681,16 @@
     </row>
     <row r="182" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C182">
         <v>2245</v>
       </c>
       <c r="D182" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F182" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G182" t="s">
         <v>10</v>
@@ -5707,16 +5710,16 @@
     </row>
     <row r="183" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C183">
         <v>2750</v>
       </c>
       <c r="D183" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F183" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G183" t="s">
         <v>10</v>
@@ -5736,16 +5739,16 @@
     </row>
     <row r="184" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C184">
         <v>2747</v>
       </c>
       <c r="D184" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F184" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G184" t="s">
         <v>10</v>
@@ -5765,16 +5768,16 @@
     </row>
     <row r="185" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C185">
         <v>2741</v>
       </c>
       <c r="D185" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F185" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G185" t="s">
         <v>13</v>
@@ -5794,16 +5797,16 @@
     </row>
     <row r="186" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B186" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C186">
         <v>2739</v>
       </c>
       <c r="D186" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F186" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G186" t="s">
         <v>13</v>
@@ -5823,16 +5826,16 @@
     </row>
     <row r="187" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B187" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C187">
         <v>2736</v>
       </c>
       <c r="D187" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F187" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G187" t="s">
         <v>10</v>
@@ -5852,16 +5855,16 @@
     </row>
     <row r="188" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C188">
         <v>2738</v>
       </c>
       <c r="D188" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F188" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G188" t="s">
         <v>13</v>
@@ -5881,16 +5884,16 @@
     </row>
     <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C189">
         <v>3832</v>
       </c>
       <c r="D189" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F189" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G189" t="s">
         <v>10</v>
@@ -5910,16 +5913,16 @@
     </row>
     <row r="190" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B190" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C190">
         <v>2740</v>
       </c>
       <c r="D190" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F190" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G190" t="s">
         <v>13</v>
@@ -5939,16 +5942,16 @@
     </row>
     <row r="191" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B191" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C191">
         <v>3885</v>
       </c>
       <c r="D191" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F191" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G191" t="s">
         <v>10</v>
@@ -5968,16 +5971,16 @@
     </row>
     <row r="192" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B192" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C192">
         <v>2742</v>
       </c>
       <c r="D192" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F192" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G192" t="s">
         <v>10</v>
@@ -5997,16 +6000,16 @@
     </row>
     <row r="193" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B193" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C193">
         <v>2737</v>
       </c>
       <c r="D193" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F193" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G193" t="s">
         <v>13</v>
@@ -6026,16 +6029,16 @@
     </row>
     <row r="194" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B194" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C194">
         <v>2748</v>
       </c>
       <c r="D194" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F194" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G194" t="s">
         <v>10</v>
@@ -6055,16 +6058,16 @@
     </row>
     <row r="195" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B195" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C195">
         <v>2745</v>
       </c>
       <c r="D195" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F195" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G195" t="s">
         <v>13</v>
@@ -6084,16 +6087,16 @@
     </row>
     <row r="196" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C196">
         <v>2246</v>
       </c>
       <c r="D196" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F196" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G196" t="s">
         <v>10</v>
@@ -6113,16 +6116,16 @@
     </row>
     <row r="197" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C197">
         <v>2743</v>
       </c>
       <c r="D197" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F197" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G197" t="s">
         <v>13</v>
@@ -6142,16 +6145,16 @@
     </row>
     <row r="198" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C198">
         <v>2749</v>
       </c>
       <c r="D198" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F198" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G198" t="s">
         <v>10</v>
@@ -6171,16 +6174,16 @@
     </row>
     <row r="199" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C199">
         <v>2245</v>
       </c>
       <c r="D199" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F199" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G199" t="s">
         <v>10</v>
@@ -6200,16 +6203,16 @@
     </row>
     <row r="200" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C200">
         <v>2750</v>
       </c>
       <c r="D200" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F200" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G200" t="s">
         <v>10</v>
@@ -6229,16 +6232,16 @@
     </row>
     <row r="201" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C201">
         <v>2747</v>
       </c>
       <c r="D201" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F201" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G201" t="s">
         <v>13</v>
@@ -6258,16 +6261,16 @@
     </row>
     <row r="202" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C202">
         <v>2741</v>
       </c>
       <c r="D202" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F202" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G202" t="s">
         <v>13</v>
@@ -6287,16 +6290,16 @@
     </row>
     <row r="203" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B203" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C203">
         <v>2739</v>
       </c>
       <c r="D203" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F203" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G203" t="s">
         <v>13</v>
@@ -6316,16 +6319,16 @@
     </row>
     <row r="204" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B204" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C204">
         <v>2736</v>
       </c>
       <c r="D204" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F204" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G204" t="s">
         <v>10</v>
@@ -6345,16 +6348,16 @@
     </row>
     <row r="205" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B205" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C205">
         <v>2738</v>
       </c>
       <c r="D205" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F205" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G205" t="s">
         <v>10</v>
@@ -6374,16 +6377,16 @@
     </row>
     <row r="206" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B206" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C206">
         <v>3832</v>
       </c>
       <c r="D206" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F206" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G206" t="s">
         <v>10</v>
@@ -6403,16 +6406,16 @@
     </row>
     <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C207">
         <v>2740</v>
       </c>
       <c r="D207" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F207" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G207" t="s">
         <v>13</v>
@@ -6432,16 +6435,16 @@
     </row>
     <row r="208" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B208" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C208">
         <v>3885</v>
       </c>
       <c r="D208" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F208" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G208" t="s">
         <v>10</v>
@@ -6461,16 +6464,16 @@
     </row>
     <row r="209" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B209" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C209">
         <v>2742</v>
       </c>
       <c r="D209" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F209" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G209" t="s">
         <v>10</v>
@@ -6490,16 +6493,16 @@
     </row>
     <row r="210" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B210" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C210">
         <v>2737</v>
       </c>
       <c r="D210" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F210" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G210" t="s">
         <v>10</v>
@@ -6519,16 +6522,16 @@
     </row>
     <row r="211" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B211" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C211">
         <v>2748</v>
       </c>
       <c r="D211" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F211" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G211" t="s">
         <v>10</v>
@@ -6548,16 +6551,16 @@
     </row>
     <row r="212" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B212" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C212">
         <v>2745</v>
       </c>
       <c r="D212" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F212" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G212" t="s">
         <v>10</v>
@@ -6577,16 +6580,16 @@
     </row>
     <row r="213" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B213" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C213">
         <v>2246</v>
       </c>
       <c r="D213" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F213" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G213" t="s">
         <v>10</v>
@@ -6606,16 +6609,16 @@
     </row>
     <row r="214" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B214" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C214">
         <v>2743</v>
       </c>
       <c r="D214" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F214" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G214" t="s">
         <v>10</v>
@@ -6635,16 +6638,16 @@
     </row>
     <row r="215" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B215" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C215">
         <v>2749</v>
       </c>
       <c r="D215" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F215" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G215" t="s">
         <v>10</v>
@@ -6664,16 +6667,16 @@
     </row>
     <row r="216" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B216" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C216">
         <v>4755</v>
       </c>
       <c r="D216" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F216" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G216" t="s">
         <v>10</v>
@@ -6693,16 +6696,16 @@
     </row>
     <row r="217" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B217" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C217">
         <v>2245</v>
       </c>
       <c r="D217" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F217" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G217" t="s">
         <v>10</v>
@@ -6722,16 +6725,16 @@
     </row>
     <row r="218" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B218" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C218">
         <v>2750</v>
       </c>
       <c r="D218" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F218" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G218" t="s">
         <v>10</v>
@@ -6751,16 +6754,16 @@
     </row>
     <row r="219" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B219" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C219">
         <v>2747</v>
       </c>
       <c r="D219" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F219" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G219" t="s">
         <v>10</v>
@@ -6780,16 +6783,16 @@
     </row>
     <row r="220" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B220" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C220">
         <v>2741</v>
       </c>
       <c r="D220" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F220" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G220" t="s">
         <v>10</v>
@@ -6809,16 +6812,16 @@
     </row>
     <row r="221" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B221" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C221">
         <v>2739</v>
       </c>
       <c r="D221" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F221" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G221" t="s">
         <v>10</v>
@@ -6838,16 +6841,16 @@
     </row>
     <row r="222" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B222" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C222">
         <v>2736</v>
       </c>
       <c r="D222" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F222" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G222" t="s">
         <v>10</v>
@@ -6867,13 +6870,13 @@
     </row>
     <row r="223" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B223" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C223">
         <v>2738</v>
       </c>
       <c r="D223" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F223" t="s">
         <v>17</v>
@@ -6896,13 +6899,13 @@
     </row>
     <row r="224" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B224" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C224">
         <v>3832</v>
       </c>
       <c r="D224" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F224" t="s">
         <v>17</v>
@@ -6925,13 +6928,13 @@
     </row>
     <row r="225" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B225" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C225">
         <v>2740</v>
       </c>
       <c r="D225" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F225" t="s">
         <v>17</v>
@@ -6962,13 +6965,13 @@
     </row>
     <row r="227" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B227" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C227">
         <v>3885</v>
       </c>
       <c r="D227" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F227" t="s">
         <v>17</v>
@@ -6991,13 +6994,13 @@
     </row>
     <row r="228" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B228" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C228">
         <v>2742</v>
       </c>
       <c r="D228" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F228" t="s">
         <v>17</v>
@@ -7020,13 +7023,13 @@
     </row>
     <row r="229" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B229" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C229">
         <v>2737</v>
       </c>
       <c r="D229" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F229" t="s">
         <v>17</v>
@@ -7049,13 +7052,13 @@
     </row>
     <row r="230" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B230" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C230">
         <v>2748</v>
       </c>
       <c r="D230" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F230" t="s">
         <v>17</v>
@@ -7078,13 +7081,13 @@
     </row>
     <row r="231" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C231">
         <v>2745</v>
       </c>
       <c r="D231" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F231" t="s">
         <v>17</v>
@@ -7107,13 +7110,13 @@
     </row>
     <row r="232" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B232" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C232">
         <v>2246</v>
       </c>
       <c r="D232" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F232" t="s">
         <v>17</v>
@@ -7136,13 +7139,13 @@
     </row>
     <row r="233" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B233" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C233">
         <v>2743</v>
       </c>
       <c r="D233" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F233" t="s">
         <v>17</v>
@@ -7165,13 +7168,13 @@
     </row>
     <row r="234" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B234" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C234">
         <v>2749</v>
       </c>
       <c r="D234" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F234" t="s">
         <v>17</v>
@@ -7194,13 +7197,13 @@
     </row>
     <row r="235" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B235" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C235">
         <v>4755</v>
       </c>
       <c r="D235" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F235" t="s">
         <v>17</v>
@@ -7223,13 +7226,13 @@
     </row>
     <row r="236" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B236" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C236">
         <v>2245</v>
       </c>
       <c r="D236" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F236" t="s">
         <v>17</v>
@@ -7252,13 +7255,13 @@
     </row>
     <row r="237" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B237" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C237">
         <v>2750</v>
       </c>
       <c r="D237" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F237" t="s">
         <v>17</v>
@@ -7281,13 +7284,13 @@
     </row>
     <row r="238" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B238" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C238">
         <v>2747</v>
       </c>
       <c r="D238" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F238" t="s">
         <v>17</v>
@@ -7310,13 +7313,13 @@
     </row>
     <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C239">
         <v>2741</v>
       </c>
       <c r="D239" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F239" t="s">
         <v>17</v>
@@ -7339,13 +7342,13 @@
     </row>
     <row r="240" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B240" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C240">
         <v>2739</v>
       </c>
       <c r="D240" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F240" t="s">
         <v>17</v>
@@ -7368,13 +7371,13 @@
     </row>
     <row r="241" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B241" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C241">
         <v>2736</v>
       </c>
       <c r="D241" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F241" t="s">
         <v>17</v>
@@ -7397,13 +7400,13 @@
     </row>
     <row r="242" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B242" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C242">
         <v>2738</v>
       </c>
       <c r="D242" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F242" t="s">
         <v>18</v>
@@ -7426,13 +7429,13 @@
     </row>
     <row r="243" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B243" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C243">
         <v>3832</v>
       </c>
       <c r="D243" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F243" t="s">
         <v>18</v>
@@ -7455,13 +7458,13 @@
     </row>
     <row r="244" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B244" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C244">
         <v>2740</v>
       </c>
       <c r="D244" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F244" t="s">
         <v>18</v>
@@ -7484,13 +7487,13 @@
     </row>
     <row r="245" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B245" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C245">
         <v>3885</v>
       </c>
       <c r="D245" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F245" t="s">
         <v>18</v>
@@ -7513,13 +7516,13 @@
     </row>
     <row r="246" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B246" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C246">
         <v>2742</v>
       </c>
       <c r="D246" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F246" t="s">
         <v>18</v>
@@ -7550,13 +7553,13 @@
     </row>
     <row r="248" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B248" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C248">
         <v>2737</v>
       </c>
       <c r="D248" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F248" t="s">
         <v>18</v>
@@ -7579,13 +7582,13 @@
     </row>
     <row r="249" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B249" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C249">
         <v>2748</v>
       </c>
       <c r="D249" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F249" t="s">
         <v>18</v>
@@ -7608,13 +7611,13 @@
     </row>
     <row r="250" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B250" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C250">
         <v>2745</v>
       </c>
       <c r="D250" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F250" t="s">
         <v>18</v>
@@ -7637,13 +7640,13 @@
     </row>
     <row r="251" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B251" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C251">
         <v>2246</v>
       </c>
       <c r="D251" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F251" t="s">
         <v>18</v>
@@ -7666,13 +7669,13 @@
     </row>
     <row r="252" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B252" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C252">
         <v>2749</v>
       </c>
       <c r="D252" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F252" t="s">
         <v>18</v>
@@ -7695,13 +7698,13 @@
     </row>
     <row r="253" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B253" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C253">
         <v>5032</v>
       </c>
       <c r="D253" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F253" t="s">
         <v>18</v>
@@ -7724,13 +7727,13 @@
     </row>
     <row r="254" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B254" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C254">
         <v>4755</v>
       </c>
       <c r="D254" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F254" t="s">
         <v>18</v>
@@ -7761,13 +7764,13 @@
     </row>
     <row r="256" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B256" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C256">
         <v>2245</v>
       </c>
       <c r="D256" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F256" t="s">
         <v>18</v>
@@ -7790,13 +7793,13 @@
     </row>
     <row r="257" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B257" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C257">
         <v>2750</v>
       </c>
       <c r="D257" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F257" t="s">
         <v>18</v>
@@ -7819,13 +7822,13 @@
     </row>
     <row r="258" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B258" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C258">
         <v>2747</v>
       </c>
       <c r="D258" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F258" t="s">
         <v>18</v>
@@ -7848,13 +7851,13 @@
     </row>
     <row r="259" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B259" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C259">
         <v>2741</v>
       </c>
       <c r="D259" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F259" t="s">
         <v>18</v>
@@ -7885,13 +7888,13 @@
     </row>
     <row r="261" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B261" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C261">
         <v>2739</v>
       </c>
       <c r="D261" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F261" t="s">
         <v>18</v>
@@ -7922,13 +7925,13 @@
     </row>
     <row r="263" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B263" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C263">
         <v>2736</v>
       </c>
       <c r="D263" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F263" t="s">
         <v>18</v>
@@ -7951,13 +7954,13 @@
     </row>
     <row r="264" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B264" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C264">
         <v>2738</v>
       </c>
       <c r="D264" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F264" t="s">
         <v>25</v>
@@ -7980,13 +7983,13 @@
     </row>
     <row r="265" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B265" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C265">
         <v>3832</v>
       </c>
       <c r="D265" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F265" t="s">
         <v>25</v>
@@ -8009,13 +8012,13 @@
     </row>
     <row r="266" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B266" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C266">
         <v>2740</v>
       </c>
       <c r="D266" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F266" t="s">
         <v>25</v>
@@ -8038,13 +8041,13 @@
     </row>
     <row r="267" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B267" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C267">
         <v>3885</v>
       </c>
       <c r="D267" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F267" t="s">
         <v>25</v>
@@ -8067,13 +8070,13 @@
     </row>
     <row r="268" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B268" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C268">
         <v>2742</v>
       </c>
       <c r="D268" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F268" t="s">
         <v>25</v>
@@ -8096,13 +8099,13 @@
     </row>
     <row r="269" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B269" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C269">
         <v>2737</v>
       </c>
       <c r="D269" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F269" t="s">
         <v>25</v>
@@ -8125,13 +8128,13 @@
     </row>
     <row r="270" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B270" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C270">
         <v>2748</v>
       </c>
       <c r="D270" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F270" t="s">
         <v>25</v>
@@ -8154,13 +8157,13 @@
     </row>
     <row r="271" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B271" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C271">
         <v>2745</v>
       </c>
       <c r="D271" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F271" t="s">
         <v>25</v>
@@ -8183,13 +8186,13 @@
     </row>
     <row r="272" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B272" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C272">
         <v>2246</v>
       </c>
       <c r="D272" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F272" t="s">
         <v>25</v>
@@ -8212,13 +8215,13 @@
     </row>
     <row r="273" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B273" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C273">
         <v>2749</v>
       </c>
       <c r="D273" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F273" t="s">
         <v>25</v>
@@ -8241,13 +8244,13 @@
     </row>
     <row r="274" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B274" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C274">
         <v>5032</v>
       </c>
       <c r="D274" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F274" t="s">
         <v>25</v>
@@ -8270,13 +8273,13 @@
     </row>
     <row r="275" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B275" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C275">
         <v>4755</v>
       </c>
       <c r="D275" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F275" t="s">
         <v>25</v>
@@ -8299,13 +8302,13 @@
     </row>
     <row r="276" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B276" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C276">
         <v>2245</v>
       </c>
       <c r="D276" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F276" t="s">
         <v>25</v>
@@ -8328,13 +8331,13 @@
     </row>
     <row r="277" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B277" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C277">
         <v>2750</v>
       </c>
       <c r="D277" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F277" t="s">
         <v>25</v>
@@ -8357,13 +8360,13 @@
     </row>
     <row r="278" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B278" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C278">
         <v>2747</v>
       </c>
       <c r="D278" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F278" t="s">
         <v>25</v>
@@ -8386,13 +8389,13 @@
     </row>
     <row r="279" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B279" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C279">
         <v>2741</v>
       </c>
       <c r="D279" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F279" t="s">
         <v>25</v>
@@ -8415,13 +8418,13 @@
     </row>
     <row r="280" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B280" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C280">
         <v>2739</v>
       </c>
       <c r="D280" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F280" t="s">
         <v>25</v>
@@ -8444,13 +8447,13 @@
     </row>
     <row r="281" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B281" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C281">
         <v>2736</v>
       </c>
       <c r="D281" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F281" t="s">
         <v>25</v>
@@ -8473,16 +8476,16 @@
     </row>
     <row r="282" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B282" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C282">
         <v>2738</v>
       </c>
       <c r="D282" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F282" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G282" t="s">
         <v>10</v>
@@ -8502,16 +8505,16 @@
     </row>
     <row r="283" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B283" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C283">
         <v>3832</v>
       </c>
       <c r="D283" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F283" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G283" t="s">
         <v>10</v>
@@ -8531,16 +8534,16 @@
     </row>
     <row r="284" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B284" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C284">
         <v>2740</v>
       </c>
       <c r="D284" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F284" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G284" t="s">
         <v>10</v>
@@ -8560,16 +8563,16 @@
     </row>
     <row r="285" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B285" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C285">
         <v>3885</v>
       </c>
       <c r="D285" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F285" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G285" t="s">
         <v>10</v>
@@ -8589,16 +8592,16 @@
     </row>
     <row r="286" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B286" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C286">
         <v>2742</v>
       </c>
       <c r="D286" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F286" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G286" t="s">
         <v>10</v>
@@ -8618,16 +8621,16 @@
     </row>
     <row r="287" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B287" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C287">
         <v>2737</v>
       </c>
       <c r="D287" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F287" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G287" t="s">
         <v>10</v>
@@ -8647,16 +8650,16 @@
     </row>
     <row r="288" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B288" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C288">
         <v>2748</v>
       </c>
       <c r="D288" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F288" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G288" t="s">
         <v>10</v>
@@ -8676,16 +8679,16 @@
     </row>
     <row r="289" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B289" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C289">
         <v>2745</v>
       </c>
       <c r="D289" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F289" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G289" t="s">
         <v>10</v>
@@ -8705,16 +8708,16 @@
     </row>
     <row r="290" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B290" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C290">
         <v>2246</v>
       </c>
       <c r="D290" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F290" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G290" t="s">
         <v>10</v>
@@ -8734,16 +8737,16 @@
     </row>
     <row r="291" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B291" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C291">
         <v>2749</v>
       </c>
       <c r="D291" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F291" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G291" t="s">
         <v>10</v>
@@ -8763,16 +8766,16 @@
     </row>
     <row r="292" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B292" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C292">
         <v>5032</v>
       </c>
       <c r="D292" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F292" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G292" t="s">
         <v>12</v>
@@ -8800,16 +8803,16 @@
     </row>
     <row r="294" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B294" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C294">
         <v>4755</v>
       </c>
       <c r="D294" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F294" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G294" t="s">
         <v>10</v>
@@ -8829,16 +8832,16 @@
     </row>
     <row r="295" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B295" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C295">
         <v>2245</v>
       </c>
       <c r="D295" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F295" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G295" t="s">
         <v>10</v>
@@ -8858,16 +8861,16 @@
     </row>
     <row r="296" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B296" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C296">
         <v>2750</v>
       </c>
       <c r="D296" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F296" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G296" t="s">
         <v>10</v>
@@ -8887,16 +8890,16 @@
     </row>
     <row r="297" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B297" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C297">
         <v>2747</v>
       </c>
       <c r="D297" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F297" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G297" t="s">
         <v>10</v>
@@ -8916,16 +8919,16 @@
     </row>
     <row r="298" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B298" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C298">
         <v>2741</v>
       </c>
       <c r="D298" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F298" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G298" t="s">
         <v>10</v>
@@ -8945,16 +8948,16 @@
     </row>
     <row r="299" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B299" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C299">
         <v>2739</v>
       </c>
       <c r="D299" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F299" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G299" t="s">
         <v>10</v>
@@ -8974,16 +8977,16 @@
     </row>
     <row r="300" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B300" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C300">
         <v>2736</v>
       </c>
       <c r="D300" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F300" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G300" t="s">
         <v>12</v>
@@ -9011,13 +9014,13 @@
     </row>
     <row r="302" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B302" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C302">
         <v>3832</v>
       </c>
       <c r="D302" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F302" t="s">
         <v>26</v>
@@ -9040,13 +9043,13 @@
     </row>
     <row r="303" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B303" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C303">
         <v>2740</v>
       </c>
       <c r="D303" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F303" t="s">
         <v>26</v>
@@ -9069,13 +9072,13 @@
     </row>
     <row r="304" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B304" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C304">
         <v>3885</v>
       </c>
       <c r="D304" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F304" t="s">
         <v>26</v>
@@ -9098,13 +9101,13 @@
     </row>
     <row r="305" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B305" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C305">
         <v>2742</v>
       </c>
       <c r="D305" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F305" t="s">
         <v>26</v>
@@ -9127,13 +9130,13 @@
     </row>
     <row r="306" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B306" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C306">
         <v>2737</v>
       </c>
       <c r="D306" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F306" t="s">
         <v>26</v>
@@ -9164,13 +9167,13 @@
     </row>
     <row r="308" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B308" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C308">
         <v>2748</v>
       </c>
       <c r="D308" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F308" t="s">
         <v>26</v>
@@ -9193,13 +9196,13 @@
     </row>
     <row r="309" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B309" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C309">
         <v>2745</v>
       </c>
       <c r="D309" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F309" t="s">
         <v>26</v>
@@ -9222,13 +9225,13 @@
     </row>
     <row r="310" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B310" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C310">
         <v>2246</v>
       </c>
       <c r="D310" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F310" t="s">
         <v>26</v>
@@ -9251,13 +9254,13 @@
     </row>
     <row r="311" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B311" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C311">
         <v>5274</v>
       </c>
       <c r="D311" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F311" t="s">
         <v>26</v>
@@ -9280,13 +9283,13 @@
     </row>
     <row r="312" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B312" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C312">
         <v>2749</v>
       </c>
       <c r="D312" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F312" t="s">
         <v>26</v>
@@ -9309,13 +9312,13 @@
     </row>
     <row r="313" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B313" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C313">
         <v>5032</v>
       </c>
       <c r="D313" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F313" t="s">
         <v>26</v>
@@ -9338,13 +9341,13 @@
     </row>
     <row r="314" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B314" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C314">
         <v>4755</v>
       </c>
       <c r="D314" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F314" t="s">
         <v>26</v>
@@ -9367,13 +9370,13 @@
     </row>
     <row r="315" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B315" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C315">
         <v>2245</v>
       </c>
       <c r="D315" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F315" t="s">
         <v>26</v>
@@ -9396,13 +9399,13 @@
     </row>
     <row r="316" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B316" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C316">
         <v>2750</v>
       </c>
       <c r="D316" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F316" t="s">
         <v>26</v>
@@ -9425,13 +9428,13 @@
     </row>
     <row r="317" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B317" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C317">
         <v>2747</v>
       </c>
       <c r="D317" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F317" t="s">
         <v>26</v>
@@ -9454,13 +9457,13 @@
     </row>
     <row r="318" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B318" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C318">
         <v>2741</v>
       </c>
       <c r="D318" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F318" t="s">
         <v>26</v>
@@ -9491,13 +9494,13 @@
     </row>
     <row r="320" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B320" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C320">
         <v>2739</v>
       </c>
       <c r="D320" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F320" t="s">
         <v>26</v>
@@ -9520,13 +9523,13 @@
     </row>
     <row r="321" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B321" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C321">
         <v>2736</v>
       </c>
       <c r="D321" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F321" t="s">
         <v>26</v>
@@ -9549,13 +9552,13 @@
     </row>
     <row r="322" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B322" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C322">
         <v>3832</v>
       </c>
       <c r="D322" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F322" t="s">
         <v>27</v>
@@ -9578,13 +9581,13 @@
     </row>
     <row r="323" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B323" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C323">
         <v>2740</v>
       </c>
       <c r="D323" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F323" t="s">
         <v>27</v>
@@ -9607,13 +9610,13 @@
     </row>
     <row r="324" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B324" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C324">
         <v>3885</v>
       </c>
       <c r="D324" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F324" t="s">
         <v>27</v>
@@ -9636,13 +9639,13 @@
     </row>
     <row r="325" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C325">
         <v>2742</v>
       </c>
       <c r="D325" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F325" t="s">
         <v>27</v>
@@ -9665,13 +9668,13 @@
     </row>
     <row r="326" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B326" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C326">
         <v>2737</v>
       </c>
       <c r="D326" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F326" t="s">
         <v>27</v>
@@ -9702,13 +9705,13 @@
     </row>
     <row r="328" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B328" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C328">
         <v>2748</v>
       </c>
       <c r="D328" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F328" t="s">
         <v>27</v>
@@ -9731,13 +9734,13 @@
     </row>
     <row r="329" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B329" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C329">
         <v>2745</v>
       </c>
       <c r="D329" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F329" t="s">
         <v>27</v>
@@ -9760,13 +9763,13 @@
     </row>
     <row r="330" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B330" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C330">
         <v>2246</v>
       </c>
       <c r="D330" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F330" t="s">
         <v>27</v>
@@ -9789,13 +9792,13 @@
     </row>
     <row r="331" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B331" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C331">
         <v>5274</v>
       </c>
       <c r="D331" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F331" t="s">
         <v>27</v>
@@ -9818,13 +9821,13 @@
     </row>
     <row r="332" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B332" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C332">
         <v>2749</v>
       </c>
       <c r="D332" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F332" t="s">
         <v>27</v>
@@ -9855,13 +9858,13 @@
     </row>
     <row r="334" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B334" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C334">
         <v>5032</v>
       </c>
       <c r="D334" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F334" t="s">
         <v>27</v>
@@ -9884,13 +9887,13 @@
     </row>
     <row r="335" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B335" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C335">
         <v>4755</v>
       </c>
       <c r="D335" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F335" t="s">
         <v>27</v>
@@ -9913,13 +9916,13 @@
     </row>
     <row r="336" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C336">
         <v>2245</v>
       </c>
       <c r="D336" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F336" t="s">
         <v>27</v>
@@ -9942,13 +9945,13 @@
     </row>
     <row r="337" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B337" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C337">
         <v>2750</v>
       </c>
       <c r="D337" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F337" t="s">
         <v>27</v>
@@ -9971,13 +9974,13 @@
     </row>
     <row r="338" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C338">
         <v>2747</v>
       </c>
       <c r="D338" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F338" t="s">
         <v>27</v>
@@ -10000,13 +10003,13 @@
     </row>
     <row r="339" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B339" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C339">
         <v>2741</v>
       </c>
       <c r="D339" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F339" t="s">
         <v>27</v>
@@ -10029,13 +10032,13 @@
     </row>
     <row r="340" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B340" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C340">
         <v>2739</v>
       </c>
       <c r="D340" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F340" t="s">
         <v>27</v>
@@ -10058,13 +10061,13 @@
     </row>
     <row r="341" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B341" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C341">
         <v>2736</v>
       </c>
       <c r="D341" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F341" t="s">
         <v>27</v>
@@ -10087,13 +10090,13 @@
     </row>
     <row r="342" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B342" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C342">
         <v>3832</v>
       </c>
       <c r="D342" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F342" t="s">
         <v>19</v>
@@ -10116,13 +10119,13 @@
     </row>
     <row r="343" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B343" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C343">
         <v>2740</v>
       </c>
       <c r="D343" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F343" t="s">
         <v>19</v>
@@ -10145,13 +10148,13 @@
     </row>
     <row r="344" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B344" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C344">
         <v>3885</v>
       </c>
       <c r="D344" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F344" t="s">
         <v>19</v>
@@ -10174,13 +10177,13 @@
     </row>
     <row r="345" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B345" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C345">
         <v>2742</v>
       </c>
       <c r="D345" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F345" t="s">
         <v>19</v>
@@ -10203,13 +10206,13 @@
     </row>
     <row r="346" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B346" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C346">
         <v>2737</v>
       </c>
       <c r="D346" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F346" t="s">
         <v>19</v>
@@ -10232,13 +10235,13 @@
     </row>
     <row r="347" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B347" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C347">
         <v>2748</v>
       </c>
       <c r="D347" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F347" t="s">
         <v>19</v>
@@ -10261,13 +10264,13 @@
     </row>
     <row r="348" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B348" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C348">
         <v>2745</v>
       </c>
       <c r="D348" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F348" t="s">
         <v>19</v>
@@ -10290,13 +10293,13 @@
     </row>
     <row r="349" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B349" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C349">
         <v>2246</v>
       </c>
       <c r="D349" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F349" t="s">
         <v>19</v>
@@ -10319,13 +10322,13 @@
     </row>
     <row r="350" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B350" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C350">
         <v>5274</v>
       </c>
       <c r="D350" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F350" t="s">
         <v>19</v>
@@ -10348,13 +10351,13 @@
     </row>
     <row r="351" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B351" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C351">
         <v>2749</v>
       </c>
       <c r="D351" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F351" t="s">
         <v>19</v>
@@ -10377,13 +10380,13 @@
     </row>
     <row r="352" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B352" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C352">
         <v>5032</v>
       </c>
       <c r="D352" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F352" t="s">
         <v>19</v>
@@ -10414,13 +10417,13 @@
     </row>
     <row r="354" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C354">
         <v>4755</v>
       </c>
       <c r="D354" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F354" t="s">
         <v>19</v>
@@ -10451,13 +10454,13 @@
     </row>
     <row r="356" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C356">
         <v>2245</v>
       </c>
       <c r="D356" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F356" t="s">
         <v>19</v>
@@ -10480,13 +10483,13 @@
     </row>
     <row r="357" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B357" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C357">
         <v>2750</v>
       </c>
       <c r="D357" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F357" t="s">
         <v>19</v>
@@ -10509,13 +10512,13 @@
     </row>
     <row r="358" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B358" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C358">
         <v>2747</v>
       </c>
       <c r="D358" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F358" t="s">
         <v>19</v>
@@ -10538,13 +10541,13 @@
     </row>
     <row r="359" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B359" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C359">
         <v>2741</v>
       </c>
       <c r="D359" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F359" t="s">
         <v>19</v>
@@ -10567,13 +10570,13 @@
     </row>
     <row r="360" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B360" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C360">
         <v>2739</v>
       </c>
       <c r="D360" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F360" t="s">
         <v>19</v>
@@ -10596,13 +10599,13 @@
     </row>
     <row r="361" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B361" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C361">
         <v>2736</v>
       </c>
       <c r="D361" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F361" t="s">
         <v>19</v>
@@ -10625,13 +10628,13 @@
     </row>
     <row r="362" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B362" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C362">
         <v>3832</v>
       </c>
       <c r="D362" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F362" t="s">
         <v>23</v>
@@ -10654,13 +10657,13 @@
     </row>
     <row r="363" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B363" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C363">
         <v>3885</v>
       </c>
       <c r="D363" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F363" t="s">
         <v>23</v>
@@ -10683,13 +10686,13 @@
     </row>
     <row r="364" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B364" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C364">
         <v>5032</v>
       </c>
       <c r="D364" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F364" t="s">
         <v>23</v>
@@ -10712,13 +10715,13 @@
     </row>
     <row r="365" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B365" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C365">
         <v>2245</v>
       </c>
       <c r="D365" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F365" t="s">
         <v>23</v>
@@ -10741,13 +10744,13 @@
     </row>
     <row r="366" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B366" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C366">
         <v>2747</v>
       </c>
       <c r="D366" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F366" t="s">
         <v>23</v>
@@ -10770,13 +10773,13 @@
     </row>
     <row r="367" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B367" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C367">
         <v>2745</v>
       </c>
       <c r="D367" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F367" t="s">
         <v>28</v>
@@ -10799,13 +10802,13 @@
     </row>
     <row r="368" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B368" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C368">
         <v>2740</v>
       </c>
       <c r="D368" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F368" t="s">
         <v>28</v>
@@ -10828,13 +10831,13 @@
     </row>
     <row r="369" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B369" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C369">
         <v>2742</v>
       </c>
       <c r="D369" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F369" t="s">
         <v>28</v>
@@ -10857,13 +10860,13 @@
     </row>
     <row r="370" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B370" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C370">
         <v>2737</v>
       </c>
       <c r="D370" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F370" t="s">
         <v>28</v>
@@ -10886,13 +10889,13 @@
     </row>
     <row r="371" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B371" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C371">
         <v>2748</v>
       </c>
       <c r="D371" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F371" t="s">
         <v>28</v>
@@ -10915,13 +10918,13 @@
     </row>
     <row r="372" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C372">
         <v>2246</v>
       </c>
       <c r="D372" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F372" t="s">
         <v>28</v>
@@ -10944,13 +10947,13 @@
     </row>
     <row r="373" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B373" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C373">
         <v>5274</v>
       </c>
       <c r="D373" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F373" t="s">
         <v>28</v>
@@ -10973,13 +10976,13 @@
     </row>
     <row r="374" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B374" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C374">
         <v>5607</v>
       </c>
       <c r="D374" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F374" t="s">
         <v>28</v>
@@ -11002,13 +11005,13 @@
     </row>
     <row r="375" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B375" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C375">
         <v>4755</v>
       </c>
       <c r="D375" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F375" t="s">
         <v>28</v>
@@ -11031,13 +11034,13 @@
     </row>
     <row r="376" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B376" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C376">
         <v>2750</v>
       </c>
       <c r="D376" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F376" t="s">
         <v>28</v>
@@ -11060,13 +11063,13 @@
     </row>
     <row r="377" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B377" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C377">
         <v>2741</v>
       </c>
       <c r="D377" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F377" t="s">
         <v>28</v>
@@ -11089,13 +11092,13 @@
     </row>
     <row r="378" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B378" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C378">
         <v>2739</v>
       </c>
       <c r="D378" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F378" t="s">
         <v>28</v>
@@ -11118,13 +11121,13 @@
     </row>
     <row r="379" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B379" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C379">
         <v>2736</v>
       </c>
       <c r="D379" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F379" t="s">
         <v>28</v>
@@ -11147,13 +11150,13 @@
     </row>
     <row r="380" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B380" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C380">
         <v>3832</v>
       </c>
       <c r="D380" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F380" t="s">
         <v>21</v>
@@ -11176,13 +11179,13 @@
     </row>
     <row r="381" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B381" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C381">
         <v>2740</v>
       </c>
       <c r="D381" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F381" t="s">
         <v>21</v>
@@ -11205,13 +11208,13 @@
     </row>
     <row r="382" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C382">
         <v>3885</v>
       </c>
       <c r="D382" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F382" t="s">
         <v>21</v>
@@ -11234,13 +11237,13 @@
     </row>
     <row r="383" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B383" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C383">
         <v>2742</v>
       </c>
       <c r="D383" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F383" t="s">
         <v>21</v>
@@ -11263,13 +11266,13 @@
     </row>
     <row r="384" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B384" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C384">
         <v>2737</v>
       </c>
       <c r="D384" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F384" t="s">
         <v>21</v>
@@ -11292,13 +11295,13 @@
     </row>
     <row r="385" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B385" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C385">
         <v>2748</v>
       </c>
       <c r="D385" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F385" t="s">
         <v>21</v>
@@ -11321,13 +11324,13 @@
     </row>
     <row r="386" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B386" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C386">
         <v>2745</v>
       </c>
       <c r="D386" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F386" t="s">
         <v>21</v>
@@ -11350,13 +11353,13 @@
     </row>
     <row r="387" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B387" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C387">
         <v>2246</v>
       </c>
       <c r="D387" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F387" t="s">
         <v>21</v>
@@ -11379,13 +11382,13 @@
     </row>
     <row r="388" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B388" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C388">
         <v>5274</v>
       </c>
       <c r="D388" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F388" t="s">
         <v>21</v>
@@ -11408,13 +11411,13 @@
     </row>
     <row r="389" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B389" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C389">
         <v>5607</v>
       </c>
       <c r="D389" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F389" t="s">
         <v>21</v>
@@ -11437,13 +11440,13 @@
     </row>
     <row r="390" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B390" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C390">
         <v>2749</v>
       </c>
       <c r="D390" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F390" t="s">
         <v>21</v>
@@ -11466,13 +11469,13 @@
     </row>
     <row r="391" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B391" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C391">
         <v>5032</v>
       </c>
       <c r="D391" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F391" t="s">
         <v>21</v>
@@ -11495,13 +11498,13 @@
     </row>
     <row r="392" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B392" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C392">
         <v>4755</v>
       </c>
       <c r="D392" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F392" t="s">
         <v>21</v>
@@ -11524,13 +11527,13 @@
     </row>
     <row r="393" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B393" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C393">
         <v>2245</v>
       </c>
       <c r="D393" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F393" t="s">
         <v>21</v>
@@ -11553,13 +11556,13 @@
     </row>
     <row r="394" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B394" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C394">
         <v>2750</v>
       </c>
       <c r="D394" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F394" t="s">
         <v>21</v>
@@ -11582,13 +11585,13 @@
     </row>
     <row r="395" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B395" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C395">
         <v>2747</v>
       </c>
       <c r="D395" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F395" t="s">
         <v>21</v>
@@ -11611,13 +11614,13 @@
     </row>
     <row r="396" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B396" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C396">
         <v>2741</v>
       </c>
       <c r="D396" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F396" t="s">
         <v>21</v>
@@ -11640,13 +11643,13 @@
     </row>
     <row r="397" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B397" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C397">
         <v>2739</v>
       </c>
       <c r="D397" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F397" t="s">
         <v>21</v>
@@ -11669,13 +11672,13 @@
     </row>
     <row r="398" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B398" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C398">
         <v>2736</v>
       </c>
       <c r="D398" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F398" t="s">
         <v>21</v>
@@ -11697,204 +11700,641 @@
       </c>
     </row>
     <row r="399" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H399" s="2"/>
-      <c r="I399" s="1"/>
-      <c r="J399" s="2"/>
-      <c r="K399" s="1"/>
+      <c r="B399" t="s">
+        <v>38</v>
+      </c>
+      <c r="C399">
+        <v>3832</v>
+      </c>
+      <c r="D399" t="s">
+        <v>57</v>
+      </c>
+      <c r="F399" t="s">
+        <v>29</v>
+      </c>
+      <c r="G399" t="s">
+        <v>10</v>
+      </c>
+      <c r="H399" s="2">
+        <v>7.6504629629629631E-3</v>
+      </c>
+      <c r="I399" s="1">
+        <v>46237.816319444442</v>
+      </c>
+      <c r="J399" s="2">
+        <v>0</v>
+      </c>
+      <c r="K399" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="400" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H400" s="2"/>
-      <c r="I400" s="1"/>
-      <c r="J400" s="2"/>
-      <c r="K400" s="1"/>
-    </row>
-    <row r="401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H401" s="2"/>
-      <c r="I401" s="1"/>
-      <c r="J401" s="2"/>
-      <c r="K401" s="1"/>
-    </row>
-    <row r="402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H402" s="2"/>
-      <c r="I402" s="1"/>
-      <c r="J402" s="2"/>
-      <c r="K402" s="1"/>
-    </row>
-    <row r="403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H403" s="2"/>
-      <c r="I403" s="1"/>
-      <c r="J403" s="2"/>
-      <c r="K403" s="1"/>
-    </row>
-    <row r="404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H404" s="2"/>
-      <c r="I404" s="1"/>
-      <c r="J404" s="2"/>
-      <c r="K404" s="1"/>
-    </row>
-    <row r="405" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H405" s="2"/>
-      <c r="I405" s="1"/>
-      <c r="J405" s="2"/>
-      <c r="K405" s="1"/>
-    </row>
-    <row r="406" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H406" s="2"/>
-      <c r="I406" s="1"/>
-      <c r="J406" s="2"/>
-      <c r="K406" s="1"/>
-    </row>
-    <row r="407" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H407" s="2"/>
-      <c r="I407" s="1"/>
-      <c r="J407" s="2"/>
-      <c r="K407" s="1"/>
-    </row>
-    <row r="408" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H408" s="2"/>
-      <c r="I408" s="1"/>
-      <c r="J408" s="2"/>
-      <c r="K408" s="1"/>
-    </row>
-    <row r="409" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H409" s="2"/>
-      <c r="I409" s="1"/>
-      <c r="J409" s="2"/>
-      <c r="K409" s="1"/>
-    </row>
-    <row r="410" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H410" s="2"/>
-      <c r="I410" s="1"/>
-      <c r="J410" s="2"/>
-      <c r="K410" s="1"/>
-    </row>
-    <row r="411" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H411" s="2"/>
-      <c r="I411" s="1"/>
-      <c r="J411" s="2"/>
-      <c r="K411" s="1"/>
-    </row>
-    <row r="412" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H412" s="2"/>
-      <c r="I412" s="1"/>
-      <c r="J412" s="2"/>
-      <c r="K412" s="1"/>
-    </row>
-    <row r="413" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H413" s="2"/>
-      <c r="I413" s="1"/>
-      <c r="J413" s="2"/>
-      <c r="K413" s="1"/>
-    </row>
-    <row r="414" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H414" s="2"/>
-      <c r="I414" s="1"/>
-      <c r="J414" s="2"/>
-      <c r="K414" s="1"/>
-    </row>
-    <row r="415" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H415" s="2"/>
-      <c r="I415" s="1"/>
-      <c r="J415" s="2"/>
-      <c r="K415" s="1"/>
-    </row>
-    <row r="416" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H416" s="2"/>
-      <c r="I416" s="1"/>
-      <c r="J416" s="2"/>
-      <c r="K416" s="1"/>
-    </row>
-    <row r="417" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H417" s="2"/>
-      <c r="I417" s="1"/>
-      <c r="J417" s="2"/>
-      <c r="K417" s="1"/>
-    </row>
-    <row r="418" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="B400" t="s">
+        <v>38</v>
+      </c>
+      <c r="C400">
+        <v>2740</v>
+      </c>
+      <c r="D400" t="s">
+        <v>42</v>
+      </c>
+      <c r="F400" t="s">
+        <v>29</v>
+      </c>
+      <c r="G400" t="s">
+        <v>13</v>
+      </c>
+      <c r="H400" s="2">
+        <v>0</v>
+      </c>
+      <c r="I400" s="1">
+        <v>46237.816319444442</v>
+      </c>
+      <c r="J400" s="2">
+        <v>0</v>
+      </c>
+      <c r="K400" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="401" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B401" t="s">
+        <v>38</v>
+      </c>
+      <c r="C401">
+        <v>3885</v>
+      </c>
+      <c r="D401" t="s">
+        <v>58</v>
+      </c>
+      <c r="F401" t="s">
+        <v>29</v>
+      </c>
+      <c r="G401" t="s">
+        <v>10</v>
+      </c>
+      <c r="H401" s="2">
+        <v>6.0069444444444441E-3</v>
+      </c>
+      <c r="I401" s="1">
+        <v>46237.817013888889</v>
+      </c>
+      <c r="J401" s="2">
+        <v>0</v>
+      </c>
+      <c r="K401" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="402" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B402" t="s">
+        <v>38</v>
+      </c>
+      <c r="C402">
+        <v>2742</v>
+      </c>
+      <c r="D402" t="s">
+        <v>44</v>
+      </c>
+      <c r="F402" t="s">
+        <v>29</v>
+      </c>
+      <c r="G402" t="s">
+        <v>10</v>
+      </c>
+      <c r="H402" s="2">
+        <v>9.3055555555555548E-3</v>
+      </c>
+      <c r="I402" s="1">
+        <v>46237.79351851852</v>
+      </c>
+      <c r="J402" s="2">
+        <v>0</v>
+      </c>
+      <c r="K402" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="403" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B403" t="s">
+        <v>38</v>
+      </c>
+      <c r="C403">
+        <v>2737</v>
+      </c>
+      <c r="D403" t="s">
+        <v>45</v>
+      </c>
+      <c r="F403" t="s">
+        <v>29</v>
+      </c>
+      <c r="G403" t="s">
+        <v>13</v>
+      </c>
+      <c r="H403" s="2">
+        <v>0</v>
+      </c>
+      <c r="I403" s="1">
+        <v>46237.794212962966</v>
+      </c>
+      <c r="J403" s="2">
+        <v>0</v>
+      </c>
+      <c r="K403" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="404" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B404" t="s">
+        <v>38</v>
+      </c>
+      <c r="C404">
+        <v>2748</v>
+      </c>
+      <c r="D404" t="s">
+        <v>46</v>
+      </c>
+      <c r="F404" t="s">
+        <v>29</v>
+      </c>
+      <c r="G404" t="s">
+        <v>10</v>
+      </c>
+      <c r="H404" s="2">
+        <v>7.1412037037037034E-3</v>
+      </c>
+      <c r="I404" s="1">
+        <v>46237.794907407406</v>
+      </c>
+      <c r="J404" s="2">
+        <v>0</v>
+      </c>
+      <c r="K404" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="405" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B405" t="s">
+        <v>38</v>
+      </c>
+      <c r="C405">
+        <v>2745</v>
+      </c>
+      <c r="D405" t="s">
+        <v>47</v>
+      </c>
+      <c r="F405" t="s">
+        <v>29</v>
+      </c>
+      <c r="G405" t="s">
+        <v>13</v>
+      </c>
+      <c r="H405" s="2">
+        <v>0</v>
+      </c>
+      <c r="I405" s="1">
+        <v>46237.795601851853</v>
+      </c>
+      <c r="J405" s="2">
+        <v>0</v>
+      </c>
+      <c r="K405" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="406" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B406" t="s">
+        <v>38</v>
+      </c>
+      <c r="C406">
+        <v>2246</v>
+      </c>
+      <c r="D406" t="s">
+        <v>39</v>
+      </c>
+      <c r="F406" t="s">
+        <v>29</v>
+      </c>
+      <c r="G406" t="s">
+        <v>13</v>
+      </c>
+      <c r="H406" s="2">
+        <v>0</v>
+      </c>
+      <c r="I406" s="1">
+        <v>46237.796296296299</v>
+      </c>
+      <c r="J406" s="2">
+        <v>0</v>
+      </c>
+      <c r="K406" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="407" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B407" t="s">
+        <v>38</v>
+      </c>
+      <c r="C407">
+        <v>5274</v>
+      </c>
+      <c r="D407" t="s">
+        <v>61</v>
+      </c>
+      <c r="F407" t="s">
+        <v>29</v>
+      </c>
+      <c r="G407" t="s">
+        <v>13</v>
+      </c>
+      <c r="H407" s="2">
+        <v>0</v>
+      </c>
+      <c r="I407" s="1">
+        <v>46237.796296296299</v>
+      </c>
+      <c r="J407" s="2">
+        <v>0</v>
+      </c>
+      <c r="K407" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="408" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B408" t="s">
+        <v>38</v>
+      </c>
+      <c r="C408">
+        <v>5607</v>
+      </c>
+      <c r="D408" t="s">
+        <v>62</v>
+      </c>
+      <c r="F408" t="s">
+        <v>29</v>
+      </c>
+      <c r="G408" t="s">
+        <v>13</v>
+      </c>
+      <c r="H408" s="2">
+        <v>0</v>
+      </c>
+      <c r="I408" s="1">
+        <v>46237.796990740739</v>
+      </c>
+      <c r="J408" s="2">
+        <v>0</v>
+      </c>
+      <c r="K408" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="409" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B409" t="s">
+        <v>38</v>
+      </c>
+      <c r="C409">
+        <v>2749</v>
+      </c>
+      <c r="D409" t="s">
+        <v>50</v>
+      </c>
+      <c r="F409" t="s">
+        <v>29</v>
+      </c>
+      <c r="G409" t="s">
+        <v>13</v>
+      </c>
+      <c r="H409" s="2">
+        <v>0</v>
+      </c>
+      <c r="I409" s="1">
+        <v>46237.797685185185</v>
+      </c>
+      <c r="J409" s="2">
+        <v>0</v>
+      </c>
+      <c r="K409" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="410" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B410" t="s">
+        <v>38</v>
+      </c>
+      <c r="C410">
+        <v>5032</v>
+      </c>
+      <c r="D410" t="s">
+        <v>60</v>
+      </c>
+      <c r="F410" t="s">
+        <v>29</v>
+      </c>
+      <c r="G410" t="s">
+        <v>13</v>
+      </c>
+      <c r="H410" s="2">
+        <v>0</v>
+      </c>
+      <c r="I410" s="1">
+        <v>46237.797685185185</v>
+      </c>
+      <c r="J410" s="2">
+        <v>0</v>
+      </c>
+      <c r="K410" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="411" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B411" t="s">
+        <v>38</v>
+      </c>
+      <c r="C411">
+        <v>4755</v>
+      </c>
+      <c r="D411" t="s">
+        <v>59</v>
+      </c>
+      <c r="F411" t="s">
+        <v>29</v>
+      </c>
+      <c r="G411" t="s">
+        <v>13</v>
+      </c>
+      <c r="H411" s="2">
+        <v>0</v>
+      </c>
+      <c r="I411" s="1">
+        <v>46237.798379629632</v>
+      </c>
+      <c r="J411" s="2">
+        <v>0</v>
+      </c>
+      <c r="K411" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="412" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B412" t="s">
+        <v>38</v>
+      </c>
+      <c r="C412">
+        <v>2245</v>
+      </c>
+      <c r="D412" t="s">
+        <v>40</v>
+      </c>
+      <c r="F412" t="s">
+        <v>29</v>
+      </c>
+      <c r="G412" t="s">
+        <v>10</v>
+      </c>
+      <c r="H412" s="2">
+        <v>6.6898148148148151E-3</v>
+      </c>
+      <c r="I412" s="1">
+        <v>46237.799074074072</v>
+      </c>
+      <c r="J412" s="2">
+        <v>0</v>
+      </c>
+      <c r="K412" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="413" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B413" t="s">
+        <v>38</v>
+      </c>
+      <c r="C413">
+        <v>2750</v>
+      </c>
+      <c r="D413" t="s">
+        <v>52</v>
+      </c>
+      <c r="F413" t="s">
+        <v>29</v>
+      </c>
+      <c r="G413" t="s">
+        <v>10</v>
+      </c>
+      <c r="H413" s="2">
+        <v>1.0752314814814815E-2</v>
+      </c>
+      <c r="I413" s="1">
+        <v>46237.799768518518</v>
+      </c>
+      <c r="J413" s="2">
+        <v>0</v>
+      </c>
+      <c r="K413" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="414" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B414" t="s">
+        <v>38</v>
+      </c>
+      <c r="C414">
+        <v>2747</v>
+      </c>
+      <c r="D414" t="s">
+        <v>53</v>
+      </c>
+      <c r="F414" t="s">
+        <v>29</v>
+      </c>
+      <c r="G414" t="s">
+        <v>13</v>
+      </c>
+      <c r="H414" s="2">
+        <v>0</v>
+      </c>
+      <c r="I414" s="1">
+        <v>46237.799768518518</v>
+      </c>
+      <c r="J414" s="2">
+        <v>0</v>
+      </c>
+      <c r="K414" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="415" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B415" t="s">
+        <v>38</v>
+      </c>
+      <c r="C415">
+        <v>2741</v>
+      </c>
+      <c r="D415" t="s">
+        <v>54</v>
+      </c>
+      <c r="F415" t="s">
+        <v>29</v>
+      </c>
+      <c r="G415" t="s">
+        <v>13</v>
+      </c>
+      <c r="H415" s="2">
+        <v>0</v>
+      </c>
+      <c r="I415" s="1">
+        <v>46237.800462962965</v>
+      </c>
+      <c r="J415" s="2">
+        <v>0</v>
+      </c>
+      <c r="K415" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="416" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B416" t="s">
+        <v>38</v>
+      </c>
+      <c r="C416">
+        <v>2739</v>
+      </c>
+      <c r="D416" t="s">
+        <v>55</v>
+      </c>
+      <c r="F416" t="s">
+        <v>29</v>
+      </c>
+      <c r="G416" t="s">
+        <v>13</v>
+      </c>
+      <c r="H416" s="2">
+        <v>0</v>
+      </c>
+      <c r="I416" s="1">
+        <v>46237.801157407404</v>
+      </c>
+      <c r="J416" s="2">
+        <v>0</v>
+      </c>
+      <c r="K416" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="417" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B417" t="s">
+        <v>38</v>
+      </c>
+      <c r="C417">
+        <v>2736</v>
+      </c>
+      <c r="D417" t="s">
+        <v>56</v>
+      </c>
+      <c r="F417" t="s">
+        <v>29</v>
+      </c>
+      <c r="G417" t="s">
+        <v>10</v>
+      </c>
+      <c r="H417" s="2">
+        <v>9.7569444444444448E-3</v>
+      </c>
+      <c r="I417" s="1">
+        <v>46237.801851851851</v>
+      </c>
+      <c r="J417" s="2">
+        <v>0</v>
+      </c>
+      <c r="K417" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="418" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H418" s="2"/>
       <c r="I418" s="1"/>
       <c r="J418" s="2"/>
       <c r="K418" s="1"/>
     </row>
-    <row r="419" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H419" s="2"/>
       <c r="I419" s="1"/>
       <c r="J419" s="2"/>
       <c r="K419" s="1"/>
     </row>
-    <row r="420" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H420" s="2"/>
       <c r="I420" s="1"/>
       <c r="J420" s="2"/>
       <c r="K420" s="1"/>
     </row>
-    <row r="421" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H421" s="2"/>
       <c r="I421" s="1"/>
       <c r="J421" s="2"/>
       <c r="K421" s="1"/>
     </row>
-    <row r="422" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H422" s="2"/>
       <c r="I422" s="1"/>
       <c r="J422" s="2"/>
       <c r="K422" s="1"/>
     </row>
-    <row r="423" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H423" s="2"/>
       <c r="I423" s="1"/>
       <c r="J423" s="2"/>
       <c r="K423" s="1"/>
     </row>
-    <row r="424" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H424" s="2"/>
       <c r="I424" s="1"/>
       <c r="J424" s="2"/>
       <c r="K424" s="1"/>
     </row>
-    <row r="425" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H425" s="2"/>
       <c r="I425" s="1"/>
       <c r="J425" s="2"/>
       <c r="K425" s="1"/>
     </row>
-    <row r="426" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H426" s="2"/>
       <c r="I426" s="1"/>
       <c r="J426" s="2"/>
       <c r="K426" s="1"/>
     </row>
-    <row r="427" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H427" s="2"/>
       <c r="I427" s="1"/>
       <c r="J427" s="2"/>
       <c r="K427" s="1"/>
     </row>
-    <row r="428" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H428" s="2"/>
       <c r="I428" s="1"/>
       <c r="J428" s="2"/>
       <c r="K428" s="1"/>
     </row>
-    <row r="429" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H429" s="2"/>
       <c r="I429" s="1"/>
       <c r="J429" s="2"/>
       <c r="K429" s="1"/>
     </row>
-    <row r="430" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H430" s="2"/>
       <c r="I430" s="1"/>
       <c r="J430" s="2"/>
       <c r="K430" s="1"/>
     </row>
-    <row r="431" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H431" s="2"/>
       <c r="I431" s="1"/>
       <c r="J431" s="2"/>
       <c r="K431" s="1"/>
     </row>
-    <row r="432" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H432" s="2"/>
       <c r="I432" s="1"/>
       <c r="J432" s="2"/>
@@ -51436,6 +51876,7 @@
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
@@ -51450,11 +51891,13 @@
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -51465,10 +51908,13 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
@@ -51486,14 +51932,17 @@
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -51504,14 +51953,17 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
@@ -51538,6 +51990,7 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
@@ -51546,6 +51999,7 @@
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
@@ -51558,22 +52012,27 @@
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -51592,6 +52051,7 @@
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -51602,10 +52062,12 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
@@ -51614,10 +52076,12 @@
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
@@ -51631,82 +52095,97 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
@@ -51720,6 +52199,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -51730,6 +52210,7 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
@@ -51737,6 +52218,7 @@
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
@@ -51745,86 +52227,99 @@
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -51841,26 +52336,32 @@
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
@@ -51891,6 +52392,7 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
@@ -51900,10 +52402,12 @@
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
@@ -51916,14 +52420,17 @@
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
@@ -51932,14 +52439,17 @@
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
@@ -51958,26 +52468,32 @@
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -51996,6 +52512,7 @@
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
@@ -52004,10 +52521,12 @@
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
@@ -52016,6 +52535,7 @@
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
@@ -52028,10 +52548,12 @@
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
@@ -52040,6 +52562,7 @@
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
@@ -52048,14 +52571,17 @@
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
@@ -52064,14 +52590,17 @@
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
@@ -52088,76 +52617,85 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
@@ -52171,31 +52709,38 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
@@ -52208,10 +52753,12 @@
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
@@ -52220,10 +52767,12 @@
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
@@ -52232,6 +52781,7 @@
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -52246,10 +52796,12 @@
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
@@ -52258,10 +52810,12 @@
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
@@ -52275,6 +52829,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -52290,14 +52845,17 @@
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -52315,14 +52873,17 @@
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
@@ -52335,10 +52896,12 @@
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
@@ -52347,14 +52910,17 @@
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
@@ -52363,10 +52929,12 @@
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
@@ -52375,14 +52943,17 @@
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
@@ -52404,6 +52975,7 @@
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
@@ -52412,39 +52984,65 @@
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7395" s="2"/>
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
+    </row>
+    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7402" s="2"/>
+      <c r="I7402" s="1"/>
+    </row>
+    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7403" s="1"/>
+    </row>
+    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7404" s="2"/>
+      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\neal-pool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{148C8D81-2E0E-4BFA-B572-C88936BFBF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E69FA988-C9E6-4D44-BD65-B5736DC933D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -601,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>38</v>
       </c>
@@ -851,7 +851,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2"/>
@@ -946,7 +946,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>38</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>38</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H32" s="2"/>
       <c r="I32" s="1"/>
       <c r="J32" s="2"/>
@@ -1745,7 +1745,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>38</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>38</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>38</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>38</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>38</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>38</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>38</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>38</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>38</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>38</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>38</v>
       </c>
@@ -6404,7 +6404,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>38</v>
       </c>
@@ -7311,7 +7311,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>38</v>
       </c>
@@ -9637,7 +9637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>38</v>
       </c>
@@ -9914,7 +9914,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>38</v>
       </c>
@@ -9972,7 +9972,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>38</v>
       </c>
@@ -10415,7 +10415,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>38</v>
       </c>
@@ -10452,7 +10452,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>38</v>
       </c>
@@ -10916,7 +10916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>38</v>
       </c>
@@ -11206,7 +11206,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>38</v>
       </c>
@@ -11751,7 +11751,7 @@
         <v>46237.816319444442</v>
       </c>
       <c r="J400" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K400" s="1" t="s">
         <v>11</v>
@@ -11838,7 +11838,7 @@
         <v>46237.794212962966</v>
       </c>
       <c r="J403" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K403" s="1" t="s">
         <v>11</v>
@@ -11887,10 +11887,10 @@
         <v>29</v>
       </c>
       <c r="G405" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H405" s="2">
-        <v>0</v>
+        <v>7.7314814814814815E-3</v>
       </c>
       <c r="I405" s="1">
         <v>46237.795601851853</v>
@@ -11916,16 +11916,16 @@
         <v>29</v>
       </c>
       <c r="G406" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H406" s="2">
-        <v>0</v>
+        <v>5.8680555555555552E-3</v>
       </c>
       <c r="I406" s="1">
         <v>46237.796296296299</v>
       </c>
       <c r="J406" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K406" s="1" t="s">
         <v>11</v>
@@ -11945,16 +11945,16 @@
         <v>29</v>
       </c>
       <c r="G407" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H407" s="2">
-        <v>0</v>
+        <v>8.4259259259259253E-3</v>
       </c>
       <c r="I407" s="1">
         <v>46237.796296296299</v>
       </c>
       <c r="J407" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K407" s="1" t="s">
         <v>11</v>
@@ -11974,16 +11974,16 @@
         <v>29</v>
       </c>
       <c r="G408" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H408" s="2">
-        <v>0</v>
+        <v>6.0879629629629626E-3</v>
       </c>
       <c r="I408" s="1">
         <v>46237.796990740739</v>
       </c>
       <c r="J408" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K408" s="1" t="s">
         <v>11</v>
@@ -12003,16 +12003,16 @@
         <v>29</v>
       </c>
       <c r="G409" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H409" s="2">
-        <v>0</v>
+        <v>5.8912037037037041E-3</v>
       </c>
       <c r="I409" s="1">
         <v>46237.797685185185</v>
       </c>
       <c r="J409" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K409" s="1" t="s">
         <v>11</v>
@@ -12032,16 +12032,16 @@
         <v>29</v>
       </c>
       <c r="G410" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H410" s="2">
-        <v>0</v>
+        <v>6.8055555555555551E-3</v>
       </c>
       <c r="I410" s="1">
         <v>46237.797685185185</v>
       </c>
       <c r="J410" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K410" s="1" t="s">
         <v>11</v>
@@ -12070,7 +12070,7 @@
         <v>46237.798379629632</v>
       </c>
       <c r="J411" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K411" s="1" t="s">
         <v>11</v>
@@ -12148,16 +12148,16 @@
         <v>29</v>
       </c>
       <c r="G414" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H414" s="2">
-        <v>0</v>
+        <v>5.9953703703703705E-3</v>
       </c>
       <c r="I414" s="1">
         <v>46237.799768518518</v>
       </c>
       <c r="J414" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K414" s="1" t="s">
         <v>11</v>
@@ -12177,16 +12177,16 @@
         <v>29</v>
       </c>
       <c r="G415" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H415" s="2">
-        <v>0</v>
+        <v>1.2789351851851852E-2</v>
       </c>
       <c r="I415" s="1">
         <v>46237.800462962965</v>
       </c>
       <c r="J415" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K415" s="1" t="s">
         <v>11</v>
@@ -12215,7 +12215,7 @@
         <v>46237.801157407404</v>
       </c>
       <c r="J416" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K416" s="1" t="s">
         <v>11</v>
@@ -50987,6 +50987,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -51279,6 +51280,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -51589,6 +51592,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -51713,6 +51717,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -51724,6 +51729,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -51872,6 +51878,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -51882,10 +51889,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -51919,15 +51928,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -51968,18 +51980,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -51995,6 +52011,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -52004,10 +52021,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -52043,10 +52062,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -52072,6 +52093,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -52086,6 +52108,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -52120,6 +52143,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -52129,6 +52153,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -52138,6 +52163,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -52152,15 +52178,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -52190,6 +52217,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -52210,11 +52238,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -52223,6 +52253,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -52252,6 +52283,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -52261,10 +52293,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -52279,14 +52313,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -52306,10 +52343,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -52329,9 +52368,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -52366,18 +52408,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -52392,12 +52438,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -52412,10 +52458,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -52435,6 +52483,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -52454,6 +52503,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -52463,6 +52513,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -52508,6 +52559,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -52517,6 +52569,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -52531,6 +52584,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -52540,10 +52594,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -52558,6 +52614,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -52567,6 +52624,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -52586,6 +52644,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -52605,10 +52664,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -52618,6 +52679,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -52628,10 +52690,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -52646,18 +52710,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -52677,10 +52745,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -52700,6 +52770,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -52730,7 +52801,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -52745,10 +52815,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -52763,6 +52835,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -52777,11 +52850,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -52791,6 +52864,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -52806,6 +52880,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -52820,6 +52895,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -52840,6 +52916,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -52865,11 +52942,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -52888,15 +52967,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -52906,6 +52986,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -52925,6 +53006,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -52939,6 +53021,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -52958,10 +53041,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -52971,6 +53056,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -52981,6 +53067,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -53017,7 +53104,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -53026,6 +53112,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -53039,10 +53126,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\neal-pool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E69FA988-C9E6-4D44-BD65-B5736DC933D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AA478D9-436A-4FE5-B6EF-87040F6E14F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -143,7 +143,7 @@
     <t>Micro-Learn Safe Following Distance</t>
   </si>
   <si>
-    <t>Hazcom for CDL Drivers</t>
+    <t>Safe RR Crossing</t>
   </si>
   <si>
     <t>3 points of contact</t>
@@ -152,7 +152,7 @@
     <t>Vehicle &amp; Roadside Inspections CMV</t>
   </si>
   <si>
-    <t>Safe RR Crossing</t>
+    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>Neal Pool Rekers</t>
@@ -601,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>38</v>
       </c>
@@ -851,7 +851,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2"/>
@@ -946,7 +946,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>38</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>38</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H32" s="2"/>
       <c r="I32" s="1"/>
       <c r="J32" s="2"/>
@@ -1745,7 +1745,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>38</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>38</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>41</v>
       </c>
       <c r="F60" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G60" t="s">
         <v>12</v>
@@ -2315,7 +2315,7 @@
         <v>42</v>
       </c>
       <c r="F62" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G62" t="s">
         <v>13</v>
@@ -2344,7 +2344,7 @@
         <v>44</v>
       </c>
       <c r="F63" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G63" t="s">
         <v>10</v>
@@ -2373,7 +2373,7 @@
         <v>45</v>
       </c>
       <c r="F64" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G64" t="s">
         <v>10</v>
@@ -2402,7 +2402,7 @@
         <v>46</v>
       </c>
       <c r="F65" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G65" t="s">
         <v>10</v>
@@ -2431,7 +2431,7 @@
         <v>47</v>
       </c>
       <c r="F66" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G66" t="s">
         <v>10</v>
@@ -2460,7 +2460,7 @@
         <v>39</v>
       </c>
       <c r="F67" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G67" t="s">
         <v>10</v>
@@ -2489,7 +2489,7 @@
         <v>48</v>
       </c>
       <c r="F68" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G68" t="s">
         <v>10</v>
@@ -2518,7 +2518,7 @@
         <v>49</v>
       </c>
       <c r="F69" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G69" t="s">
         <v>13</v>
@@ -2547,7 +2547,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G70" t="s">
         <v>10</v>
@@ -2576,7 +2576,7 @@
         <v>51</v>
       </c>
       <c r="F71" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G71" t="s">
         <v>10</v>
@@ -2605,7 +2605,7 @@
         <v>40</v>
       </c>
       <c r="F72" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G72" t="s">
         <v>10</v>
@@ -2634,7 +2634,7 @@
         <v>52</v>
       </c>
       <c r="F73" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G73" t="s">
         <v>10</v>
@@ -2652,7 +2652,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>38</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>53</v>
       </c>
       <c r="F74" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G74" t="s">
         <v>10</v>
@@ -2692,7 +2692,7 @@
         <v>54</v>
       </c>
       <c r="F75" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G75" t="s">
         <v>13</v>
@@ -2721,7 +2721,7 @@
         <v>55</v>
       </c>
       <c r="F76" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G76" t="s">
         <v>10</v>
@@ -2750,7 +2750,7 @@
         <v>56</v>
       </c>
       <c r="F77" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G77" t="s">
         <v>10</v>
@@ -2884,7 +2884,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>38</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>38</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>38</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>38</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>38</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>41</v>
       </c>
       <c r="F127" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G127" t="s">
         <v>13</v>
@@ -4187,7 +4187,7 @@
         <v>42</v>
       </c>
       <c r="F128" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G128" t="s">
         <v>13</v>
@@ -4216,7 +4216,7 @@
         <v>44</v>
       </c>
       <c r="F129" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G129" t="s">
         <v>10</v>
@@ -4245,7 +4245,7 @@
         <v>45</v>
       </c>
       <c r="F130" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G130" t="s">
         <v>13</v>
@@ -4274,7 +4274,7 @@
         <v>46</v>
       </c>
       <c r="F131" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G131" t="s">
         <v>10</v>
@@ -4303,7 +4303,7 @@
         <v>47</v>
       </c>
       <c r="F132" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G132" t="s">
         <v>10</v>
@@ -4332,7 +4332,7 @@
         <v>39</v>
       </c>
       <c r="F133" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G133" t="s">
         <v>10</v>
@@ -4361,7 +4361,7 @@
         <v>50</v>
       </c>
       <c r="F134" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G134" t="s">
         <v>10</v>
@@ -4390,7 +4390,7 @@
         <v>40</v>
       </c>
       <c r="F135" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G135" t="s">
         <v>10</v>
@@ -4419,7 +4419,7 @@
         <v>52</v>
       </c>
       <c r="F136" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G136" t="s">
         <v>10</v>
@@ -4448,7 +4448,7 @@
         <v>53</v>
       </c>
       <c r="F137" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G137" t="s">
         <v>13</v>
@@ -4477,7 +4477,7 @@
         <v>54</v>
       </c>
       <c r="F138" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G138" t="s">
         <v>13</v>
@@ -4506,7 +4506,7 @@
         <v>55</v>
       </c>
       <c r="F139" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G139" t="s">
         <v>13</v>
@@ -4535,7 +4535,7 @@
         <v>56</v>
       </c>
       <c r="F140" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G140" t="s">
         <v>10</v>
@@ -5468,7 +5468,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>38</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>38</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>38</v>
       </c>
@@ -6404,7 +6404,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>38</v>
       </c>
@@ -7311,7 +7311,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>38</v>
       </c>
@@ -9637,7 +9637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>38</v>
       </c>
@@ -9914,7 +9914,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="336" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>38</v>
       </c>
@@ -9972,7 +9972,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>38</v>
       </c>
@@ -10415,7 +10415,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="354" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>38</v>
       </c>
@@ -10452,7 +10452,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="356" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>38</v>
       </c>
@@ -10916,7 +10916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>38</v>
       </c>
@@ -11206,7 +11206,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>38</v>
       </c>
@@ -11742,10 +11742,10 @@
         <v>29</v>
       </c>
       <c r="G400" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H400" s="2">
-        <v>0</v>
+        <v>7.1064814814814819E-3</v>
       </c>
       <c r="I400" s="1">
         <v>46237.816319444442</v>
@@ -11829,10 +11829,10 @@
         <v>29</v>
       </c>
       <c r="G403" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H403" s="2">
-        <v>0</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="I403" s="1">
         <v>46237.794212962966</v>
@@ -12206,10 +12206,10 @@
         <v>29</v>
       </c>
       <c r="G416" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H416" s="2">
-        <v>0</v>
+        <v>6.5740740740740742E-3</v>
       </c>
       <c r="I416" s="1">
         <v>46237.801157407404</v>
@@ -50987,7 +50987,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -51280,8 +51279,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -51592,7 +51589,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -51717,7 +51713,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -51729,7 +51724,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -51878,35 +51872,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -51917,44 +51905,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -51965,37 +51944,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -52006,52 +51978,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -52062,17 +52024,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -52083,32 +52042,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -52118,106 +52071,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -52227,7 +52160,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -52238,127 +52170,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -52368,62 +52274,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -52443,67 +52336,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -52513,38 +52393,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -52559,117 +52432,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -52678,99 +52528,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -52780,23 +52611,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -52805,52 +52632,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -52864,38 +52681,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -52905,7 +52715,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -52916,23 +52725,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -52942,37 +52747,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -52981,72 +52779,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -53056,76 +52840,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\neal-pool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AA478D9-436A-4FE5-B6EF-87040F6E14F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EFF99E9-F3D8-4567-8407-B280E04F6AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -143,7 +143,7 @@
     <t>Micro-Learn Safe Following Distance</t>
   </si>
   <si>
-    <t>Safe RR Crossing</t>
+    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>3 points of contact</t>
@@ -152,7 +152,7 @@
     <t>Vehicle &amp; Roadside Inspections CMV</t>
   </si>
   <si>
-    <t>Hazcom for CDL Drivers</t>
+    <t>Safe RR Crossing</t>
   </si>
   <si>
     <t>Neal Pool Rekers</t>
@@ -601,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7400"/>
+  <dimension ref="A1:K7401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -2278,7 +2278,7 @@
         <v>41</v>
       </c>
       <c r="F60" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G60" t="s">
         <v>12</v>
@@ -2315,7 +2315,7 @@
         <v>42</v>
       </c>
       <c r="F62" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G62" t="s">
         <v>13</v>
@@ -2344,7 +2344,7 @@
         <v>44</v>
       </c>
       <c r="F63" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G63" t="s">
         <v>10</v>
@@ -2373,7 +2373,7 @@
         <v>45</v>
       </c>
       <c r="F64" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G64" t="s">
         <v>10</v>
@@ -2402,7 +2402,7 @@
         <v>46</v>
       </c>
       <c r="F65" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G65" t="s">
         <v>10</v>
@@ -2431,7 +2431,7 @@
         <v>47</v>
       </c>
       <c r="F66" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G66" t="s">
         <v>10</v>
@@ -2460,7 +2460,7 @@
         <v>39</v>
       </c>
       <c r="F67" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G67" t="s">
         <v>10</v>
@@ -2489,7 +2489,7 @@
         <v>48</v>
       </c>
       <c r="F68" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G68" t="s">
         <v>10</v>
@@ -2518,7 +2518,7 @@
         <v>49</v>
       </c>
       <c r="F69" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G69" t="s">
         <v>13</v>
@@ -2547,7 +2547,7 @@
         <v>50</v>
       </c>
       <c r="F70" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G70" t="s">
         <v>10</v>
@@ -2576,7 +2576,7 @@
         <v>51</v>
       </c>
       <c r="F71" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G71" t="s">
         <v>10</v>
@@ -2605,7 +2605,7 @@
         <v>40</v>
       </c>
       <c r="F72" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G72" t="s">
         <v>10</v>
@@ -2634,7 +2634,7 @@
         <v>52</v>
       </c>
       <c r="F73" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G73" t="s">
         <v>10</v>
@@ -2663,7 +2663,7 @@
         <v>53</v>
       </c>
       <c r="F74" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G74" t="s">
         <v>10</v>
@@ -2692,7 +2692,7 @@
         <v>54</v>
       </c>
       <c r="F75" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G75" t="s">
         <v>13</v>
@@ -2721,7 +2721,7 @@
         <v>55</v>
       </c>
       <c r="F76" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G76" t="s">
         <v>10</v>
@@ -2750,7 +2750,7 @@
         <v>56</v>
       </c>
       <c r="F77" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G77" t="s">
         <v>10</v>
@@ -4158,7 +4158,7 @@
         <v>41</v>
       </c>
       <c r="F127" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G127" t="s">
         <v>13</v>
@@ -4187,7 +4187,7 @@
         <v>42</v>
       </c>
       <c r="F128" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G128" t="s">
         <v>13</v>
@@ -4216,7 +4216,7 @@
         <v>44</v>
       </c>
       <c r="F129" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G129" t="s">
         <v>10</v>
@@ -4245,7 +4245,7 @@
         <v>45</v>
       </c>
       <c r="F130" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G130" t="s">
         <v>13</v>
@@ -4274,7 +4274,7 @@
         <v>46</v>
       </c>
       <c r="F131" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G131" t="s">
         <v>10</v>
@@ -4303,7 +4303,7 @@
         <v>47</v>
       </c>
       <c r="F132" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G132" t="s">
         <v>10</v>
@@ -4332,7 +4332,7 @@
         <v>39</v>
       </c>
       <c r="F133" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G133" t="s">
         <v>10</v>
@@ -4361,7 +4361,7 @@
         <v>50</v>
       </c>
       <c r="F134" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G134" t="s">
         <v>10</v>
@@ -4390,7 +4390,7 @@
         <v>40</v>
       </c>
       <c r="F135" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G135" t="s">
         <v>10</v>
@@ -4419,7 +4419,7 @@
         <v>52</v>
       </c>
       <c r="F136" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G136" t="s">
         <v>10</v>
@@ -4448,7 +4448,7 @@
         <v>53</v>
       </c>
       <c r="F137" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G137" t="s">
         <v>13</v>
@@ -4477,7 +4477,7 @@
         <v>54</v>
       </c>
       <c r="F138" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G138" t="s">
         <v>13</v>
@@ -4506,7 +4506,7 @@
         <v>55</v>
       </c>
       <c r="F139" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G139" t="s">
         <v>13</v>
@@ -4535,7 +4535,7 @@
         <v>56</v>
       </c>
       <c r="F140" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G140" t="s">
         <v>10</v>
@@ -50987,6 +50987,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -51279,6 +51280,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -51589,6 +51592,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -51713,6 +51717,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -51724,6 +51729,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -51872,29 +51878,35 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -51905,35 +51917,44 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -51944,30 +51965,37 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -51978,42 +52006,52 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -52024,14 +52062,17 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -52042,26 +52083,32 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -52071,86 +52118,107 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -52160,6 +52228,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -52170,101 +52239,127 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -52274,49 +52369,62 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -52331,59 +52439,73 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -52393,31 +52515,38 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -52427,99 +52556,123 @@
       <c r="K7287" s="1"/>
     </row>
     <row r="7288" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7288" s="2"/>
       <c r="I7288" s="1"/>
       <c r="J7288" s="2"/>
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -52528,80 +52681,99 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -52611,67 +52783,83 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -52681,31 +52869,38 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -52715,6 +52910,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -52725,19 +52921,23 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -52747,90 +52947,112 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -52840,51 +53062,71 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7394" s="2"/>
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7398" s="2"/>
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
